--- a/calendario-fpcv-eventos.xlsx
+++ b/calendario-fpcv-eventos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9d8b40b6d026ffaf/Desktop - LG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="11_284319F7869D0E8CAFE5D3B7EC9E0EADF7154BC1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4CB657C1-35B9-4DF0-9E68-C9829C582809}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="11_284319F7869D0E8CAFE5D3B7EC9E0EADF7154BC1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2ABA772-3AFD-4C72-83A7-45F4B7617D40}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="57">
   <si>
     <t>Inicio</t>
   </si>
@@ -189,6 +189,12 @@
   </si>
   <si>
     <t>Mañana</t>
+  </si>
+  <si>
+    <t>Beoncia</t>
+  </si>
+  <si>
+    <t>Cullera</t>
   </si>
 </sst>
 </file>
@@ -1096,12 +1102,24 @@
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="7"/>
+      <c r="A15" s="5">
+        <v>46389</v>
+      </c>
+      <c r="B15" s="5">
+        <v>46389</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F15" s="7">
+        <v>2</v>
+      </c>
       <c r="G15" s="6"/>
       <c r="H15" s="6"/>
       <c r="I15" s="6"/>

--- a/calendario-fpcv-eventos.xlsx
+++ b/calendario-fpcv-eventos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9d8b40b6d026ffaf/Desktop - LG/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bea Pallero\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="11_284319F7869D0E8CAFE5D3B7EC9E0EADF7154BC1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2ABA772-3AFD-4C72-83A7-45F4B7617D40}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D9C4B03-FB26-4B8D-B8AD-6ADB8679388E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cómo se usa" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="62">
   <si>
     <t>Inicio</t>
   </si>
@@ -173,28 +173,43 @@
     <t>Sube este archivo al repositorio de GitHub sustituyendo al anterior. La página se actualiza sola en 1-2 minutos.</t>
   </si>
   <si>
-    <t>Prueba</t>
-  </si>
-  <si>
-    <t>Algemesí</t>
-  </si>
-  <si>
     <t>Todo el día</t>
   </si>
   <si>
-    <t>Mestalla</t>
-  </si>
-  <si>
-    <t>Valencia</t>
-  </si>
-  <si>
     <t>Mañana</t>
   </si>
   <si>
-    <t>Beoncia</t>
-  </si>
-  <si>
-    <t>Cullera</t>
+    <t>Rafelbunyol</t>
+  </si>
+  <si>
+    <t>Trofeo Territorial Alginet</t>
+  </si>
+  <si>
+    <t>Alginet</t>
+  </si>
+  <si>
+    <t>Tarde</t>
+  </si>
+  <si>
+    <t>Llocnou de Sant Jeroni</t>
+  </si>
+  <si>
+    <t>L'Alcúdia de Crespins</t>
+  </si>
+  <si>
+    <t>Trofeo Iniciación Skid Xeraco</t>
+  </si>
+  <si>
+    <t>Trofeo Iniciación Rafelbunyol</t>
+  </si>
+  <si>
+    <t>Trofeo Iniciación Llombai o Llocnou</t>
+  </si>
+  <si>
+    <t>Trofeo Iniciación 8Rodes Barxeta</t>
+  </si>
+  <si>
+    <t>Trofeo Iniciación L'Alcúdia de Crespins</t>
   </si>
 </sst>
 </file>
@@ -643,23 +658,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="100" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B1" s="2"/>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
       <c r="B2" s="2"/>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>31</v>
       </c>
@@ -667,7 +682,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>0</v>
       </c>
@@ -675,7 +690,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>1</v>
       </c>
@@ -683,7 +698,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>2</v>
       </c>
@@ -691,7 +706,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>3</v>
       </c>
@@ -699,7 +714,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="28" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>4</v>
       </c>
@@ -707,7 +722,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="28" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>5</v>
       </c>
@@ -715,7 +730,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="28" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>39</v>
       </c>
@@ -723,11 +738,11 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="3"/>
       <c r="B11" s="2"/>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>41</v>
       </c>
@@ -735,7 +750,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>43</v>
       </c>
@@ -743,7 +758,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>45</v>
       </c>
@@ -751,7 +766,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>47</v>
       </c>
@@ -767,7 +782,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I300"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="13" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
@@ -777,7 +792,7 @@
     <col min="7" max="9" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -806,7 +821,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="5">
         <v>46298</v>
       </c>
@@ -820,83 +835,91 @@
         <v>10</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F2" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" s="6"/>
       <c r="H2" s="6"/>
       <c r="I2" s="6"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
+        <v>46312</v>
+      </c>
+      <c r="B3" s="5">
+        <v>46312</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="7">
+        <v>1</v>
+      </c>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="I3" s="6"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
         <v>46311</v>
-      </c>
-      <c r="B3" s="5">
-        <v>46313</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="7">
-        <v>0</v>
-      </c>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A4" s="5">
-        <v>46312</v>
       </c>
       <c r="B4" s="5">
         <v>46313</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F4" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" s="6"/>
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
-        <v>46319</v>
+        <v>46312</v>
       </c>
       <c r="B5" s="5">
-        <v>46319</v>
+        <v>46313</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="6"/>
+        <v>57</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="E5" s="6" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F5" s="7">
         <v>1</v>
       </c>
       <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="H5" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>46319</v>
       </c>
@@ -904,11 +927,9 @@
         <v>46319</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>20</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="D6" s="6"/>
       <c r="E6" s="6" t="s">
         <v>21</v>
       </c>
@@ -919,245 +940,289 @@
       <c r="H6" s="6"/>
       <c r="I6" s="6"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
+        <v>46319</v>
+      </c>
+      <c r="B7" s="5">
+        <v>46319</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="7">
+        <v>2</v>
+      </c>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="I7" s="6"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
         <v>46333</v>
       </c>
-      <c r="B7" s="5">
-        <v>46334</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" s="7">
-        <v>0</v>
-      </c>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A8" s="5">
-        <v>46340</v>
-      </c>
       <c r="B8" s="5">
-        <v>46341</v>
+        <v>46333</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F8" s="7">
         <v>1</v>
       </c>
       <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
+      <c r="H8" s="6" t="s">
+        <v>49</v>
+      </c>
       <c r="I8" s="6"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
-        <v>46347</v>
+        <v>46333</v>
       </c>
       <c r="B9" s="5">
-        <v>46348</v>
+        <v>46333</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="D9" s="6"/>
       <c r="E9" s="6" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F9" s="7">
         <v>1</v>
       </c>
       <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
+      <c r="H9" s="6" t="s">
+        <v>49</v>
+      </c>
       <c r="I9" s="6"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="5">
-        <v>46354</v>
+        <v>46333</v>
       </c>
       <c r="B10" s="5">
-        <v>46355</v>
+        <v>46334</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D10" s="6"/>
       <c r="E10" s="6" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F10" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" s="6"/>
       <c r="H10" s="6"/>
       <c r="I10" s="6"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
-        <v>46354</v>
+        <v>46339</v>
       </c>
       <c r="B11" s="5">
-        <v>46354</v>
+        <v>46339</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="F11" s="7">
-        <v>0</v>
-      </c>
-      <c r="G11" s="6"/>
+        <v>1</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>54</v>
+      </c>
       <c r="H11" s="6"/>
       <c r="I11" s="6"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
-        <v>46368</v>
+        <v>46340</v>
       </c>
       <c r="B12" s="5">
-        <v>46369</v>
+        <v>46340</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D12" s="6"/>
+        <v>23</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>13</v>
+      </c>
       <c r="E12" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F12" s="7">
+        <v>2</v>
+      </c>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="I12" s="6"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" s="5">
+        <v>46347</v>
+      </c>
+      <c r="B13" s="5">
+        <v>46347</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" s="7">
         <v>1</v>
-      </c>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A13" s="5">
-        <v>46375</v>
-      </c>
-      <c r="B13" s="5">
-        <v>46375</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F13" s="7">
-        <v>2</v>
       </c>
       <c r="G13" s="6"/>
       <c r="H13" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I13" s="6"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="5">
-        <v>46382</v>
+        <v>46347</v>
       </c>
       <c r="B14" s="5">
-        <v>46383</v>
+        <v>46347</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F14" s="7">
         <v>1</v>
       </c>
       <c r="G14" s="6"/>
       <c r="H14" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+        <v>49</v>
+      </c>
+      <c r="I14" s="6"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
-        <v>46389</v>
+        <v>46347</v>
       </c>
       <c r="B15" s="5">
-        <v>46389</v>
+        <v>46348</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>56</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="D15" s="6"/>
       <c r="E15" s="6" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F15" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G15" s="6"/>
       <c r="H15" s="6"/>
       <c r="I15" s="6"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="7"/>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" s="5">
+        <v>46354</v>
+      </c>
+      <c r="B16" s="5">
+        <v>46354</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F16" s="7">
+        <v>2</v>
+      </c>
       <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
+      <c r="H16" s="6" t="s">
+        <v>50</v>
+      </c>
       <c r="I16" s="6"/>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A17" s="5"/>
-      <c r="B17" s="5"/>
-      <c r="C17" s="6"/>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" s="5">
+        <v>46354</v>
+      </c>
+      <c r="B17" s="5">
+        <v>46355</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>25</v>
+      </c>
       <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="7"/>
+      <c r="E17" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F17" s="7">
+        <v>0</v>
+      </c>
       <c r="G17" s="6"/>
       <c r="H17" s="6"/>
       <c r="I17" s="6"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A18" s="5"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="6"/>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18" s="5">
+        <v>46368</v>
+      </c>
+      <c r="B18" s="5">
+        <v>46368</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>29</v>
+      </c>
       <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="7"/>
+      <c r="E18" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F18" s="7">
+        <v>1</v>
+      </c>
       <c r="G18" s="6"/>
       <c r="H18" s="6"/>
       <c r="I18" s="6"/>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
       <c r="C19" s="6"/>
@@ -1168,7 +1233,7 @@
       <c r="H19" s="6"/>
       <c r="I19" s="6"/>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="C20" s="6"/>
@@ -1179,7 +1244,7 @@
       <c r="H20" s="6"/>
       <c r="I20" s="6"/>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
       <c r="C21" s="6"/>
@@ -1190,7 +1255,7 @@
       <c r="H21" s="6"/>
       <c r="I21" s="6"/>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="5"/>
       <c r="B22" s="5"/>
       <c r="C22" s="6"/>
@@ -1201,7 +1266,7 @@
       <c r="H22" s="6"/>
       <c r="I22" s="6"/>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="C23" s="6"/>
@@ -1212,7 +1277,7 @@
       <c r="H23" s="6"/>
       <c r="I23" s="6"/>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="5"/>
       <c r="B24" s="5"/>
       <c r="C24" s="6"/>
@@ -1223,7 +1288,7 @@
       <c r="H24" s="6"/>
       <c r="I24" s="6"/>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="5"/>
       <c r="B25" s="5"/>
       <c r="C25" s="6"/>
@@ -1234,7 +1299,7 @@
       <c r="H25" s="6"/>
       <c r="I25" s="6"/>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="5"/>
       <c r="B26" s="5"/>
       <c r="C26" s="6"/>
@@ -1245,7 +1310,7 @@
       <c r="H26" s="6"/>
       <c r="I26" s="6"/>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="5"/>
       <c r="B27" s="5"/>
       <c r="C27" s="6"/>
@@ -1256,7 +1321,7 @@
       <c r="H27" s="6"/>
       <c r="I27" s="6"/>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="5"/>
       <c r="B28" s="5"/>
       <c r="C28" s="6"/>
@@ -1267,7 +1332,7 @@
       <c r="H28" s="6"/>
       <c r="I28" s="6"/>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="5"/>
       <c r="B29" s="5"/>
       <c r="C29" s="6"/>
@@ -1278,7 +1343,7 @@
       <c r="H29" s="6"/>
       <c r="I29" s="6"/>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="5"/>
       <c r="B30" s="5"/>
       <c r="C30" s="6"/>
@@ -1289,7 +1354,7 @@
       <c r="H30" s="6"/>
       <c r="I30" s="6"/>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="5"/>
       <c r="B31" s="5"/>
       <c r="C31" s="6"/>
@@ -1300,7 +1365,7 @@
       <c r="H31" s="6"/>
       <c r="I31" s="6"/>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="5"/>
       <c r="B32" s="5"/>
       <c r="C32" s="6"/>
@@ -1311,7 +1376,7 @@
       <c r="H32" s="6"/>
       <c r="I32" s="6"/>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="5"/>
       <c r="B33" s="5"/>
       <c r="C33" s="6"/>
@@ -1322,7 +1387,7 @@
       <c r="H33" s="6"/>
       <c r="I33" s="6"/>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="5"/>
       <c r="B34" s="5"/>
       <c r="C34" s="6"/>
@@ -1333,7 +1398,7 @@
       <c r="H34" s="6"/>
       <c r="I34" s="6"/>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="5"/>
       <c r="B35" s="5"/>
       <c r="C35" s="6"/>
@@ -1344,7 +1409,7 @@
       <c r="H35" s="6"/>
       <c r="I35" s="6"/>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="5"/>
       <c r="B36" s="5"/>
       <c r="C36" s="6"/>
@@ -1355,7 +1420,7 @@
       <c r="H36" s="6"/>
       <c r="I36" s="6"/>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="5"/>
       <c r="B37" s="5"/>
       <c r="C37" s="6"/>
@@ -1366,7 +1431,7 @@
       <c r="H37" s="6"/>
       <c r="I37" s="6"/>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" s="5"/>
       <c r="B38" s="5"/>
       <c r="C38" s="6"/>
@@ -1377,7 +1442,7 @@
       <c r="H38" s="6"/>
       <c r="I38" s="6"/>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" s="5"/>
       <c r="B39" s="5"/>
       <c r="C39" s="6"/>
@@ -1388,7 +1453,7 @@
       <c r="H39" s="6"/>
       <c r="I39" s="6"/>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" s="5"/>
       <c r="B40" s="5"/>
       <c r="C40" s="6"/>
@@ -1399,7 +1464,7 @@
       <c r="H40" s="6"/>
       <c r="I40" s="6"/>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" s="5"/>
       <c r="B41" s="5"/>
       <c r="C41" s="6"/>
@@ -1410,7 +1475,7 @@
       <c r="H41" s="6"/>
       <c r="I41" s="6"/>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" s="5"/>
       <c r="B42" s="5"/>
       <c r="C42" s="6"/>
@@ -1421,7 +1486,7 @@
       <c r="H42" s="6"/>
       <c r="I42" s="6"/>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" s="5"/>
       <c r="B43" s="5"/>
       <c r="C43" s="6"/>
@@ -1432,7 +1497,7 @@
       <c r="H43" s="6"/>
       <c r="I43" s="6"/>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" s="5"/>
       <c r="B44" s="5"/>
       <c r="C44" s="6"/>
@@ -1443,7 +1508,7 @@
       <c r="H44" s="6"/>
       <c r="I44" s="6"/>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" s="5"/>
       <c r="B45" s="5"/>
       <c r="C45" s="6"/>
@@ -1454,7 +1519,7 @@
       <c r="H45" s="6"/>
       <c r="I45" s="6"/>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" s="5"/>
       <c r="B46" s="5"/>
       <c r="C46" s="6"/>
@@ -1465,7 +1530,7 @@
       <c r="H46" s="6"/>
       <c r="I46" s="6"/>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" s="5"/>
       <c r="B47" s="5"/>
       <c r="C47" s="6"/>
@@ -1476,7 +1541,7 @@
       <c r="H47" s="6"/>
       <c r="I47" s="6"/>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" s="5"/>
       <c r="B48" s="5"/>
       <c r="C48" s="6"/>
@@ -1487,7 +1552,7 @@
       <c r="H48" s="6"/>
       <c r="I48" s="6"/>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" s="5"/>
       <c r="B49" s="5"/>
       <c r="C49" s="6"/>
@@ -1498,7 +1563,7 @@
       <c r="H49" s="6"/>
       <c r="I49" s="6"/>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" s="5"/>
       <c r="B50" s="5"/>
       <c r="C50" s="6"/>
@@ -1509,7 +1574,7 @@
       <c r="H50" s="6"/>
       <c r="I50" s="6"/>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" s="5"/>
       <c r="B51" s="5"/>
       <c r="C51" s="6"/>
@@ -1520,7 +1585,7 @@
       <c r="H51" s="6"/>
       <c r="I51" s="6"/>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" s="5"/>
       <c r="B52" s="5"/>
       <c r="C52" s="6"/>
@@ -1531,7 +1596,7 @@
       <c r="H52" s="6"/>
       <c r="I52" s="6"/>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" s="5"/>
       <c r="B53" s="5"/>
       <c r="C53" s="6"/>
@@ -1542,7 +1607,7 @@
       <c r="H53" s="6"/>
       <c r="I53" s="6"/>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" s="5"/>
       <c r="B54" s="5"/>
       <c r="C54" s="6"/>
@@ -1553,7 +1618,7 @@
       <c r="H54" s="6"/>
       <c r="I54" s="6"/>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" s="5"/>
       <c r="B55" s="5"/>
       <c r="C55" s="6"/>
@@ -1564,7 +1629,7 @@
       <c r="H55" s="6"/>
       <c r="I55" s="6"/>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" s="5"/>
       <c r="B56" s="5"/>
       <c r="C56" s="6"/>
@@ -1575,7 +1640,7 @@
       <c r="H56" s="6"/>
       <c r="I56" s="6"/>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" s="5"/>
       <c r="B57" s="5"/>
       <c r="C57" s="6"/>
@@ -1586,7 +1651,7 @@
       <c r="H57" s="6"/>
       <c r="I57" s="6"/>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" s="5"/>
       <c r="B58" s="5"/>
       <c r="C58" s="6"/>
@@ -1597,7 +1662,7 @@
       <c r="H58" s="6"/>
       <c r="I58" s="6"/>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" s="5"/>
       <c r="B59" s="5"/>
       <c r="C59" s="6"/>
@@ -1608,7 +1673,7 @@
       <c r="H59" s="6"/>
       <c r="I59" s="6"/>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" s="5"/>
       <c r="B60" s="5"/>
       <c r="C60" s="6"/>
@@ -1619,7 +1684,7 @@
       <c r="H60" s="6"/>
       <c r="I60" s="6"/>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" s="5"/>
       <c r="B61" s="5"/>
       <c r="C61" s="6"/>
@@ -1630,7 +1695,7 @@
       <c r="H61" s="6"/>
       <c r="I61" s="6"/>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" s="5"/>
       <c r="B62" s="5"/>
       <c r="C62" s="6"/>
@@ -1641,7 +1706,7 @@
       <c r="H62" s="6"/>
       <c r="I62" s="6"/>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" s="5"/>
       <c r="B63" s="5"/>
       <c r="C63" s="6"/>
@@ -1652,7 +1717,7 @@
       <c r="H63" s="6"/>
       <c r="I63" s="6"/>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" s="5"/>
       <c r="B64" s="5"/>
       <c r="C64" s="6"/>
@@ -1663,7 +1728,7 @@
       <c r="H64" s="6"/>
       <c r="I64" s="6"/>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" s="5"/>
       <c r="B65" s="5"/>
       <c r="C65" s="6"/>
@@ -1674,7 +1739,7 @@
       <c r="H65" s="6"/>
       <c r="I65" s="6"/>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" s="5"/>
       <c r="B66" s="5"/>
       <c r="C66" s="6"/>
@@ -1685,7 +1750,7 @@
       <c r="H66" s="6"/>
       <c r="I66" s="6"/>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" s="5"/>
       <c r="B67" s="5"/>
       <c r="C67" s="6"/>
@@ -1696,7 +1761,7 @@
       <c r="H67" s="6"/>
       <c r="I67" s="6"/>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" s="5"/>
       <c r="B68" s="5"/>
       <c r="C68" s="6"/>
@@ -1707,7 +1772,7 @@
       <c r="H68" s="6"/>
       <c r="I68" s="6"/>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" s="5"/>
       <c r="B69" s="5"/>
       <c r="C69" s="6"/>
@@ -1718,7 +1783,7 @@
       <c r="H69" s="6"/>
       <c r="I69" s="6"/>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" s="5"/>
       <c r="B70" s="5"/>
       <c r="C70" s="6"/>
@@ -1729,7 +1794,7 @@
       <c r="H70" s="6"/>
       <c r="I70" s="6"/>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" s="5"/>
       <c r="B71" s="5"/>
       <c r="C71" s="6"/>
@@ -1740,7 +1805,7 @@
       <c r="H71" s="6"/>
       <c r="I71" s="6"/>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" s="5"/>
       <c r="B72" s="5"/>
       <c r="C72" s="6"/>
@@ -1751,7 +1816,7 @@
       <c r="H72" s="6"/>
       <c r="I72" s="6"/>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" s="5"/>
       <c r="B73" s="5"/>
       <c r="C73" s="6"/>
@@ -1762,7 +1827,7 @@
       <c r="H73" s="6"/>
       <c r="I73" s="6"/>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" s="5"/>
       <c r="B74" s="5"/>
       <c r="C74" s="6"/>
@@ -1773,7 +1838,7 @@
       <c r="H74" s="6"/>
       <c r="I74" s="6"/>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" s="5"/>
       <c r="B75" s="5"/>
       <c r="C75" s="6"/>
@@ -1784,7 +1849,7 @@
       <c r="H75" s="6"/>
       <c r="I75" s="6"/>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" s="5"/>
       <c r="B76" s="5"/>
       <c r="C76" s="6"/>
@@ -1795,7 +1860,7 @@
       <c r="H76" s="6"/>
       <c r="I76" s="6"/>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" s="5"/>
       <c r="B77" s="5"/>
       <c r="C77" s="6"/>
@@ -1806,7 +1871,7 @@
       <c r="H77" s="6"/>
       <c r="I77" s="6"/>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" s="5"/>
       <c r="B78" s="5"/>
       <c r="C78" s="6"/>
@@ -1817,7 +1882,7 @@
       <c r="H78" s="6"/>
       <c r="I78" s="6"/>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" s="5"/>
       <c r="B79" s="5"/>
       <c r="C79" s="6"/>
@@ -1828,7 +1893,7 @@
       <c r="H79" s="6"/>
       <c r="I79" s="6"/>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80" s="5"/>
       <c r="B80" s="5"/>
       <c r="C80" s="6"/>
@@ -1839,7 +1904,7 @@
       <c r="H80" s="6"/>
       <c r="I80" s="6"/>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A81" s="5"/>
       <c r="B81" s="5"/>
       <c r="C81" s="6"/>
@@ -1850,7 +1915,7 @@
       <c r="H81" s="6"/>
       <c r="I81" s="6"/>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A82" s="5"/>
       <c r="B82" s="5"/>
       <c r="C82" s="6"/>
@@ -1861,7 +1926,7 @@
       <c r="H82" s="6"/>
       <c r="I82" s="6"/>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A83" s="5"/>
       <c r="B83" s="5"/>
       <c r="C83" s="6"/>
@@ -1872,7 +1937,7 @@
       <c r="H83" s="6"/>
       <c r="I83" s="6"/>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A84" s="5"/>
       <c r="B84" s="5"/>
       <c r="C84" s="6"/>
@@ -1883,7 +1948,7 @@
       <c r="H84" s="6"/>
       <c r="I84" s="6"/>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A85" s="5"/>
       <c r="B85" s="5"/>
       <c r="C85" s="6"/>
@@ -1894,7 +1959,7 @@
       <c r="H85" s="6"/>
       <c r="I85" s="6"/>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A86" s="5"/>
       <c r="B86" s="5"/>
       <c r="C86" s="6"/>
@@ -1905,7 +1970,7 @@
       <c r="H86" s="6"/>
       <c r="I86" s="6"/>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A87" s="5"/>
       <c r="B87" s="5"/>
       <c r="C87" s="6"/>
@@ -1916,7 +1981,7 @@
       <c r="H87" s="6"/>
       <c r="I87" s="6"/>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A88" s="5"/>
       <c r="B88" s="5"/>
       <c r="C88" s="6"/>
@@ -1927,7 +1992,7 @@
       <c r="H88" s="6"/>
       <c r="I88" s="6"/>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A89" s="5"/>
       <c r="B89" s="5"/>
       <c r="C89" s="6"/>
@@ -1938,7 +2003,7 @@
       <c r="H89" s="6"/>
       <c r="I89" s="6"/>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A90" s="5"/>
       <c r="B90" s="5"/>
       <c r="C90" s="6"/>
@@ -1949,7 +2014,7 @@
       <c r="H90" s="6"/>
       <c r="I90" s="6"/>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A91" s="5"/>
       <c r="B91" s="5"/>
       <c r="C91" s="6"/>
@@ -1960,7 +2025,7 @@
       <c r="H91" s="6"/>
       <c r="I91" s="6"/>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A92" s="5"/>
       <c r="B92" s="5"/>
       <c r="C92" s="6"/>
@@ -1971,7 +2036,7 @@
       <c r="H92" s="6"/>
       <c r="I92" s="6"/>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A93" s="5"/>
       <c r="B93" s="5"/>
       <c r="C93" s="6"/>
@@ -1982,7 +2047,7 @@
       <c r="H93" s="6"/>
       <c r="I93" s="6"/>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A94" s="5"/>
       <c r="B94" s="5"/>
       <c r="C94" s="6"/>
@@ -1993,7 +2058,7 @@
       <c r="H94" s="6"/>
       <c r="I94" s="6"/>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A95" s="5"/>
       <c r="B95" s="5"/>
       <c r="C95" s="6"/>
@@ -2004,7 +2069,7 @@
       <c r="H95" s="6"/>
       <c r="I95" s="6"/>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A96" s="5"/>
       <c r="B96" s="5"/>
       <c r="C96" s="6"/>
@@ -2015,7 +2080,7 @@
       <c r="H96" s="6"/>
       <c r="I96" s="6"/>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A97" s="5"/>
       <c r="B97" s="5"/>
       <c r="C97" s="6"/>
@@ -2026,7 +2091,7 @@
       <c r="H97" s="6"/>
       <c r="I97" s="6"/>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A98" s="5"/>
       <c r="B98" s="5"/>
       <c r="C98" s="6"/>
@@ -2037,7 +2102,7 @@
       <c r="H98" s="6"/>
       <c r="I98" s="6"/>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A99" s="5"/>
       <c r="B99" s="5"/>
       <c r="C99" s="6"/>
@@ -2048,7 +2113,7 @@
       <c r="H99" s="6"/>
       <c r="I99" s="6"/>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A100" s="5"/>
       <c r="B100" s="5"/>
       <c r="C100" s="6"/>
@@ -2059,7 +2124,7 @@
       <c r="H100" s="6"/>
       <c r="I100" s="6"/>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A101" s="5"/>
       <c r="B101" s="5"/>
       <c r="C101" s="6"/>
@@ -2070,7 +2135,7 @@
       <c r="H101" s="6"/>
       <c r="I101" s="6"/>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A102" s="5"/>
       <c r="B102" s="5"/>
       <c r="C102" s="6"/>
@@ -2081,7 +2146,7 @@
       <c r="H102" s="6"/>
       <c r="I102" s="6"/>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A103" s="5"/>
       <c r="B103" s="5"/>
       <c r="C103" s="6"/>
@@ -2092,7 +2157,7 @@
       <c r="H103" s="6"/>
       <c r="I103" s="6"/>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A104" s="5"/>
       <c r="B104" s="5"/>
       <c r="C104" s="6"/>
@@ -2103,7 +2168,7 @@
       <c r="H104" s="6"/>
       <c r="I104" s="6"/>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A105" s="5"/>
       <c r="B105" s="5"/>
       <c r="C105" s="6"/>
@@ -2114,7 +2179,7 @@
       <c r="H105" s="6"/>
       <c r="I105" s="6"/>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A106" s="5"/>
       <c r="B106" s="5"/>
       <c r="C106" s="6"/>
@@ -2125,7 +2190,7 @@
       <c r="H106" s="6"/>
       <c r="I106" s="6"/>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A107" s="5"/>
       <c r="B107" s="5"/>
       <c r="C107" s="6"/>
@@ -2136,7 +2201,7 @@
       <c r="H107" s="6"/>
       <c r="I107" s="6"/>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A108" s="5"/>
       <c r="B108" s="5"/>
       <c r="C108" s="6"/>
@@ -2147,7 +2212,7 @@
       <c r="H108" s="6"/>
       <c r="I108" s="6"/>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A109" s="5"/>
       <c r="B109" s="5"/>
       <c r="C109" s="6"/>
@@ -2158,7 +2223,7 @@
       <c r="H109" s="6"/>
       <c r="I109" s="6"/>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A110" s="5"/>
       <c r="B110" s="5"/>
       <c r="C110" s="6"/>
@@ -2169,7 +2234,7 @@
       <c r="H110" s="6"/>
       <c r="I110" s="6"/>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A111" s="5"/>
       <c r="B111" s="5"/>
       <c r="C111" s="6"/>
@@ -2180,7 +2245,7 @@
       <c r="H111" s="6"/>
       <c r="I111" s="6"/>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A112" s="5"/>
       <c r="B112" s="5"/>
       <c r="C112" s="6"/>
@@ -2191,7 +2256,7 @@
       <c r="H112" s="6"/>
       <c r="I112" s="6"/>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A113" s="5"/>
       <c r="B113" s="5"/>
       <c r="C113" s="6"/>
@@ -2202,7 +2267,7 @@
       <c r="H113" s="6"/>
       <c r="I113" s="6"/>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A114" s="5"/>
       <c r="B114" s="5"/>
       <c r="C114" s="6"/>
@@ -2213,7 +2278,7 @@
       <c r="H114" s="6"/>
       <c r="I114" s="6"/>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A115" s="5"/>
       <c r="B115" s="5"/>
       <c r="C115" s="6"/>
@@ -2224,7 +2289,7 @@
       <c r="H115" s="6"/>
       <c r="I115" s="6"/>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A116" s="5"/>
       <c r="B116" s="5"/>
       <c r="C116" s="6"/>
@@ -2235,7 +2300,7 @@
       <c r="H116" s="6"/>
       <c r="I116" s="6"/>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A117" s="5"/>
       <c r="B117" s="5"/>
       <c r="C117" s="6"/>
@@ -2246,7 +2311,7 @@
       <c r="H117" s="6"/>
       <c r="I117" s="6"/>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A118" s="5"/>
       <c r="B118" s="5"/>
       <c r="C118" s="6"/>
@@ -2257,7 +2322,7 @@
       <c r="H118" s="6"/>
       <c r="I118" s="6"/>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A119" s="5"/>
       <c r="B119" s="5"/>
       <c r="C119" s="6"/>
@@ -2268,7 +2333,7 @@
       <c r="H119" s="6"/>
       <c r="I119" s="6"/>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A120" s="5"/>
       <c r="B120" s="5"/>
       <c r="C120" s="6"/>
@@ -2279,7 +2344,7 @@
       <c r="H120" s="6"/>
       <c r="I120" s="6"/>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A121" s="5"/>
       <c r="B121" s="5"/>
       <c r="C121" s="6"/>
@@ -2290,7 +2355,7 @@
       <c r="H121" s="6"/>
       <c r="I121" s="6"/>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A122" s="5"/>
       <c r="B122" s="5"/>
       <c r="C122" s="6"/>
@@ -2301,7 +2366,7 @@
       <c r="H122" s="6"/>
       <c r="I122" s="6"/>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A123" s="5"/>
       <c r="B123" s="5"/>
       <c r="C123" s="6"/>
@@ -2312,7 +2377,7 @@
       <c r="H123" s="6"/>
       <c r="I123" s="6"/>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A124" s="5"/>
       <c r="B124" s="5"/>
       <c r="C124" s="6"/>
@@ -2323,7 +2388,7 @@
       <c r="H124" s="6"/>
       <c r="I124" s="6"/>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A125" s="5"/>
       <c r="B125" s="5"/>
       <c r="C125" s="6"/>
@@ -2334,7 +2399,7 @@
       <c r="H125" s="6"/>
       <c r="I125" s="6"/>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A126" s="5"/>
       <c r="B126" s="5"/>
       <c r="C126" s="6"/>
@@ -2345,7 +2410,7 @@
       <c r="H126" s="6"/>
       <c r="I126" s="6"/>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A127" s="5"/>
       <c r="B127" s="5"/>
       <c r="C127" s="6"/>
@@ -2356,7 +2421,7 @@
       <c r="H127" s="6"/>
       <c r="I127" s="6"/>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A128" s="5"/>
       <c r="B128" s="5"/>
       <c r="C128" s="6"/>
@@ -2367,7 +2432,7 @@
       <c r="H128" s="6"/>
       <c r="I128" s="6"/>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A129" s="5"/>
       <c r="B129" s="5"/>
       <c r="C129" s="6"/>
@@ -2378,7 +2443,7 @@
       <c r="H129" s="6"/>
       <c r="I129" s="6"/>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A130" s="5"/>
       <c r="B130" s="5"/>
       <c r="C130" s="6"/>
@@ -2389,7 +2454,7 @@
       <c r="H130" s="6"/>
       <c r="I130" s="6"/>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A131" s="5"/>
       <c r="B131" s="5"/>
       <c r="C131" s="6"/>
@@ -2400,7 +2465,7 @@
       <c r="H131" s="6"/>
       <c r="I131" s="6"/>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A132" s="5"/>
       <c r="B132" s="5"/>
       <c r="C132" s="6"/>
@@ -2411,7 +2476,7 @@
       <c r="H132" s="6"/>
       <c r="I132" s="6"/>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A133" s="5"/>
       <c r="B133" s="5"/>
       <c r="C133" s="6"/>
@@ -2422,7 +2487,7 @@
       <c r="H133" s="6"/>
       <c r="I133" s="6"/>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A134" s="5"/>
       <c r="B134" s="5"/>
       <c r="C134" s="6"/>
@@ -2433,7 +2498,7 @@
       <c r="H134" s="6"/>
       <c r="I134" s="6"/>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A135" s="5"/>
       <c r="B135" s="5"/>
       <c r="C135" s="6"/>
@@ -2444,7 +2509,7 @@
       <c r="H135" s="6"/>
       <c r="I135" s="6"/>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A136" s="5"/>
       <c r="B136" s="5"/>
       <c r="C136" s="6"/>
@@ -2455,7 +2520,7 @@
       <c r="H136" s="6"/>
       <c r="I136" s="6"/>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A137" s="5"/>
       <c r="B137" s="5"/>
       <c r="C137" s="6"/>
@@ -2466,7 +2531,7 @@
       <c r="H137" s="6"/>
       <c r="I137" s="6"/>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A138" s="5"/>
       <c r="B138" s="5"/>
       <c r="C138" s="6"/>
@@ -2477,7 +2542,7 @@
       <c r="H138" s="6"/>
       <c r="I138" s="6"/>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A139" s="5"/>
       <c r="B139" s="5"/>
       <c r="C139" s="6"/>
@@ -2488,7 +2553,7 @@
       <c r="H139" s="6"/>
       <c r="I139" s="6"/>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A140" s="5"/>
       <c r="B140" s="5"/>
       <c r="C140" s="6"/>
@@ -2499,7 +2564,7 @@
       <c r="H140" s="6"/>
       <c r="I140" s="6"/>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A141" s="5"/>
       <c r="B141" s="5"/>
       <c r="C141" s="6"/>
@@ -2510,7 +2575,7 @@
       <c r="H141" s="6"/>
       <c r="I141" s="6"/>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A142" s="5"/>
       <c r="B142" s="5"/>
       <c r="C142" s="6"/>
@@ -2521,7 +2586,7 @@
       <c r="H142" s="6"/>
       <c r="I142" s="6"/>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A143" s="5"/>
       <c r="B143" s="5"/>
       <c r="C143" s="6"/>
@@ -2532,7 +2597,7 @@
       <c r="H143" s="6"/>
       <c r="I143" s="6"/>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A144" s="5"/>
       <c r="B144" s="5"/>
       <c r="C144" s="6"/>
@@ -2543,7 +2608,7 @@
       <c r="H144" s="6"/>
       <c r="I144" s="6"/>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A145" s="5"/>
       <c r="B145" s="5"/>
       <c r="C145" s="6"/>
@@ -2554,7 +2619,7 @@
       <c r="H145" s="6"/>
       <c r="I145" s="6"/>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A146" s="5"/>
       <c r="B146" s="5"/>
       <c r="C146" s="6"/>
@@ -2565,7 +2630,7 @@
       <c r="H146" s="6"/>
       <c r="I146" s="6"/>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A147" s="5"/>
       <c r="B147" s="5"/>
       <c r="C147" s="6"/>
@@ -2576,7 +2641,7 @@
       <c r="H147" s="6"/>
       <c r="I147" s="6"/>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A148" s="5"/>
       <c r="B148" s="5"/>
       <c r="C148" s="6"/>
@@ -2587,7 +2652,7 @@
       <c r="H148" s="6"/>
       <c r="I148" s="6"/>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A149" s="5"/>
       <c r="B149" s="5"/>
       <c r="C149" s="6"/>
@@ -2598,7 +2663,7 @@
       <c r="H149" s="6"/>
       <c r="I149" s="6"/>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A150" s="5"/>
       <c r="B150" s="5"/>
       <c r="C150" s="6"/>
@@ -2609,7 +2674,7 @@
       <c r="H150" s="6"/>
       <c r="I150" s="6"/>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A151" s="5"/>
       <c r="B151" s="5"/>
       <c r="C151" s="6"/>
@@ -2620,7 +2685,7 @@
       <c r="H151" s="6"/>
       <c r="I151" s="6"/>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A152" s="5"/>
       <c r="B152" s="5"/>
       <c r="C152" s="6"/>
@@ -2631,7 +2696,7 @@
       <c r="H152" s="6"/>
       <c r="I152" s="6"/>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A153" s="5"/>
       <c r="B153" s="5"/>
       <c r="C153" s="6"/>
@@ -2642,7 +2707,7 @@
       <c r="H153" s="6"/>
       <c r="I153" s="6"/>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A154" s="5"/>
       <c r="B154" s="5"/>
       <c r="C154" s="6"/>
@@ -2653,7 +2718,7 @@
       <c r="H154" s="6"/>
       <c r="I154" s="6"/>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A155" s="5"/>
       <c r="B155" s="5"/>
       <c r="C155" s="6"/>
@@ -2664,7 +2729,7 @@
       <c r="H155" s="6"/>
       <c r="I155" s="6"/>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A156" s="5"/>
       <c r="B156" s="5"/>
       <c r="C156" s="6"/>
@@ -2675,7 +2740,7 @@
       <c r="H156" s="6"/>
       <c r="I156" s="6"/>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A157" s="5"/>
       <c r="B157" s="5"/>
       <c r="C157" s="6"/>
@@ -2686,7 +2751,7 @@
       <c r="H157" s="6"/>
       <c r="I157" s="6"/>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A158" s="5"/>
       <c r="B158" s="5"/>
       <c r="C158" s="6"/>
@@ -2697,7 +2762,7 @@
       <c r="H158" s="6"/>
       <c r="I158" s="6"/>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A159" s="5"/>
       <c r="B159" s="5"/>
       <c r="C159" s="6"/>
@@ -2708,7 +2773,7 @@
       <c r="H159" s="6"/>
       <c r="I159" s="6"/>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A160" s="5"/>
       <c r="B160" s="5"/>
       <c r="C160" s="6"/>
@@ -2719,7 +2784,7 @@
       <c r="H160" s="6"/>
       <c r="I160" s="6"/>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A161" s="5"/>
       <c r="B161" s="5"/>
       <c r="C161" s="6"/>
@@ -2730,7 +2795,7 @@
       <c r="H161" s="6"/>
       <c r="I161" s="6"/>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A162" s="5"/>
       <c r="B162" s="5"/>
       <c r="C162" s="6"/>
@@ -2741,7 +2806,7 @@
       <c r="H162" s="6"/>
       <c r="I162" s="6"/>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A163" s="5"/>
       <c r="B163" s="5"/>
       <c r="C163" s="6"/>
@@ -2752,7 +2817,7 @@
       <c r="H163" s="6"/>
       <c r="I163" s="6"/>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A164" s="5"/>
       <c r="B164" s="5"/>
       <c r="C164" s="6"/>
@@ -2763,7 +2828,7 @@
       <c r="H164" s="6"/>
       <c r="I164" s="6"/>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A165" s="5"/>
       <c r="B165" s="5"/>
       <c r="C165" s="6"/>
@@ -2774,7 +2839,7 @@
       <c r="H165" s="6"/>
       <c r="I165" s="6"/>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A166" s="5"/>
       <c r="B166" s="5"/>
       <c r="C166" s="6"/>
@@ -2785,7 +2850,7 @@
       <c r="H166" s="6"/>
       <c r="I166" s="6"/>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A167" s="5"/>
       <c r="B167" s="5"/>
       <c r="C167" s="6"/>
@@ -2796,7 +2861,7 @@
       <c r="H167" s="6"/>
       <c r="I167" s="6"/>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A168" s="5"/>
       <c r="B168" s="5"/>
       <c r="C168" s="6"/>
@@ -2807,7 +2872,7 @@
       <c r="H168" s="6"/>
       <c r="I168" s="6"/>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A169" s="5"/>
       <c r="B169" s="5"/>
       <c r="C169" s="6"/>
@@ -2818,7 +2883,7 @@
       <c r="H169" s="6"/>
       <c r="I169" s="6"/>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A170" s="5"/>
       <c r="B170" s="5"/>
       <c r="C170" s="6"/>
@@ -2829,7 +2894,7 @@
       <c r="H170" s="6"/>
       <c r="I170" s="6"/>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A171" s="5"/>
       <c r="B171" s="5"/>
       <c r="C171" s="6"/>
@@ -2840,7 +2905,7 @@
       <c r="H171" s="6"/>
       <c r="I171" s="6"/>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A172" s="5"/>
       <c r="B172" s="5"/>
       <c r="C172" s="6"/>
@@ -2851,7 +2916,7 @@
       <c r="H172" s="6"/>
       <c r="I172" s="6"/>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A173" s="5"/>
       <c r="B173" s="5"/>
       <c r="C173" s="6"/>
@@ -2862,7 +2927,7 @@
       <c r="H173" s="6"/>
       <c r="I173" s="6"/>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A174" s="5"/>
       <c r="B174" s="5"/>
       <c r="C174" s="6"/>
@@ -2873,7 +2938,7 @@
       <c r="H174" s="6"/>
       <c r="I174" s="6"/>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A175" s="5"/>
       <c r="B175" s="5"/>
       <c r="C175" s="6"/>
@@ -2884,7 +2949,7 @@
       <c r="H175" s="6"/>
       <c r="I175" s="6"/>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A176" s="5"/>
       <c r="B176" s="5"/>
       <c r="C176" s="6"/>
@@ -2895,7 +2960,7 @@
       <c r="H176" s="6"/>
       <c r="I176" s="6"/>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A177" s="5"/>
       <c r="B177" s="5"/>
       <c r="C177" s="6"/>
@@ -2906,7 +2971,7 @@
       <c r="H177" s="6"/>
       <c r="I177" s="6"/>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A178" s="5"/>
       <c r="B178" s="5"/>
       <c r="C178" s="6"/>
@@ -2917,7 +2982,7 @@
       <c r="H178" s="6"/>
       <c r="I178" s="6"/>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A179" s="5"/>
       <c r="B179" s="5"/>
       <c r="C179" s="6"/>
@@ -2928,7 +2993,7 @@
       <c r="H179" s="6"/>
       <c r="I179" s="6"/>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A180" s="5"/>
       <c r="B180" s="5"/>
       <c r="C180" s="6"/>
@@ -2939,7 +3004,7 @@
       <c r="H180" s="6"/>
       <c r="I180" s="6"/>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A181" s="5"/>
       <c r="B181" s="5"/>
       <c r="C181" s="6"/>
@@ -2950,7 +3015,7 @@
       <c r="H181" s="6"/>
       <c r="I181" s="6"/>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A182" s="5"/>
       <c r="B182" s="5"/>
       <c r="C182" s="6"/>
@@ -2961,7 +3026,7 @@
       <c r="H182" s="6"/>
       <c r="I182" s="6"/>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A183" s="5"/>
       <c r="B183" s="5"/>
       <c r="C183" s="6"/>
@@ -2972,7 +3037,7 @@
       <c r="H183" s="6"/>
       <c r="I183" s="6"/>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A184" s="5"/>
       <c r="B184" s="5"/>
       <c r="C184" s="6"/>
@@ -2983,7 +3048,7 @@
       <c r="H184" s="6"/>
       <c r="I184" s="6"/>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A185" s="5"/>
       <c r="B185" s="5"/>
       <c r="C185" s="6"/>
@@ -2994,7 +3059,7 @@
       <c r="H185" s="6"/>
       <c r="I185" s="6"/>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A186" s="5"/>
       <c r="B186" s="5"/>
       <c r="C186" s="6"/>
@@ -3005,7 +3070,7 @@
       <c r="H186" s="6"/>
       <c r="I186" s="6"/>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A187" s="5"/>
       <c r="B187" s="5"/>
       <c r="C187" s="6"/>
@@ -3016,7 +3081,7 @@
       <c r="H187" s="6"/>
       <c r="I187" s="6"/>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A188" s="5"/>
       <c r="B188" s="5"/>
       <c r="C188" s="6"/>
@@ -3027,7 +3092,7 @@
       <c r="H188" s="6"/>
       <c r="I188" s="6"/>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A189" s="5"/>
       <c r="B189" s="5"/>
       <c r="C189" s="6"/>
@@ -3038,7 +3103,7 @@
       <c r="H189" s="6"/>
       <c r="I189" s="6"/>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A190" s="5"/>
       <c r="B190" s="5"/>
       <c r="C190" s="6"/>
@@ -3049,7 +3114,7 @@
       <c r="H190" s="6"/>
       <c r="I190" s="6"/>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A191" s="5"/>
       <c r="B191" s="5"/>
       <c r="C191" s="6"/>
@@ -3060,7 +3125,7 @@
       <c r="H191" s="6"/>
       <c r="I191" s="6"/>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A192" s="5"/>
       <c r="B192" s="5"/>
       <c r="C192" s="6"/>
@@ -3071,7 +3136,7 @@
       <c r="H192" s="6"/>
       <c r="I192" s="6"/>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A193" s="5"/>
       <c r="B193" s="5"/>
       <c r="C193" s="6"/>
@@ -3082,7 +3147,7 @@
       <c r="H193" s="6"/>
       <c r="I193" s="6"/>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A194" s="5"/>
       <c r="B194" s="5"/>
       <c r="C194" s="6"/>
@@ -3093,7 +3158,7 @@
       <c r="H194" s="6"/>
       <c r="I194" s="6"/>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A195" s="5"/>
       <c r="B195" s="5"/>
       <c r="C195" s="6"/>
@@ -3104,7 +3169,7 @@
       <c r="H195" s="6"/>
       <c r="I195" s="6"/>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A196" s="5"/>
       <c r="B196" s="5"/>
       <c r="C196" s="6"/>
@@ -3115,7 +3180,7 @@
       <c r="H196" s="6"/>
       <c r="I196" s="6"/>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A197" s="5"/>
       <c r="B197" s="5"/>
       <c r="C197" s="6"/>
@@ -3126,7 +3191,7 @@
       <c r="H197" s="6"/>
       <c r="I197" s="6"/>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A198" s="5"/>
       <c r="B198" s="5"/>
       <c r="C198" s="6"/>
@@ -3137,7 +3202,7 @@
       <c r="H198" s="6"/>
       <c r="I198" s="6"/>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A199" s="5"/>
       <c r="B199" s="5"/>
       <c r="C199" s="6"/>
@@ -3148,7 +3213,7 @@
       <c r="H199" s="6"/>
       <c r="I199" s="6"/>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A200" s="5"/>
       <c r="B200" s="5"/>
       <c r="C200" s="6"/>
@@ -3159,7 +3224,7 @@
       <c r="H200" s="6"/>
       <c r="I200" s="6"/>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A201" s="5"/>
       <c r="B201" s="5"/>
       <c r="C201" s="6"/>
@@ -3170,7 +3235,7 @@
       <c r="H201" s="6"/>
       <c r="I201" s="6"/>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A202" s="5"/>
       <c r="B202" s="5"/>
       <c r="C202" s="6"/>
@@ -3181,7 +3246,7 @@
       <c r="H202" s="6"/>
       <c r="I202" s="6"/>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A203" s="5"/>
       <c r="B203" s="5"/>
       <c r="C203" s="6"/>
@@ -3192,7 +3257,7 @@
       <c r="H203" s="6"/>
       <c r="I203" s="6"/>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A204" s="5"/>
       <c r="B204" s="5"/>
       <c r="C204" s="6"/>
@@ -3203,7 +3268,7 @@
       <c r="H204" s="6"/>
       <c r="I204" s="6"/>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A205" s="5"/>
       <c r="B205" s="5"/>
       <c r="C205" s="6"/>
@@ -3214,7 +3279,7 @@
       <c r="H205" s="6"/>
       <c r="I205" s="6"/>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A206" s="5"/>
       <c r="B206" s="5"/>
       <c r="C206" s="6"/>
@@ -3225,7 +3290,7 @@
       <c r="H206" s="6"/>
       <c r="I206" s="6"/>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A207" s="5"/>
       <c r="B207" s="5"/>
       <c r="C207" s="6"/>
@@ -3236,7 +3301,7 @@
       <c r="H207" s="6"/>
       <c r="I207" s="6"/>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A208" s="5"/>
       <c r="B208" s="5"/>
       <c r="C208" s="6"/>
@@ -3247,7 +3312,7 @@
       <c r="H208" s="6"/>
       <c r="I208" s="6"/>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A209" s="5"/>
       <c r="B209" s="5"/>
       <c r="C209" s="6"/>
@@ -3258,7 +3323,7 @@
       <c r="H209" s="6"/>
       <c r="I209" s="6"/>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A210" s="5"/>
       <c r="B210" s="5"/>
       <c r="C210" s="6"/>
@@ -3269,7 +3334,7 @@
       <c r="H210" s="6"/>
       <c r="I210" s="6"/>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A211" s="5"/>
       <c r="B211" s="5"/>
       <c r="C211" s="6"/>
@@ -3280,7 +3345,7 @@
       <c r="H211" s="6"/>
       <c r="I211" s="6"/>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A212" s="5"/>
       <c r="B212" s="5"/>
       <c r="C212" s="6"/>
@@ -3291,7 +3356,7 @@
       <c r="H212" s="6"/>
       <c r="I212" s="6"/>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A213" s="5"/>
       <c r="B213" s="5"/>
       <c r="C213" s="6"/>
@@ -3302,7 +3367,7 @@
       <c r="H213" s="6"/>
       <c r="I213" s="6"/>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A214" s="5"/>
       <c r="B214" s="5"/>
       <c r="C214" s="6"/>
@@ -3313,7 +3378,7 @@
       <c r="H214" s="6"/>
       <c r="I214" s="6"/>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A215" s="5"/>
       <c r="B215" s="5"/>
       <c r="C215" s="6"/>
@@ -3324,7 +3389,7 @@
       <c r="H215" s="6"/>
       <c r="I215" s="6"/>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A216" s="5"/>
       <c r="B216" s="5"/>
       <c r="C216" s="6"/>
@@ -3335,7 +3400,7 @@
       <c r="H216" s="6"/>
       <c r="I216" s="6"/>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A217" s="5"/>
       <c r="B217" s="5"/>
       <c r="C217" s="6"/>
@@ -3346,7 +3411,7 @@
       <c r="H217" s="6"/>
       <c r="I217" s="6"/>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A218" s="5"/>
       <c r="B218" s="5"/>
       <c r="C218" s="6"/>
@@ -3357,7 +3422,7 @@
       <c r="H218" s="6"/>
       <c r="I218" s="6"/>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A219" s="5"/>
       <c r="B219" s="5"/>
       <c r="C219" s="6"/>
@@ -3368,7 +3433,7 @@
       <c r="H219" s="6"/>
       <c r="I219" s="6"/>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A220" s="5"/>
       <c r="B220" s="5"/>
       <c r="C220" s="6"/>
@@ -3379,7 +3444,7 @@
       <c r="H220" s="6"/>
       <c r="I220" s="6"/>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A221" s="5"/>
       <c r="B221" s="5"/>
       <c r="C221" s="6"/>
@@ -3390,7 +3455,7 @@
       <c r="H221" s="6"/>
       <c r="I221" s="6"/>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A222" s="5"/>
       <c r="B222" s="5"/>
       <c r="C222" s="6"/>
@@ -3401,7 +3466,7 @@
       <c r="H222" s="6"/>
       <c r="I222" s="6"/>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A223" s="5"/>
       <c r="B223" s="5"/>
       <c r="C223" s="6"/>
@@ -3412,7 +3477,7 @@
       <c r="H223" s="6"/>
       <c r="I223" s="6"/>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A224" s="5"/>
       <c r="B224" s="5"/>
       <c r="C224" s="6"/>
@@ -3423,7 +3488,7 @@
       <c r="H224" s="6"/>
       <c r="I224" s="6"/>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A225" s="5"/>
       <c r="B225" s="5"/>
       <c r="C225" s="6"/>
@@ -3434,7 +3499,7 @@
       <c r="H225" s="6"/>
       <c r="I225" s="6"/>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A226" s="5"/>
       <c r="B226" s="5"/>
       <c r="C226" s="6"/>
@@ -3445,7 +3510,7 @@
       <c r="H226" s="6"/>
       <c r="I226" s="6"/>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A227" s="5"/>
       <c r="B227" s="5"/>
       <c r="C227" s="6"/>
@@ -3456,7 +3521,7 @@
       <c r="H227" s="6"/>
       <c r="I227" s="6"/>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A228" s="5"/>
       <c r="B228" s="5"/>
       <c r="C228" s="6"/>
@@ -3467,7 +3532,7 @@
       <c r="H228" s="6"/>
       <c r="I228" s="6"/>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A229" s="5"/>
       <c r="B229" s="5"/>
       <c r="C229" s="6"/>
@@ -3478,7 +3543,7 @@
       <c r="H229" s="6"/>
       <c r="I229" s="6"/>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A230" s="5"/>
       <c r="B230" s="5"/>
       <c r="C230" s="6"/>
@@ -3489,7 +3554,7 @@
       <c r="H230" s="6"/>
       <c r="I230" s="6"/>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A231" s="5"/>
       <c r="B231" s="5"/>
       <c r="C231" s="6"/>
@@ -3500,7 +3565,7 @@
       <c r="H231" s="6"/>
       <c r="I231" s="6"/>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A232" s="5"/>
       <c r="B232" s="5"/>
       <c r="C232" s="6"/>
@@ -3511,7 +3576,7 @@
       <c r="H232" s="6"/>
       <c r="I232" s="6"/>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A233" s="5"/>
       <c r="B233" s="5"/>
       <c r="C233" s="6"/>
@@ -3522,7 +3587,7 @@
       <c r="H233" s="6"/>
       <c r="I233" s="6"/>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A234" s="5"/>
       <c r="B234" s="5"/>
       <c r="C234" s="6"/>
@@ -3533,7 +3598,7 @@
       <c r="H234" s="6"/>
       <c r="I234" s="6"/>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A235" s="5"/>
       <c r="B235" s="5"/>
       <c r="C235" s="6"/>
@@ -3544,7 +3609,7 @@
       <c r="H235" s="6"/>
       <c r="I235" s="6"/>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A236" s="5"/>
       <c r="B236" s="5"/>
       <c r="C236" s="6"/>
@@ -3555,7 +3620,7 @@
       <c r="H236" s="6"/>
       <c r="I236" s="6"/>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A237" s="5"/>
       <c r="B237" s="5"/>
       <c r="C237" s="6"/>
@@ -3566,7 +3631,7 @@
       <c r="H237" s="6"/>
       <c r="I237" s="6"/>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A238" s="5"/>
       <c r="B238" s="5"/>
       <c r="C238" s="6"/>
@@ -3577,7 +3642,7 @@
       <c r="H238" s="6"/>
       <c r="I238" s="6"/>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A239" s="5"/>
       <c r="B239" s="5"/>
       <c r="C239" s="6"/>
@@ -3588,7 +3653,7 @@
       <c r="H239" s="6"/>
       <c r="I239" s="6"/>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A240" s="5"/>
       <c r="B240" s="5"/>
       <c r="C240" s="6"/>
@@ -3599,7 +3664,7 @@
       <c r="H240" s="6"/>
       <c r="I240" s="6"/>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A241" s="5"/>
       <c r="B241" s="5"/>
       <c r="C241" s="6"/>
@@ -3610,7 +3675,7 @@
       <c r="H241" s="6"/>
       <c r="I241" s="6"/>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A242" s="5"/>
       <c r="B242" s="5"/>
       <c r="C242" s="6"/>
@@ -3621,7 +3686,7 @@
       <c r="H242" s="6"/>
       <c r="I242" s="6"/>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A243" s="5"/>
       <c r="B243" s="5"/>
       <c r="C243" s="6"/>
@@ -3632,7 +3697,7 @@
       <c r="H243" s="6"/>
       <c r="I243" s="6"/>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A244" s="5"/>
       <c r="B244" s="5"/>
       <c r="C244" s="6"/>
@@ -3643,7 +3708,7 @@
       <c r="H244" s="6"/>
       <c r="I244" s="6"/>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A245" s="5"/>
       <c r="B245" s="5"/>
       <c r="C245" s="6"/>
@@ -3654,7 +3719,7 @@
       <c r="H245" s="6"/>
       <c r="I245" s="6"/>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A246" s="5"/>
       <c r="B246" s="5"/>
       <c r="C246" s="6"/>
@@ -3665,7 +3730,7 @@
       <c r="H246" s="6"/>
       <c r="I246" s="6"/>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A247" s="5"/>
       <c r="B247" s="5"/>
       <c r="C247" s="6"/>
@@ -3676,7 +3741,7 @@
       <c r="H247" s="6"/>
       <c r="I247" s="6"/>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A248" s="5"/>
       <c r="B248" s="5"/>
       <c r="C248" s="6"/>
@@ -3687,7 +3752,7 @@
       <c r="H248" s="6"/>
       <c r="I248" s="6"/>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A249" s="5"/>
       <c r="B249" s="5"/>
       <c r="C249" s="6"/>
@@ -3698,7 +3763,7 @@
       <c r="H249" s="6"/>
       <c r="I249" s="6"/>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A250" s="5"/>
       <c r="B250" s="5"/>
       <c r="C250" s="6"/>
@@ -3709,7 +3774,7 @@
       <c r="H250" s="6"/>
       <c r="I250" s="6"/>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A251" s="5"/>
       <c r="B251" s="5"/>
       <c r="C251" s="6"/>
@@ -3720,7 +3785,7 @@
       <c r="H251" s="6"/>
       <c r="I251" s="6"/>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A252" s="5"/>
       <c r="B252" s="5"/>
       <c r="C252" s="6"/>
@@ -3731,7 +3796,7 @@
       <c r="H252" s="6"/>
       <c r="I252" s="6"/>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A253" s="5"/>
       <c r="B253" s="5"/>
       <c r="C253" s="6"/>
@@ -3742,7 +3807,7 @@
       <c r="H253" s="6"/>
       <c r="I253" s="6"/>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A254" s="5"/>
       <c r="B254" s="5"/>
       <c r="C254" s="6"/>
@@ -3753,7 +3818,7 @@
       <c r="H254" s="6"/>
       <c r="I254" s="6"/>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A255" s="5"/>
       <c r="B255" s="5"/>
       <c r="C255" s="6"/>
@@ -3764,7 +3829,7 @@
       <c r="H255" s="6"/>
       <c r="I255" s="6"/>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A256" s="5"/>
       <c r="B256" s="5"/>
       <c r="C256" s="6"/>
@@ -3775,7 +3840,7 @@
       <c r="H256" s="6"/>
       <c r="I256" s="6"/>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A257" s="5"/>
       <c r="B257" s="5"/>
       <c r="C257" s="6"/>
@@ -3786,7 +3851,7 @@
       <c r="H257" s="6"/>
       <c r="I257" s="6"/>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A258" s="5"/>
       <c r="B258" s="5"/>
       <c r="C258" s="6"/>
@@ -3797,7 +3862,7 @@
       <c r="H258" s="6"/>
       <c r="I258" s="6"/>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A259" s="5"/>
       <c r="B259" s="5"/>
       <c r="C259" s="6"/>
@@ -3808,7 +3873,7 @@
       <c r="H259" s="6"/>
       <c r="I259" s="6"/>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A260" s="5"/>
       <c r="B260" s="5"/>
       <c r="C260" s="6"/>
@@ -3819,7 +3884,7 @@
       <c r="H260" s="6"/>
       <c r="I260" s="6"/>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A261" s="5"/>
       <c r="B261" s="5"/>
       <c r="C261" s="6"/>
@@ -3830,7 +3895,7 @@
       <c r="H261" s="6"/>
       <c r="I261" s="6"/>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A262" s="5"/>
       <c r="B262" s="5"/>
       <c r="C262" s="6"/>
@@ -3841,7 +3906,7 @@
       <c r="H262" s="6"/>
       <c r="I262" s="6"/>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A263" s="5"/>
       <c r="B263" s="5"/>
       <c r="C263" s="6"/>
@@ -3852,7 +3917,7 @@
       <c r="H263" s="6"/>
       <c r="I263" s="6"/>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A264" s="5"/>
       <c r="B264" s="5"/>
       <c r="C264" s="6"/>
@@ -3863,7 +3928,7 @@
       <c r="H264" s="6"/>
       <c r="I264" s="6"/>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A265" s="5"/>
       <c r="B265" s="5"/>
       <c r="C265" s="6"/>
@@ -3874,7 +3939,7 @@
       <c r="H265" s="6"/>
       <c r="I265" s="6"/>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A266" s="5"/>
       <c r="B266" s="5"/>
       <c r="C266" s="6"/>
@@ -3885,7 +3950,7 @@
       <c r="H266" s="6"/>
       <c r="I266" s="6"/>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A267" s="5"/>
       <c r="B267" s="5"/>
       <c r="C267" s="6"/>
@@ -3896,7 +3961,7 @@
       <c r="H267" s="6"/>
       <c r="I267" s="6"/>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A268" s="5"/>
       <c r="B268" s="5"/>
       <c r="C268" s="6"/>
@@ -3907,7 +3972,7 @@
       <c r="H268" s="6"/>
       <c r="I268" s="6"/>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A269" s="5"/>
       <c r="B269" s="5"/>
       <c r="C269" s="6"/>
@@ -3918,7 +3983,7 @@
       <c r="H269" s="6"/>
       <c r="I269" s="6"/>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A270" s="5"/>
       <c r="B270" s="5"/>
       <c r="C270" s="6"/>
@@ -3929,7 +3994,7 @@
       <c r="H270" s="6"/>
       <c r="I270" s="6"/>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A271" s="5"/>
       <c r="B271" s="5"/>
       <c r="C271" s="6"/>
@@ -3940,7 +4005,7 @@
       <c r="H271" s="6"/>
       <c r="I271" s="6"/>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A272" s="5"/>
       <c r="B272" s="5"/>
       <c r="C272" s="6"/>
@@ -3951,7 +4016,7 @@
       <c r="H272" s="6"/>
       <c r="I272" s="6"/>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A273" s="5"/>
       <c r="B273" s="5"/>
       <c r="C273" s="6"/>
@@ -3962,7 +4027,7 @@
       <c r="H273" s="6"/>
       <c r="I273" s="6"/>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A274" s="5"/>
       <c r="B274" s="5"/>
       <c r="C274" s="6"/>
@@ -3973,7 +4038,7 @@
       <c r="H274" s="6"/>
       <c r="I274" s="6"/>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A275" s="5"/>
       <c r="B275" s="5"/>
       <c r="C275" s="6"/>
@@ -3984,7 +4049,7 @@
       <c r="H275" s="6"/>
       <c r="I275" s="6"/>
     </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A276" s="5"/>
       <c r="B276" s="5"/>
       <c r="C276" s="6"/>
@@ -3995,7 +4060,7 @@
       <c r="H276" s="6"/>
       <c r="I276" s="6"/>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A277" s="5"/>
       <c r="B277" s="5"/>
       <c r="C277" s="6"/>
@@ -4006,7 +4071,7 @@
       <c r="H277" s="6"/>
       <c r="I277" s="6"/>
     </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A278" s="5"/>
       <c r="B278" s="5"/>
       <c r="C278" s="6"/>
@@ -4017,7 +4082,7 @@
       <c r="H278" s="6"/>
       <c r="I278" s="6"/>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A279" s="5"/>
       <c r="B279" s="5"/>
       <c r="C279" s="6"/>
@@ -4028,7 +4093,7 @@
       <c r="H279" s="6"/>
       <c r="I279" s="6"/>
     </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A280" s="5"/>
       <c r="B280" s="5"/>
       <c r="C280" s="6"/>
@@ -4039,7 +4104,7 @@
       <c r="H280" s="6"/>
       <c r="I280" s="6"/>
     </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A281" s="5"/>
       <c r="B281" s="5"/>
       <c r="C281" s="6"/>
@@ -4050,7 +4115,7 @@
       <c r="H281" s="6"/>
       <c r="I281" s="6"/>
     </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A282" s="5"/>
       <c r="B282" s="5"/>
       <c r="C282" s="6"/>
@@ -4061,7 +4126,7 @@
       <c r="H282" s="6"/>
       <c r="I282" s="6"/>
     </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A283" s="5"/>
       <c r="B283" s="5"/>
       <c r="C283" s="6"/>
@@ -4072,7 +4137,7 @@
       <c r="H283" s="6"/>
       <c r="I283" s="6"/>
     </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A284" s="5"/>
       <c r="B284" s="5"/>
       <c r="C284" s="6"/>
@@ -4083,7 +4148,7 @@
       <c r="H284" s="6"/>
       <c r="I284" s="6"/>
     </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A285" s="5"/>
       <c r="B285" s="5"/>
       <c r="C285" s="6"/>
@@ -4094,7 +4159,7 @@
       <c r="H285" s="6"/>
       <c r="I285" s="6"/>
     </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A286" s="5"/>
       <c r="B286" s="5"/>
       <c r="C286" s="6"/>
@@ -4105,7 +4170,7 @@
       <c r="H286" s="6"/>
       <c r="I286" s="6"/>
     </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A287" s="5"/>
       <c r="B287" s="5"/>
       <c r="C287" s="6"/>
@@ -4116,7 +4181,7 @@
       <c r="H287" s="6"/>
       <c r="I287" s="6"/>
     </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A288" s="5"/>
       <c r="B288" s="5"/>
       <c r="C288" s="6"/>
@@ -4127,7 +4192,7 @@
       <c r="H288" s="6"/>
       <c r="I288" s="6"/>
     </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A289" s="5"/>
       <c r="B289" s="5"/>
       <c r="C289" s="6"/>
@@ -4138,7 +4203,7 @@
       <c r="H289" s="6"/>
       <c r="I289" s="6"/>
     </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A290" s="5"/>
       <c r="B290" s="5"/>
       <c r="C290" s="6"/>
@@ -4149,7 +4214,7 @@
       <c r="H290" s="6"/>
       <c r="I290" s="6"/>
     </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A291" s="5"/>
       <c r="B291" s="5"/>
       <c r="C291" s="6"/>
@@ -4160,7 +4225,7 @@
       <c r="H291" s="6"/>
       <c r="I291" s="6"/>
     </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A292" s="5"/>
       <c r="B292" s="5"/>
       <c r="C292" s="6"/>
@@ -4171,7 +4236,7 @@
       <c r="H292" s="6"/>
       <c r="I292" s="6"/>
     </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A293" s="5"/>
       <c r="B293" s="5"/>
       <c r="C293" s="6"/>
@@ -4182,7 +4247,7 @@
       <c r="H293" s="6"/>
       <c r="I293" s="6"/>
     </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A294" s="5"/>
       <c r="B294" s="5"/>
       <c r="C294" s="6"/>
@@ -4193,7 +4258,7 @@
       <c r="H294" s="6"/>
       <c r="I294" s="6"/>
     </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A295" s="5"/>
       <c r="B295" s="5"/>
       <c r="C295" s="6"/>
@@ -4204,7 +4269,7 @@
       <c r="H295" s="6"/>
       <c r="I295" s="6"/>
     </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A296" s="5"/>
       <c r="B296" s="5"/>
       <c r="C296" s="6"/>
@@ -4215,7 +4280,7 @@
       <c r="H296" s="6"/>
       <c r="I296" s="6"/>
     </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A297" s="5"/>
       <c r="B297" s="5"/>
       <c r="C297" s="6"/>
@@ -4226,7 +4291,7 @@
       <c r="H297" s="6"/>
       <c r="I297" s="6"/>
     </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A298" s="5"/>
       <c r="B298" s="5"/>
       <c r="C298" s="6"/>
@@ -4237,7 +4302,7 @@
       <c r="H298" s="6"/>
       <c r="I298" s="6"/>
     </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A299" s="5"/>
       <c r="B299" s="5"/>
       <c r="C299" s="6"/>
@@ -4248,7 +4313,7 @@
       <c r="H299" s="6"/>
       <c r="I299" s="6"/>
     </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A300" s="5"/>
       <c r="B300" s="5"/>
       <c r="C300" s="6"/>
@@ -4260,7 +4325,11 @@
       <c r="I300" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I300" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="A1:I300" xr:uid="{00000000-0009-0000-0000-000001000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I300">
+      <sortCondition ref="B1:B300"/>
+    </sortState>
+  </autoFilter>
   <conditionalFormatting sqref="E2:E300">
     <cfRule type="expression" dxfId="6" priority="1">
       <formula>$E2="Competición FPCV"</formula>

--- a/calendario-fpcv-eventos.xlsx
+++ b/calendario-fpcv-eventos.xlsx
@@ -8,23 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bea Pallero\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D9C4B03-FB26-4B8D-B8AD-6ADB8679388E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBF296C7-BF25-459F-891A-95BF6B966FB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cómo se usa" sheetId="1" r:id="rId1"/>
     <sheet name="Eventos" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Eventos!$A$1:$I$300</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Eventos!$A$1:$I$302</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="67">
   <si>
     <t>Inicio</t>
   </si>
@@ -210,6 +210,21 @@
   </si>
   <si>
     <t>Trofeo Iniciación L'Alcúdia de Crespins</t>
+  </si>
+  <si>
+    <t>World Skate Games</t>
+  </si>
+  <si>
+    <t>Asunción</t>
+  </si>
+  <si>
+    <t>Competición Internacional</t>
+  </si>
+  <si>
+    <t>Copa Europa Libre-Danza-Parejas Artístico</t>
+  </si>
+  <si>
+    <t>Stade (Alemania)</t>
   </si>
 </sst>
 </file>
@@ -781,7 +796,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I300"/>
+  <dimension ref="A1:I302"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="13" customWidth="1"/>
@@ -846,92 +861,90 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
-        <v>46312</v>
+        <v>46301</v>
       </c>
       <c r="B3" s="5">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>15</v>
+        <v>62</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>16</v>
+        <v>63</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="F3" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" s="6"/>
-      <c r="H3" s="6" t="s">
-        <v>49</v>
-      </c>
+      <c r="H3" s="6"/>
       <c r="I3" s="6"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B4" s="5">
-        <v>46313</v>
+        <v>46312</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F4" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
+      <c r="H4" s="6" t="s">
+        <v>49</v>
+      </c>
       <c r="I4" s="6"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
-        <v>46312</v>
+        <v>46311</v>
       </c>
       <c r="B5" s="5">
         <v>46313</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>57</v>
+        <v>12</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F5" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" s="6"/>
-      <c r="H5" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>50</v>
-      </c>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
-        <v>46319</v>
+        <v>46312</v>
       </c>
       <c r="B6" s="5">
         <v>46319</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="6"/>
+        <v>65</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>66</v>
+      </c>
       <c r="E6" s="6" t="s">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="F6" s="7">
         <v>0</v>
@@ -942,70 +955,70 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
-        <v>46319</v>
+        <v>46312</v>
       </c>
       <c r="B7" s="5">
-        <v>46319</v>
+        <v>46313</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>20</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F7" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7" s="6"/>
       <c r="H7" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="I7" s="6"/>
+      <c r="I7" s="6" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
-        <v>46333</v>
+        <v>46319</v>
       </c>
       <c r="B8" s="5">
-        <v>46333</v>
+        <v>46319</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>51</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="D8" s="6"/>
       <c r="E8" s="6" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F8" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" s="6"/>
-      <c r="H8" s="6" t="s">
-        <v>49</v>
-      </c>
+      <c r="H8" s="6"/>
       <c r="I8" s="6"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
-        <v>46333</v>
+        <v>46319</v>
       </c>
       <c r="B9" s="5">
-        <v>46333</v>
+        <v>46319</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="D9" s="6"/>
+        <v>19</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="E9" s="6" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F9" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G9" s="6"/>
       <c r="H9" s="6" t="s">
@@ -1018,84 +1031,82 @@
         <v>46333</v>
       </c>
       <c r="B10" s="5">
-        <v>46334</v>
+        <v>46333</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" s="6"/>
+        <v>58</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>51</v>
+      </c>
       <c r="E10" s="6" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F10" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
+      <c r="H10" s="6" t="s">
+        <v>49</v>
+      </c>
       <c r="I10" s="6"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
-        <v>46339</v>
+        <v>46333</v>
       </c>
       <c r="B11" s="5">
-        <v>46339</v>
+        <v>46333</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>53</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="D11" s="6"/>
       <c r="E11" s="6" t="s">
         <v>11</v>
       </c>
       <c r="F11" s="7">
         <v>1</v>
       </c>
-      <c r="G11" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="H11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6" t="s">
+        <v>49</v>
+      </c>
       <c r="I11" s="6"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
-        <v>46340</v>
+        <v>46333</v>
       </c>
       <c r="B12" s="5">
-        <v>46340</v>
+        <v>46334</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>13</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="D12" s="6"/>
       <c r="E12" s="6" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F12" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G12" s="6"/>
-      <c r="H12" s="6" t="s">
-        <v>49</v>
-      </c>
+      <c r="H12" s="6"/>
       <c r="I12" s="6"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
-        <v>46347</v>
+        <v>46339</v>
       </c>
       <c r="B13" s="5">
-        <v>46347</v>
+        <v>46339</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>11</v>
@@ -1103,30 +1114,30 @@
       <c r="F13" s="7">
         <v>1</v>
       </c>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6" t="s">
-        <v>49</v>
-      </c>
+      <c r="G13" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="H13" s="6"/>
       <c r="I13" s="6"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="5">
-        <v>46347</v>
+        <v>46340</v>
       </c>
       <c r="B14" s="5">
-        <v>46347</v>
+        <v>46340</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F14" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G14" s="6"/>
       <c r="H14" s="6" t="s">
@@ -1139,56 +1150,60 @@
         <v>46347</v>
       </c>
       <c r="B15" s="5">
-        <v>46348</v>
+        <v>46347</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D15" s="6"/>
+        <v>60</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>55</v>
+      </c>
       <c r="E15" s="6" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F15" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
+      <c r="H15" s="6" t="s">
+        <v>49</v>
+      </c>
       <c r="I15" s="6"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="5">
-        <v>46354</v>
+        <v>46347</v>
       </c>
       <c r="B16" s="5">
-        <v>46354</v>
+        <v>46347</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="F16" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I16" s="6"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
-        <v>46354</v>
+        <v>46347</v>
       </c>
       <c r="B17" s="5">
-        <v>46355</v>
+        <v>46348</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D17" s="6"/>
       <c r="E17" s="6" t="s">
@@ -1203,68 +1218,70 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="5">
-        <v>46368</v>
+        <v>46354</v>
       </c>
       <c r="B18" s="5">
-        <v>46368</v>
+        <v>46354</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D18" s="6"/>
+        <v>26</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>27</v>
+      </c>
       <c r="E18" s="6" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F18" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
+      <c r="H18" s="6" t="s">
+        <v>50</v>
+      </c>
       <c r="I18" s="6"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="5"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="6"/>
+      <c r="A19" s="5">
+        <v>46354</v>
+      </c>
+      <c r="B19" s="5">
+        <v>46355</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>25</v>
+      </c>
       <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="7"/>
+      <c r="E19" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F19" s="7">
+        <v>0</v>
+      </c>
       <c r="G19" s="6"/>
       <c r="H19" s="6"/>
       <c r="I19" s="6"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" s="5"/>
-      <c r="B20" s="5"/>
-      <c r="C20" s="6"/>
+      <c r="A20" s="5">
+        <v>46368</v>
+      </c>
+      <c r="B20" s="5">
+        <v>46368</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>29</v>
+      </c>
       <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="7"/>
+      <c r="E20" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F20" s="7">
+        <v>1</v>
+      </c>
       <c r="G20" s="6"/>
       <c r="H20" s="6"/>
       <c r="I20" s="6"/>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="5"/>
-      <c r="B21" s="5"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="5"/>
-      <c r="B22" s="5"/>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="5"/>
@@ -4324,13 +4341,35 @@
       <c r="H300" s="6"/>
       <c r="I300" s="6"/>
     </row>
+    <row r="301" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A301" s="5"/>
+      <c r="B301" s="5"/>
+      <c r="C301" s="6"/>
+      <c r="D301" s="6"/>
+      <c r="E301" s="6"/>
+      <c r="F301" s="7"/>
+      <c r="G301" s="6"/>
+      <c r="H301" s="6"/>
+      <c r="I301" s="6"/>
+    </row>
+    <row r="302" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A302" s="5"/>
+      <c r="B302" s="5"/>
+      <c r="C302" s="6"/>
+      <c r="D302" s="6"/>
+      <c r="E302" s="6"/>
+      <c r="F302" s="7"/>
+      <c r="G302" s="6"/>
+      <c r="H302" s="6"/>
+      <c r="I302" s="6"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I300" xr:uid="{00000000-0009-0000-0000-000001000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I300">
-      <sortCondition ref="B1:B300"/>
+  <autoFilter ref="A1:I302" xr:uid="{00000000-0009-0000-0000-000001000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I302">
+      <sortCondition ref="B1:B302"/>
     </sortState>
   </autoFilter>
-  <conditionalFormatting sqref="E2:E300">
+  <conditionalFormatting sqref="E23:E302 E2:E20">
     <cfRule type="expression" dxfId="6" priority="1">
       <formula>$E2="Competición FPCV"</formula>
     </cfRule>
@@ -4354,16 +4393,16 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" errorTitle="Valor no válido" error="Elige una categoría de la lista" sqref="E2:E300" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" errorTitle="Valor no válido" error="Elige una categoría de la lista" sqref="E2:E20 E23:E302" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Competición FPCV,Campeonato de España,Competición Internacional,Trofeo Club,Curso,Reunión,Prueba de Acceso"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" errorTitle="Valor no válido" error="Huecos: pon 0, 1 o 2" sqref="F2:F300" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" errorTitle="Valor no válido" error="Huecos: pon 0, 1 o 2" sqref="F2:F20 F23:F302" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"0,1,2"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" errorTitle="Valor no válido" error="Elige Mañana, Tarde o Todo el día" sqref="G2:I300" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" errorTitle="Valor no válido" error="Elige Mañana, Tarde o Todo el día" sqref="G2:I20 G23:I302" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"Mañana,Tarde,Todo el día"</formula1>
     </dataValidation>
-    <dataValidation type="date" operator="greaterThan" allowBlank="1" errorTitle="Fecha" error="Escribe una fecha, por ejemplo 17/10/2026" sqref="A2:B300" xr:uid="{00000000-0002-0000-0100-000003000000}">
+    <dataValidation type="date" operator="greaterThan" allowBlank="1" errorTitle="Fecha" error="Escribe una fecha, por ejemplo 17/10/2026" sqref="A2:B20 A23:B302" xr:uid="{00000000-0002-0000-0100-000003000000}">
       <formula1>36526</formula1>
     </dataValidation>
   </dataValidations>

--- a/calendario-fpcv-eventos.xlsx
+++ b/calendario-fpcv-eventos.xlsx
@@ -5,26 +5,26 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bea Pallero\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5bbe44e6a3b5fd34/Federación/EVENTOS AÑO 2027/Calendario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBF296C7-BF25-459F-891A-95BF6B966FB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="13_ncr:1_{BBF296C7-BF25-459F-891A-95BF6B966FB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D3342B2D-270A-4FE0-BC5B-3E767710CEF9}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cómo se usa" sheetId="1" r:id="rId1"/>
     <sheet name="Eventos" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Eventos!$A$1:$I$302</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Eventos!$A$1:$I$303</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="69">
   <si>
     <t>Inicio</t>
   </si>
@@ -225,6 +225,12 @@
   </si>
   <si>
     <t>Stade (Alemania)</t>
+  </si>
+  <si>
+    <t>Trofeo Iniciación Azalea</t>
+  </si>
+  <si>
+    <t>Castelló de la Plana</t>
   </si>
 </sst>
 </file>
@@ -796,7 +802,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I302"/>
+  <dimension ref="A1:I303"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="13" customWidth="1"/>
@@ -1264,24 +1270,74 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="5">
-        <v>46368</v>
+        <v>46355</v>
       </c>
       <c r="B20" s="5">
-        <v>46368</v>
+        <v>46355</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D20" s="6"/>
+        <v>67</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>68</v>
+      </c>
       <c r="E20" s="6" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F20" s="7">
         <v>1</v>
       </c>
       <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
+      <c r="H20" s="6" t="s">
+        <v>49</v>
+      </c>
       <c r="I20" s="6"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A21" s="5">
+        <v>46368</v>
+      </c>
+      <c r="B21" s="5">
+        <v>46368</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F21" s="7">
+        <v>1</v>
+      </c>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
+      <c r="I21" s="6"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A22" s="5">
+        <v>46397</v>
+      </c>
+      <c r="B22" s="5">
+        <v>46397</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" s="7">
+        <v>1</v>
+      </c>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="I22" s="6"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="5"/>
@@ -2065,2223 +2121,2223 @@
       <c r="I93" s="6"/>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A94" s="5"/>
-      <c r="B94" s="5"/>
+      <c r="A94" s="6"/>
+      <c r="B94" s="6"/>
       <c r="C94" s="6"/>
       <c r="D94" s="6"/>
       <c r="E94" s="6"/>
-      <c r="F94" s="7"/>
+      <c r="F94" s="6"/>
       <c r="G94" s="6"/>
       <c r="H94" s="6"/>
       <c r="I94" s="6"/>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A95" s="5"/>
-      <c r="B95" s="5"/>
+      <c r="A95" s="6"/>
+      <c r="B95" s="6"/>
       <c r="C95" s="6"/>
       <c r="D95" s="6"/>
       <c r="E95" s="6"/>
-      <c r="F95" s="7"/>
+      <c r="F95" s="6"/>
       <c r="G95" s="6"/>
       <c r="H95" s="6"/>
       <c r="I95" s="6"/>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A96" s="5"/>
-      <c r="B96" s="5"/>
+      <c r="A96" s="6"/>
+      <c r="B96" s="6"/>
       <c r="C96" s="6"/>
       <c r="D96" s="6"/>
       <c r="E96" s="6"/>
-      <c r="F96" s="7"/>
+      <c r="F96" s="6"/>
       <c r="G96" s="6"/>
       <c r="H96" s="6"/>
       <c r="I96" s="6"/>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A97" s="5"/>
-      <c r="B97" s="5"/>
+      <c r="A97" s="6"/>
+      <c r="B97" s="6"/>
       <c r="C97" s="6"/>
       <c r="D97" s="6"/>
       <c r="E97" s="6"/>
-      <c r="F97" s="7"/>
+      <c r="F97" s="6"/>
       <c r="G97" s="6"/>
       <c r="H97" s="6"/>
       <c r="I97" s="6"/>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A98" s="5"/>
-      <c r="B98" s="5"/>
+      <c r="A98" s="6"/>
+      <c r="B98" s="6"/>
       <c r="C98" s="6"/>
       <c r="D98" s="6"/>
       <c r="E98" s="6"/>
-      <c r="F98" s="7"/>
+      <c r="F98" s="6"/>
       <c r="G98" s="6"/>
       <c r="H98" s="6"/>
       <c r="I98" s="6"/>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A99" s="5"/>
-      <c r="B99" s="5"/>
+      <c r="A99" s="6"/>
+      <c r="B99" s="6"/>
       <c r="C99" s="6"/>
       <c r="D99" s="6"/>
       <c r="E99" s="6"/>
-      <c r="F99" s="7"/>
+      <c r="F99" s="6"/>
       <c r="G99" s="6"/>
       <c r="H99" s="6"/>
       <c r="I99" s="6"/>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A100" s="5"/>
-      <c r="B100" s="5"/>
+      <c r="A100" s="6"/>
+      <c r="B100" s="6"/>
       <c r="C100" s="6"/>
       <c r="D100" s="6"/>
       <c r="E100" s="6"/>
-      <c r="F100" s="7"/>
+      <c r="F100" s="6"/>
       <c r="G100" s="6"/>
       <c r="H100" s="6"/>
       <c r="I100" s="6"/>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A101" s="5"/>
-      <c r="B101" s="5"/>
+      <c r="A101" s="6"/>
+      <c r="B101" s="6"/>
       <c r="C101" s="6"/>
       <c r="D101" s="6"/>
       <c r="E101" s="6"/>
-      <c r="F101" s="7"/>
+      <c r="F101" s="6"/>
       <c r="G101" s="6"/>
       <c r="H101" s="6"/>
       <c r="I101" s="6"/>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A102" s="5"/>
-      <c r="B102" s="5"/>
+      <c r="A102" s="6"/>
+      <c r="B102" s="6"/>
       <c r="C102" s="6"/>
       <c r="D102" s="6"/>
       <c r="E102" s="6"/>
-      <c r="F102" s="7"/>
+      <c r="F102" s="6"/>
       <c r="G102" s="6"/>
       <c r="H102" s="6"/>
       <c r="I102" s="6"/>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A103" s="5"/>
-      <c r="B103" s="5"/>
+      <c r="A103" s="6"/>
+      <c r="B103" s="6"/>
       <c r="C103" s="6"/>
       <c r="D103" s="6"/>
       <c r="E103" s="6"/>
-      <c r="F103" s="7"/>
+      <c r="F103" s="6"/>
       <c r="G103" s="6"/>
       <c r="H103" s="6"/>
       <c r="I103" s="6"/>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A104" s="5"/>
-      <c r="B104" s="5"/>
+      <c r="A104" s="6"/>
+      <c r="B104" s="6"/>
       <c r="C104" s="6"/>
       <c r="D104" s="6"/>
       <c r="E104" s="6"/>
-      <c r="F104" s="7"/>
+      <c r="F104" s="6"/>
       <c r="G104" s="6"/>
       <c r="H104" s="6"/>
       <c r="I104" s="6"/>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A105" s="5"/>
-      <c r="B105" s="5"/>
+      <c r="A105" s="6"/>
+      <c r="B105" s="6"/>
       <c r="C105" s="6"/>
       <c r="D105" s="6"/>
       <c r="E105" s="6"/>
-      <c r="F105" s="7"/>
+      <c r="F105" s="6"/>
       <c r="G105" s="6"/>
       <c r="H105" s="6"/>
       <c r="I105" s="6"/>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A106" s="5"/>
-      <c r="B106" s="5"/>
+      <c r="A106" s="6"/>
+      <c r="B106" s="6"/>
       <c r="C106" s="6"/>
       <c r="D106" s="6"/>
       <c r="E106" s="6"/>
-      <c r="F106" s="7"/>
+      <c r="F106" s="6"/>
       <c r="G106" s="6"/>
       <c r="H106" s="6"/>
       <c r="I106" s="6"/>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A107" s="5"/>
-      <c r="B107" s="5"/>
+      <c r="A107" s="6"/>
+      <c r="B107" s="6"/>
       <c r="C107" s="6"/>
       <c r="D107" s="6"/>
       <c r="E107" s="6"/>
-      <c r="F107" s="7"/>
+      <c r="F107" s="6"/>
       <c r="G107" s="6"/>
       <c r="H107" s="6"/>
       <c r="I107" s="6"/>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A108" s="5"/>
-      <c r="B108" s="5"/>
+      <c r="A108" s="6"/>
+      <c r="B108" s="6"/>
       <c r="C108" s="6"/>
       <c r="D108" s="6"/>
       <c r="E108" s="6"/>
-      <c r="F108" s="7"/>
+      <c r="F108" s="6"/>
       <c r="G108" s="6"/>
       <c r="H108" s="6"/>
       <c r="I108" s="6"/>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A109" s="5"/>
-      <c r="B109" s="5"/>
+      <c r="A109" s="6"/>
+      <c r="B109" s="6"/>
       <c r="C109" s="6"/>
       <c r="D109" s="6"/>
       <c r="E109" s="6"/>
-      <c r="F109" s="7"/>
+      <c r="F109" s="6"/>
       <c r="G109" s="6"/>
       <c r="H109" s="6"/>
       <c r="I109" s="6"/>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A110" s="5"/>
-      <c r="B110" s="5"/>
+      <c r="A110" s="6"/>
+      <c r="B110" s="6"/>
       <c r="C110" s="6"/>
       <c r="D110" s="6"/>
       <c r="E110" s="6"/>
-      <c r="F110" s="7"/>
+      <c r="F110" s="6"/>
       <c r="G110" s="6"/>
       <c r="H110" s="6"/>
       <c r="I110" s="6"/>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A111" s="5"/>
-      <c r="B111" s="5"/>
+      <c r="A111" s="6"/>
+      <c r="B111" s="6"/>
       <c r="C111" s="6"/>
       <c r="D111" s="6"/>
       <c r="E111" s="6"/>
-      <c r="F111" s="7"/>
+      <c r="F111" s="6"/>
       <c r="G111" s="6"/>
       <c r="H111" s="6"/>
       <c r="I111" s="6"/>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A112" s="5"/>
-      <c r="B112" s="5"/>
+      <c r="A112" s="6"/>
+      <c r="B112" s="6"/>
       <c r="C112" s="6"/>
       <c r="D112" s="6"/>
       <c r="E112" s="6"/>
-      <c r="F112" s="7"/>
+      <c r="F112" s="6"/>
       <c r="G112" s="6"/>
       <c r="H112" s="6"/>
       <c r="I112" s="6"/>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A113" s="5"/>
-      <c r="B113" s="5"/>
+      <c r="A113" s="6"/>
+      <c r="B113" s="6"/>
       <c r="C113" s="6"/>
       <c r="D113" s="6"/>
       <c r="E113" s="6"/>
-      <c r="F113" s="7"/>
+      <c r="F113" s="6"/>
       <c r="G113" s="6"/>
       <c r="H113" s="6"/>
       <c r="I113" s="6"/>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A114" s="5"/>
-      <c r="B114" s="5"/>
+      <c r="A114" s="6"/>
+      <c r="B114" s="6"/>
       <c r="C114" s="6"/>
       <c r="D114" s="6"/>
       <c r="E114" s="6"/>
-      <c r="F114" s="7"/>
+      <c r="F114" s="6"/>
       <c r="G114" s="6"/>
       <c r="H114" s="6"/>
       <c r="I114" s="6"/>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A115" s="5"/>
-      <c r="B115" s="5"/>
+      <c r="A115" s="6"/>
+      <c r="B115" s="6"/>
       <c r="C115" s="6"/>
       <c r="D115" s="6"/>
       <c r="E115" s="6"/>
-      <c r="F115" s="7"/>
+      <c r="F115" s="6"/>
       <c r="G115" s="6"/>
       <c r="H115" s="6"/>
       <c r="I115" s="6"/>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A116" s="5"/>
-      <c r="B116" s="5"/>
+      <c r="A116" s="6"/>
+      <c r="B116" s="6"/>
       <c r="C116" s="6"/>
       <c r="D116" s="6"/>
       <c r="E116" s="6"/>
-      <c r="F116" s="7"/>
+      <c r="F116" s="6"/>
       <c r="G116" s="6"/>
       <c r="H116" s="6"/>
       <c r="I116" s="6"/>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A117" s="5"/>
-      <c r="B117" s="5"/>
+      <c r="A117" s="6"/>
+      <c r="B117" s="6"/>
       <c r="C117" s="6"/>
       <c r="D117" s="6"/>
       <c r="E117" s="6"/>
-      <c r="F117" s="7"/>
+      <c r="F117" s="6"/>
       <c r="G117" s="6"/>
       <c r="H117" s="6"/>
       <c r="I117" s="6"/>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A118" s="5"/>
-      <c r="B118" s="5"/>
+      <c r="A118" s="6"/>
+      <c r="B118" s="6"/>
       <c r="C118" s="6"/>
       <c r="D118" s="6"/>
       <c r="E118" s="6"/>
-      <c r="F118" s="7"/>
+      <c r="F118" s="6"/>
       <c r="G118" s="6"/>
       <c r="H118" s="6"/>
       <c r="I118" s="6"/>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A119" s="5"/>
-      <c r="B119" s="5"/>
+      <c r="A119" s="6"/>
+      <c r="B119" s="6"/>
       <c r="C119" s="6"/>
       <c r="D119" s="6"/>
       <c r="E119" s="6"/>
-      <c r="F119" s="7"/>
+      <c r="F119" s="6"/>
       <c r="G119" s="6"/>
       <c r="H119" s="6"/>
       <c r="I119" s="6"/>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A120" s="5"/>
-      <c r="B120" s="5"/>
+      <c r="A120" s="6"/>
+      <c r="B120" s="6"/>
       <c r="C120" s="6"/>
       <c r="D120" s="6"/>
       <c r="E120" s="6"/>
-      <c r="F120" s="7"/>
+      <c r="F120" s="6"/>
       <c r="G120" s="6"/>
       <c r="H120" s="6"/>
       <c r="I120" s="6"/>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A121" s="5"/>
-      <c r="B121" s="5"/>
+      <c r="A121" s="6"/>
+      <c r="B121" s="6"/>
       <c r="C121" s="6"/>
       <c r="D121" s="6"/>
       <c r="E121" s="6"/>
-      <c r="F121" s="7"/>
+      <c r="F121" s="6"/>
       <c r="G121" s="6"/>
       <c r="H121" s="6"/>
       <c r="I121" s="6"/>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A122" s="5"/>
-      <c r="B122" s="5"/>
+      <c r="A122" s="6"/>
+      <c r="B122" s="6"/>
       <c r="C122" s="6"/>
       <c r="D122" s="6"/>
       <c r="E122" s="6"/>
-      <c r="F122" s="7"/>
+      <c r="F122" s="6"/>
       <c r="G122" s="6"/>
       <c r="H122" s="6"/>
       <c r="I122" s="6"/>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A123" s="5"/>
-      <c r="B123" s="5"/>
+      <c r="A123" s="6"/>
+      <c r="B123" s="6"/>
       <c r="C123" s="6"/>
       <c r="D123" s="6"/>
       <c r="E123" s="6"/>
-      <c r="F123" s="7"/>
+      <c r="F123" s="6"/>
       <c r="G123" s="6"/>
       <c r="H123" s="6"/>
       <c r="I123" s="6"/>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A124" s="5"/>
-      <c r="B124" s="5"/>
+      <c r="A124" s="6"/>
+      <c r="B124" s="6"/>
       <c r="C124" s="6"/>
       <c r="D124" s="6"/>
       <c r="E124" s="6"/>
-      <c r="F124" s="7"/>
+      <c r="F124" s="6"/>
       <c r="G124" s="6"/>
       <c r="H124" s="6"/>
       <c r="I124" s="6"/>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A125" s="5"/>
-      <c r="B125" s="5"/>
+      <c r="A125" s="6"/>
+      <c r="B125" s="6"/>
       <c r="C125" s="6"/>
       <c r="D125" s="6"/>
       <c r="E125" s="6"/>
-      <c r="F125" s="7"/>
+      <c r="F125" s="6"/>
       <c r="G125" s="6"/>
       <c r="H125" s="6"/>
       <c r="I125" s="6"/>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A126" s="5"/>
-      <c r="B126" s="5"/>
+      <c r="A126" s="6"/>
+      <c r="B126" s="6"/>
       <c r="C126" s="6"/>
       <c r="D126" s="6"/>
       <c r="E126" s="6"/>
-      <c r="F126" s="7"/>
+      <c r="F126" s="6"/>
       <c r="G126" s="6"/>
       <c r="H126" s="6"/>
       <c r="I126" s="6"/>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A127" s="5"/>
-      <c r="B127" s="5"/>
+      <c r="A127" s="6"/>
+      <c r="B127" s="6"/>
       <c r="C127" s="6"/>
       <c r="D127" s="6"/>
       <c r="E127" s="6"/>
-      <c r="F127" s="7"/>
+      <c r="F127" s="6"/>
       <c r="G127" s="6"/>
       <c r="H127" s="6"/>
       <c r="I127" s="6"/>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A128" s="5"/>
-      <c r="B128" s="5"/>
+      <c r="A128" s="6"/>
+      <c r="B128" s="6"/>
       <c r="C128" s="6"/>
       <c r="D128" s="6"/>
       <c r="E128" s="6"/>
-      <c r="F128" s="7"/>
+      <c r="F128" s="6"/>
       <c r="G128" s="6"/>
       <c r="H128" s="6"/>
       <c r="I128" s="6"/>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A129" s="5"/>
-      <c r="B129" s="5"/>
+      <c r="A129" s="6"/>
+      <c r="B129" s="6"/>
       <c r="C129" s="6"/>
       <c r="D129" s="6"/>
       <c r="E129" s="6"/>
-      <c r="F129" s="7"/>
+      <c r="F129" s="6"/>
       <c r="G129" s="6"/>
       <c r="H129" s="6"/>
       <c r="I129" s="6"/>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A130" s="5"/>
-      <c r="B130" s="5"/>
+      <c r="A130" s="6"/>
+      <c r="B130" s="6"/>
       <c r="C130" s="6"/>
       <c r="D130" s="6"/>
       <c r="E130" s="6"/>
-      <c r="F130" s="7"/>
+      <c r="F130" s="6"/>
       <c r="G130" s="6"/>
       <c r="H130" s="6"/>
       <c r="I130" s="6"/>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A131" s="5"/>
-      <c r="B131" s="5"/>
+      <c r="A131" s="6"/>
+      <c r="B131" s="6"/>
       <c r="C131" s="6"/>
       <c r="D131" s="6"/>
       <c r="E131" s="6"/>
-      <c r="F131" s="7"/>
+      <c r="F131" s="6"/>
       <c r="G131" s="6"/>
       <c r="H131" s="6"/>
       <c r="I131" s="6"/>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A132" s="5"/>
-      <c r="B132" s="5"/>
+      <c r="A132" s="6"/>
+      <c r="B132" s="6"/>
       <c r="C132" s="6"/>
       <c r="D132" s="6"/>
       <c r="E132" s="6"/>
-      <c r="F132" s="7"/>
+      <c r="F132" s="6"/>
       <c r="G132" s="6"/>
       <c r="H132" s="6"/>
       <c r="I132" s="6"/>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A133" s="5"/>
-      <c r="B133" s="5"/>
+      <c r="A133" s="6"/>
+      <c r="B133" s="6"/>
       <c r="C133" s="6"/>
       <c r="D133" s="6"/>
       <c r="E133" s="6"/>
-      <c r="F133" s="7"/>
+      <c r="F133" s="6"/>
       <c r="G133" s="6"/>
       <c r="H133" s="6"/>
       <c r="I133" s="6"/>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A134" s="5"/>
-      <c r="B134" s="5"/>
+      <c r="A134" s="6"/>
+      <c r="B134" s="6"/>
       <c r="C134" s="6"/>
       <c r="D134" s="6"/>
       <c r="E134" s="6"/>
-      <c r="F134" s="7"/>
+      <c r="F134" s="6"/>
       <c r="G134" s="6"/>
       <c r="H134" s="6"/>
       <c r="I134" s="6"/>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A135" s="5"/>
-      <c r="B135" s="5"/>
+      <c r="A135" s="6"/>
+      <c r="B135" s="6"/>
       <c r="C135" s="6"/>
       <c r="D135" s="6"/>
       <c r="E135" s="6"/>
-      <c r="F135" s="7"/>
+      <c r="F135" s="6"/>
       <c r="G135" s="6"/>
       <c r="H135" s="6"/>
       <c r="I135" s="6"/>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A136" s="5"/>
-      <c r="B136" s="5"/>
+      <c r="A136" s="6"/>
+      <c r="B136" s="6"/>
       <c r="C136" s="6"/>
       <c r="D136" s="6"/>
       <c r="E136" s="6"/>
-      <c r="F136" s="7"/>
+      <c r="F136" s="6"/>
       <c r="G136" s="6"/>
       <c r="H136" s="6"/>
       <c r="I136" s="6"/>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A137" s="5"/>
-      <c r="B137" s="5"/>
+      <c r="A137" s="6"/>
+      <c r="B137" s="6"/>
       <c r="C137" s="6"/>
       <c r="D137" s="6"/>
       <c r="E137" s="6"/>
-      <c r="F137" s="7"/>
+      <c r="F137" s="6"/>
       <c r="G137" s="6"/>
       <c r="H137" s="6"/>
       <c r="I137" s="6"/>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A138" s="5"/>
-      <c r="B138" s="5"/>
+      <c r="A138" s="6"/>
+      <c r="B138" s="6"/>
       <c r="C138" s="6"/>
       <c r="D138" s="6"/>
       <c r="E138" s="6"/>
-      <c r="F138" s="7"/>
+      <c r="F138" s="6"/>
       <c r="G138" s="6"/>
       <c r="H138" s="6"/>
       <c r="I138" s="6"/>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A139" s="5"/>
-      <c r="B139" s="5"/>
+      <c r="A139" s="6"/>
+      <c r="B139" s="6"/>
       <c r="C139" s="6"/>
       <c r="D139" s="6"/>
       <c r="E139" s="6"/>
-      <c r="F139" s="7"/>
+      <c r="F139" s="6"/>
       <c r="G139" s="6"/>
       <c r="H139" s="6"/>
       <c r="I139" s="6"/>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A140" s="5"/>
-      <c r="B140" s="5"/>
+      <c r="A140" s="6"/>
+      <c r="B140" s="6"/>
       <c r="C140" s="6"/>
       <c r="D140" s="6"/>
       <c r="E140" s="6"/>
-      <c r="F140" s="7"/>
+      <c r="F140" s="6"/>
       <c r="G140" s="6"/>
       <c r="H140" s="6"/>
       <c r="I140" s="6"/>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A141" s="5"/>
-      <c r="B141" s="5"/>
+      <c r="A141" s="6"/>
+      <c r="B141" s="6"/>
       <c r="C141" s="6"/>
       <c r="D141" s="6"/>
       <c r="E141" s="6"/>
-      <c r="F141" s="7"/>
+      <c r="F141" s="6"/>
       <c r="G141" s="6"/>
       <c r="H141" s="6"/>
       <c r="I141" s="6"/>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A142" s="5"/>
-      <c r="B142" s="5"/>
+      <c r="A142" s="6"/>
+      <c r="B142" s="6"/>
       <c r="C142" s="6"/>
       <c r="D142" s="6"/>
       <c r="E142" s="6"/>
-      <c r="F142" s="7"/>
+      <c r="F142" s="6"/>
       <c r="G142" s="6"/>
       <c r="H142" s="6"/>
       <c r="I142" s="6"/>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A143" s="5"/>
-      <c r="B143" s="5"/>
+      <c r="A143" s="6"/>
+      <c r="B143" s="6"/>
       <c r="C143" s="6"/>
       <c r="D143" s="6"/>
       <c r="E143" s="6"/>
-      <c r="F143" s="7"/>
+      <c r="F143" s="6"/>
       <c r="G143" s="6"/>
       <c r="H143" s="6"/>
       <c r="I143" s="6"/>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A144" s="5"/>
-      <c r="B144" s="5"/>
+      <c r="A144" s="6"/>
+      <c r="B144" s="6"/>
       <c r="C144" s="6"/>
       <c r="D144" s="6"/>
       <c r="E144" s="6"/>
-      <c r="F144" s="7"/>
+      <c r="F144" s="6"/>
       <c r="G144" s="6"/>
       <c r="H144" s="6"/>
       <c r="I144" s="6"/>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A145" s="5"/>
-      <c r="B145" s="5"/>
+      <c r="A145" s="6"/>
+      <c r="B145" s="6"/>
       <c r="C145" s="6"/>
       <c r="D145" s="6"/>
       <c r="E145" s="6"/>
-      <c r="F145" s="7"/>
+      <c r="F145" s="6"/>
       <c r="G145" s="6"/>
       <c r="H145" s="6"/>
       <c r="I145" s="6"/>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A146" s="5"/>
-      <c r="B146" s="5"/>
+      <c r="A146" s="6"/>
+      <c r="B146" s="6"/>
       <c r="C146" s="6"/>
       <c r="D146" s="6"/>
       <c r="E146" s="6"/>
-      <c r="F146" s="7"/>
+      <c r="F146" s="6"/>
       <c r="G146" s="6"/>
       <c r="H146" s="6"/>
       <c r="I146" s="6"/>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A147" s="5"/>
-      <c r="B147" s="5"/>
+      <c r="A147" s="6"/>
+      <c r="B147" s="6"/>
       <c r="C147" s="6"/>
       <c r="D147" s="6"/>
       <c r="E147" s="6"/>
-      <c r="F147" s="7"/>
+      <c r="F147" s="6"/>
       <c r="G147" s="6"/>
       <c r="H147" s="6"/>
       <c r="I147" s="6"/>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A148" s="5"/>
-      <c r="B148" s="5"/>
+      <c r="A148" s="6"/>
+      <c r="B148" s="6"/>
       <c r="C148" s="6"/>
       <c r="D148" s="6"/>
       <c r="E148" s="6"/>
-      <c r="F148" s="7"/>
+      <c r="F148" s="6"/>
       <c r="G148" s="6"/>
       <c r="H148" s="6"/>
       <c r="I148" s="6"/>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A149" s="5"/>
-      <c r="B149" s="5"/>
+      <c r="A149" s="6"/>
+      <c r="B149" s="6"/>
       <c r="C149" s="6"/>
       <c r="D149" s="6"/>
       <c r="E149" s="6"/>
-      <c r="F149" s="7"/>
+      <c r="F149" s="6"/>
       <c r="G149" s="6"/>
       <c r="H149" s="6"/>
       <c r="I149" s="6"/>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A150" s="5"/>
-      <c r="B150" s="5"/>
+      <c r="A150" s="6"/>
+      <c r="B150" s="6"/>
       <c r="C150" s="6"/>
       <c r="D150" s="6"/>
       <c r="E150" s="6"/>
-      <c r="F150" s="7"/>
+      <c r="F150" s="6"/>
       <c r="G150" s="6"/>
       <c r="H150" s="6"/>
       <c r="I150" s="6"/>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A151" s="5"/>
-      <c r="B151" s="5"/>
+      <c r="A151" s="6"/>
+      <c r="B151" s="6"/>
       <c r="C151" s="6"/>
       <c r="D151" s="6"/>
       <c r="E151" s="6"/>
-      <c r="F151" s="7"/>
+      <c r="F151" s="6"/>
       <c r="G151" s="6"/>
       <c r="H151" s="6"/>
       <c r="I151" s="6"/>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A152" s="5"/>
-      <c r="B152" s="5"/>
+      <c r="A152" s="6"/>
+      <c r="B152" s="6"/>
       <c r="C152" s="6"/>
       <c r="D152" s="6"/>
       <c r="E152" s="6"/>
-      <c r="F152" s="7"/>
+      <c r="F152" s="6"/>
       <c r="G152" s="6"/>
       <c r="H152" s="6"/>
       <c r="I152" s="6"/>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A153" s="5"/>
-      <c r="B153" s="5"/>
+      <c r="A153" s="6"/>
+      <c r="B153" s="6"/>
       <c r="C153" s="6"/>
       <c r="D153" s="6"/>
       <c r="E153" s="6"/>
-      <c r="F153" s="7"/>
+      <c r="F153" s="6"/>
       <c r="G153" s="6"/>
       <c r="H153" s="6"/>
       <c r="I153" s="6"/>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A154" s="5"/>
-      <c r="B154" s="5"/>
+      <c r="A154" s="6"/>
+      <c r="B154" s="6"/>
       <c r="C154" s="6"/>
       <c r="D154" s="6"/>
       <c r="E154" s="6"/>
-      <c r="F154" s="7"/>
+      <c r="F154" s="6"/>
       <c r="G154" s="6"/>
       <c r="H154" s="6"/>
       <c r="I154" s="6"/>
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A155" s="5"/>
-      <c r="B155" s="5"/>
+      <c r="A155" s="6"/>
+      <c r="B155" s="6"/>
       <c r="C155" s="6"/>
       <c r="D155" s="6"/>
       <c r="E155" s="6"/>
-      <c r="F155" s="7"/>
+      <c r="F155" s="6"/>
       <c r="G155" s="6"/>
       <c r="H155" s="6"/>
       <c r="I155" s="6"/>
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A156" s="5"/>
-      <c r="B156" s="5"/>
+      <c r="A156" s="6"/>
+      <c r="B156" s="6"/>
       <c r="C156" s="6"/>
       <c r="D156" s="6"/>
       <c r="E156" s="6"/>
-      <c r="F156" s="7"/>
+      <c r="F156" s="6"/>
       <c r="G156" s="6"/>
       <c r="H156" s="6"/>
       <c r="I156" s="6"/>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A157" s="5"/>
-      <c r="B157" s="5"/>
+      <c r="A157" s="6"/>
+      <c r="B157" s="6"/>
       <c r="C157" s="6"/>
       <c r="D157" s="6"/>
       <c r="E157" s="6"/>
-      <c r="F157" s="7"/>
+      <c r="F157" s="6"/>
       <c r="G157" s="6"/>
       <c r="H157" s="6"/>
       <c r="I157" s="6"/>
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A158" s="5"/>
-      <c r="B158" s="5"/>
+      <c r="A158" s="6"/>
+      <c r="B158" s="6"/>
       <c r="C158" s="6"/>
       <c r="D158" s="6"/>
       <c r="E158" s="6"/>
-      <c r="F158" s="7"/>
+      <c r="F158" s="6"/>
       <c r="G158" s="6"/>
       <c r="H158" s="6"/>
       <c r="I158" s="6"/>
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A159" s="5"/>
-      <c r="B159" s="5"/>
+      <c r="A159" s="6"/>
+      <c r="B159" s="6"/>
       <c r="C159" s="6"/>
       <c r="D159" s="6"/>
       <c r="E159" s="6"/>
-      <c r="F159" s="7"/>
+      <c r="F159" s="6"/>
       <c r="G159" s="6"/>
       <c r="H159" s="6"/>
       <c r="I159" s="6"/>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A160" s="5"/>
-      <c r="B160" s="5"/>
+      <c r="A160" s="6"/>
+      <c r="B160" s="6"/>
       <c r="C160" s="6"/>
       <c r="D160" s="6"/>
       <c r="E160" s="6"/>
-      <c r="F160" s="7"/>
+      <c r="F160" s="6"/>
       <c r="G160" s="6"/>
       <c r="H160" s="6"/>
       <c r="I160" s="6"/>
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A161" s="5"/>
-      <c r="B161" s="5"/>
+      <c r="A161" s="6"/>
+      <c r="B161" s="6"/>
       <c r="C161" s="6"/>
       <c r="D161" s="6"/>
       <c r="E161" s="6"/>
-      <c r="F161" s="7"/>
+      <c r="F161" s="6"/>
       <c r="G161" s="6"/>
       <c r="H161" s="6"/>
       <c r="I161" s="6"/>
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A162" s="5"/>
-      <c r="B162" s="5"/>
+      <c r="A162" s="6"/>
+      <c r="B162" s="6"/>
       <c r="C162" s="6"/>
       <c r="D162" s="6"/>
       <c r="E162" s="6"/>
-      <c r="F162" s="7"/>
+      <c r="F162" s="6"/>
       <c r="G162" s="6"/>
       <c r="H162" s="6"/>
       <c r="I162" s="6"/>
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A163" s="5"/>
-      <c r="B163" s="5"/>
+      <c r="A163" s="6"/>
+      <c r="B163" s="6"/>
       <c r="C163" s="6"/>
       <c r="D163" s="6"/>
       <c r="E163" s="6"/>
-      <c r="F163" s="7"/>
+      <c r="F163" s="6"/>
       <c r="G163" s="6"/>
       <c r="H163" s="6"/>
       <c r="I163" s="6"/>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A164" s="5"/>
-      <c r="B164" s="5"/>
+      <c r="A164" s="6"/>
+      <c r="B164" s="6"/>
       <c r="C164" s="6"/>
       <c r="D164" s="6"/>
       <c r="E164" s="6"/>
-      <c r="F164" s="7"/>
+      <c r="F164" s="6"/>
       <c r="G164" s="6"/>
       <c r="H164" s="6"/>
       <c r="I164" s="6"/>
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A165" s="5"/>
-      <c r="B165" s="5"/>
+      <c r="A165" s="6"/>
+      <c r="B165" s="6"/>
       <c r="C165" s="6"/>
       <c r="D165" s="6"/>
       <c r="E165" s="6"/>
-      <c r="F165" s="7"/>
+      <c r="F165" s="6"/>
       <c r="G165" s="6"/>
       <c r="H165" s="6"/>
       <c r="I165" s="6"/>
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A166" s="5"/>
-      <c r="B166" s="5"/>
+      <c r="A166" s="6"/>
+      <c r="B166" s="6"/>
       <c r="C166" s="6"/>
       <c r="D166" s="6"/>
       <c r="E166" s="6"/>
-      <c r="F166" s="7"/>
+      <c r="F166" s="6"/>
       <c r="G166" s="6"/>
       <c r="H166" s="6"/>
       <c r="I166" s="6"/>
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A167" s="5"/>
-      <c r="B167" s="5"/>
+      <c r="A167" s="6"/>
+      <c r="B167" s="6"/>
       <c r="C167" s="6"/>
       <c r="D167" s="6"/>
       <c r="E167" s="6"/>
-      <c r="F167" s="7"/>
+      <c r="F167" s="6"/>
       <c r="G167" s="6"/>
       <c r="H167" s="6"/>
       <c r="I167" s="6"/>
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A168" s="5"/>
-      <c r="B168" s="5"/>
+      <c r="A168" s="6"/>
+      <c r="B168" s="6"/>
       <c r="C168" s="6"/>
       <c r="D168" s="6"/>
       <c r="E168" s="6"/>
-      <c r="F168" s="7"/>
+      <c r="F168" s="6"/>
       <c r="G168" s="6"/>
       <c r="H168" s="6"/>
       <c r="I168" s="6"/>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A169" s="5"/>
-      <c r="B169" s="5"/>
+      <c r="A169" s="6"/>
+      <c r="B169" s="6"/>
       <c r="C169" s="6"/>
       <c r="D169" s="6"/>
       <c r="E169" s="6"/>
-      <c r="F169" s="7"/>
+      <c r="F169" s="6"/>
       <c r="G169" s="6"/>
       <c r="H169" s="6"/>
       <c r="I169" s="6"/>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A170" s="5"/>
-      <c r="B170" s="5"/>
+      <c r="A170" s="6"/>
+      <c r="B170" s="6"/>
       <c r="C170" s="6"/>
       <c r="D170" s="6"/>
       <c r="E170" s="6"/>
-      <c r="F170" s="7"/>
+      <c r="F170" s="6"/>
       <c r="G170" s="6"/>
       <c r="H170" s="6"/>
       <c r="I170" s="6"/>
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A171" s="5"/>
-      <c r="B171" s="5"/>
+      <c r="A171" s="6"/>
+      <c r="B171" s="6"/>
       <c r="C171" s="6"/>
       <c r="D171" s="6"/>
       <c r="E171" s="6"/>
-      <c r="F171" s="7"/>
+      <c r="F171" s="6"/>
       <c r="G171" s="6"/>
       <c r="H171" s="6"/>
       <c r="I171" s="6"/>
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A172" s="5"/>
-      <c r="B172" s="5"/>
+      <c r="A172" s="6"/>
+      <c r="B172" s="6"/>
       <c r="C172" s="6"/>
       <c r="D172" s="6"/>
       <c r="E172" s="6"/>
-      <c r="F172" s="7"/>
+      <c r="F172" s="6"/>
       <c r="G172" s="6"/>
       <c r="H172" s="6"/>
       <c r="I172" s="6"/>
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A173" s="5"/>
-      <c r="B173" s="5"/>
+      <c r="A173" s="6"/>
+      <c r="B173" s="6"/>
       <c r="C173" s="6"/>
       <c r="D173" s="6"/>
       <c r="E173" s="6"/>
-      <c r="F173" s="7"/>
+      <c r="F173" s="6"/>
       <c r="G173" s="6"/>
       <c r="H173" s="6"/>
       <c r="I173" s="6"/>
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A174" s="5"/>
-      <c r="B174" s="5"/>
+      <c r="A174" s="6"/>
+      <c r="B174" s="6"/>
       <c r="C174" s="6"/>
       <c r="D174" s="6"/>
       <c r="E174" s="6"/>
-      <c r="F174" s="7"/>
+      <c r="F174" s="6"/>
       <c r="G174" s="6"/>
       <c r="H174" s="6"/>
       <c r="I174" s="6"/>
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A175" s="5"/>
-      <c r="B175" s="5"/>
+      <c r="A175" s="6"/>
+      <c r="B175" s="6"/>
       <c r="C175" s="6"/>
       <c r="D175" s="6"/>
       <c r="E175" s="6"/>
-      <c r="F175" s="7"/>
+      <c r="F175" s="6"/>
       <c r="G175" s="6"/>
       <c r="H175" s="6"/>
       <c r="I175" s="6"/>
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A176" s="5"/>
-      <c r="B176" s="5"/>
+      <c r="A176" s="6"/>
+      <c r="B176" s="6"/>
       <c r="C176" s="6"/>
       <c r="D176" s="6"/>
       <c r="E176" s="6"/>
-      <c r="F176" s="7"/>
+      <c r="F176" s="6"/>
       <c r="G176" s="6"/>
       <c r="H176" s="6"/>
       <c r="I176" s="6"/>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A177" s="5"/>
-      <c r="B177" s="5"/>
+      <c r="A177" s="6"/>
+      <c r="B177" s="6"/>
       <c r="C177" s="6"/>
       <c r="D177" s="6"/>
       <c r="E177" s="6"/>
-      <c r="F177" s="7"/>
+      <c r="F177" s="6"/>
       <c r="G177" s="6"/>
       <c r="H177" s="6"/>
       <c r="I177" s="6"/>
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A178" s="5"/>
-      <c r="B178" s="5"/>
+      <c r="A178" s="6"/>
+      <c r="B178" s="6"/>
       <c r="C178" s="6"/>
       <c r="D178" s="6"/>
       <c r="E178" s="6"/>
-      <c r="F178" s="7"/>
+      <c r="F178" s="6"/>
       <c r="G178" s="6"/>
       <c r="H178" s="6"/>
       <c r="I178" s="6"/>
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A179" s="5"/>
-      <c r="B179" s="5"/>
+      <c r="A179" s="6"/>
+      <c r="B179" s="6"/>
       <c r="C179" s="6"/>
       <c r="D179" s="6"/>
       <c r="E179" s="6"/>
-      <c r="F179" s="7"/>
+      <c r="F179" s="6"/>
       <c r="G179" s="6"/>
       <c r="H179" s="6"/>
       <c r="I179" s="6"/>
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A180" s="5"/>
-      <c r="B180" s="5"/>
+      <c r="A180" s="6"/>
+      <c r="B180" s="6"/>
       <c r="C180" s="6"/>
       <c r="D180" s="6"/>
       <c r="E180" s="6"/>
-      <c r="F180" s="7"/>
+      <c r="F180" s="6"/>
       <c r="G180" s="6"/>
       <c r="H180" s="6"/>
       <c r="I180" s="6"/>
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A181" s="5"/>
-      <c r="B181" s="5"/>
+      <c r="A181" s="6"/>
+      <c r="B181" s="6"/>
       <c r="C181" s="6"/>
       <c r="D181" s="6"/>
       <c r="E181" s="6"/>
-      <c r="F181" s="7"/>
+      <c r="F181" s="6"/>
       <c r="G181" s="6"/>
       <c r="H181" s="6"/>
       <c r="I181" s="6"/>
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A182" s="5"/>
-      <c r="B182" s="5"/>
+      <c r="A182" s="6"/>
+      <c r="B182" s="6"/>
       <c r="C182" s="6"/>
       <c r="D182" s="6"/>
       <c r="E182" s="6"/>
-      <c r="F182" s="7"/>
+      <c r="F182" s="6"/>
       <c r="G182" s="6"/>
       <c r="H182" s="6"/>
       <c r="I182" s="6"/>
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A183" s="5"/>
-      <c r="B183" s="5"/>
+      <c r="A183" s="6"/>
+      <c r="B183" s="6"/>
       <c r="C183" s="6"/>
       <c r="D183" s="6"/>
       <c r="E183" s="6"/>
-      <c r="F183" s="7"/>
+      <c r="F183" s="6"/>
       <c r="G183" s="6"/>
       <c r="H183" s="6"/>
       <c r="I183" s="6"/>
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A184" s="5"/>
-      <c r="B184" s="5"/>
+      <c r="A184" s="6"/>
+      <c r="B184" s="6"/>
       <c r="C184" s="6"/>
       <c r="D184" s="6"/>
       <c r="E184" s="6"/>
-      <c r="F184" s="7"/>
+      <c r="F184" s="6"/>
       <c r="G184" s="6"/>
       <c r="H184" s="6"/>
       <c r="I184" s="6"/>
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A185" s="5"/>
-      <c r="B185" s="5"/>
+      <c r="A185" s="6"/>
+      <c r="B185" s="6"/>
       <c r="C185" s="6"/>
       <c r="D185" s="6"/>
       <c r="E185" s="6"/>
-      <c r="F185" s="7"/>
+      <c r="F185" s="6"/>
       <c r="G185" s="6"/>
       <c r="H185" s="6"/>
       <c r="I185" s="6"/>
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A186" s="5"/>
-      <c r="B186" s="5"/>
+      <c r="A186" s="6"/>
+      <c r="B186" s="6"/>
       <c r="C186" s="6"/>
       <c r="D186" s="6"/>
       <c r="E186" s="6"/>
-      <c r="F186" s="7"/>
+      <c r="F186" s="6"/>
       <c r="G186" s="6"/>
       <c r="H186" s="6"/>
       <c r="I186" s="6"/>
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A187" s="5"/>
-      <c r="B187" s="5"/>
+      <c r="A187" s="6"/>
+      <c r="B187" s="6"/>
       <c r="C187" s="6"/>
       <c r="D187" s="6"/>
       <c r="E187" s="6"/>
-      <c r="F187" s="7"/>
+      <c r="F187" s="6"/>
       <c r="G187" s="6"/>
       <c r="H187" s="6"/>
       <c r="I187" s="6"/>
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A188" s="5"/>
-      <c r="B188" s="5"/>
+      <c r="A188" s="6"/>
+      <c r="B188" s="6"/>
       <c r="C188" s="6"/>
       <c r="D188" s="6"/>
       <c r="E188" s="6"/>
-      <c r="F188" s="7"/>
+      <c r="F188" s="6"/>
       <c r="G188" s="6"/>
       <c r="H188" s="6"/>
       <c r="I188" s="6"/>
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A189" s="5"/>
-      <c r="B189" s="5"/>
+      <c r="A189" s="6"/>
+      <c r="B189" s="6"/>
       <c r="C189" s="6"/>
       <c r="D189" s="6"/>
       <c r="E189" s="6"/>
-      <c r="F189" s="7"/>
+      <c r="F189" s="6"/>
       <c r="G189" s="6"/>
       <c r="H189" s="6"/>
       <c r="I189" s="6"/>
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A190" s="5"/>
-      <c r="B190" s="5"/>
+      <c r="A190" s="6"/>
+      <c r="B190" s="6"/>
       <c r="C190" s="6"/>
       <c r="D190" s="6"/>
       <c r="E190" s="6"/>
-      <c r="F190" s="7"/>
+      <c r="F190" s="6"/>
       <c r="G190" s="6"/>
       <c r="H190" s="6"/>
       <c r="I190" s="6"/>
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A191" s="5"/>
-      <c r="B191" s="5"/>
+      <c r="A191" s="6"/>
+      <c r="B191" s="6"/>
       <c r="C191" s="6"/>
       <c r="D191" s="6"/>
       <c r="E191" s="6"/>
-      <c r="F191" s="7"/>
+      <c r="F191" s="6"/>
       <c r="G191" s="6"/>
       <c r="H191" s="6"/>
       <c r="I191" s="6"/>
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A192" s="5"/>
-      <c r="B192" s="5"/>
+      <c r="A192" s="6"/>
+      <c r="B192" s="6"/>
       <c r="C192" s="6"/>
       <c r="D192" s="6"/>
       <c r="E192" s="6"/>
-      <c r="F192" s="7"/>
+      <c r="F192" s="6"/>
       <c r="G192" s="6"/>
       <c r="H192" s="6"/>
       <c r="I192" s="6"/>
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A193" s="5"/>
-      <c r="B193" s="5"/>
+      <c r="A193" s="6"/>
+      <c r="B193" s="6"/>
       <c r="C193" s="6"/>
       <c r="D193" s="6"/>
       <c r="E193" s="6"/>
-      <c r="F193" s="7"/>
+      <c r="F193" s="6"/>
       <c r="G193" s="6"/>
       <c r="H193" s="6"/>
       <c r="I193" s="6"/>
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A194" s="5"/>
-      <c r="B194" s="5"/>
+      <c r="A194" s="6"/>
+      <c r="B194" s="6"/>
       <c r="C194" s="6"/>
       <c r="D194" s="6"/>
       <c r="E194" s="6"/>
-      <c r="F194" s="7"/>
+      <c r="F194" s="6"/>
       <c r="G194" s="6"/>
       <c r="H194" s="6"/>
       <c r="I194" s="6"/>
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A195" s="5"/>
-      <c r="B195" s="5"/>
+      <c r="A195" s="6"/>
+      <c r="B195" s="6"/>
       <c r="C195" s="6"/>
       <c r="D195" s="6"/>
       <c r="E195" s="6"/>
-      <c r="F195" s="7"/>
+      <c r="F195" s="6"/>
       <c r="G195" s="6"/>
       <c r="H195" s="6"/>
       <c r="I195" s="6"/>
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A196" s="5"/>
-      <c r="B196" s="5"/>
+      <c r="A196" s="6"/>
+      <c r="B196" s="6"/>
       <c r="C196" s="6"/>
       <c r="D196" s="6"/>
       <c r="E196" s="6"/>
-      <c r="F196" s="7"/>
+      <c r="F196" s="6"/>
       <c r="G196" s="6"/>
       <c r="H196" s="6"/>
       <c r="I196" s="6"/>
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A197" s="5"/>
-      <c r="B197" s="5"/>
+      <c r="A197" s="6"/>
+      <c r="B197" s="6"/>
       <c r="C197" s="6"/>
       <c r="D197" s="6"/>
       <c r="E197" s="6"/>
-      <c r="F197" s="7"/>
+      <c r="F197" s="6"/>
       <c r="G197" s="6"/>
       <c r="H197" s="6"/>
       <c r="I197" s="6"/>
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A198" s="5"/>
-      <c r="B198" s="5"/>
+      <c r="A198" s="6"/>
+      <c r="B198" s="6"/>
       <c r="C198" s="6"/>
       <c r="D198" s="6"/>
       <c r="E198" s="6"/>
-      <c r="F198" s="7"/>
+      <c r="F198" s="6"/>
       <c r="G198" s="6"/>
       <c r="H198" s="6"/>
       <c r="I198" s="6"/>
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A199" s="5"/>
-      <c r="B199" s="5"/>
+      <c r="A199" s="6"/>
+      <c r="B199" s="6"/>
       <c r="C199" s="6"/>
       <c r="D199" s="6"/>
       <c r="E199" s="6"/>
-      <c r="F199" s="7"/>
+      <c r="F199" s="6"/>
       <c r="G199" s="6"/>
       <c r="H199" s="6"/>
       <c r="I199" s="6"/>
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A200" s="5"/>
-      <c r="B200" s="5"/>
+      <c r="A200" s="6"/>
+      <c r="B200" s="6"/>
       <c r="C200" s="6"/>
       <c r="D200" s="6"/>
       <c r="E200" s="6"/>
-      <c r="F200" s="7"/>
+      <c r="F200" s="6"/>
       <c r="G200" s="6"/>
       <c r="H200" s="6"/>
       <c r="I200" s="6"/>
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A201" s="5"/>
-      <c r="B201" s="5"/>
+      <c r="A201" s="6"/>
+      <c r="B201" s="6"/>
       <c r="C201" s="6"/>
       <c r="D201" s="6"/>
       <c r="E201" s="6"/>
-      <c r="F201" s="7"/>
+      <c r="F201" s="6"/>
       <c r="G201" s="6"/>
       <c r="H201" s="6"/>
       <c r="I201" s="6"/>
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A202" s="5"/>
-      <c r="B202" s="5"/>
+      <c r="A202" s="6"/>
+      <c r="B202" s="6"/>
       <c r="C202" s="6"/>
       <c r="D202" s="6"/>
       <c r="E202" s="6"/>
-      <c r="F202" s="7"/>
+      <c r="F202" s="6"/>
       <c r="G202" s="6"/>
       <c r="H202" s="6"/>
       <c r="I202" s="6"/>
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A203" s="5"/>
-      <c r="B203" s="5"/>
+      <c r="A203" s="6"/>
+      <c r="B203" s="6"/>
       <c r="C203" s="6"/>
       <c r="D203" s="6"/>
       <c r="E203" s="6"/>
-      <c r="F203" s="7"/>
+      <c r="F203" s="6"/>
       <c r="G203" s="6"/>
       <c r="H203" s="6"/>
       <c r="I203" s="6"/>
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A204" s="5"/>
-      <c r="B204" s="5"/>
+      <c r="A204" s="6"/>
+      <c r="B204" s="6"/>
       <c r="C204" s="6"/>
       <c r="D204" s="6"/>
       <c r="E204" s="6"/>
-      <c r="F204" s="7"/>
+      <c r="F204" s="6"/>
       <c r="G204" s="6"/>
       <c r="H204" s="6"/>
       <c r="I204" s="6"/>
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A205" s="5"/>
-      <c r="B205" s="5"/>
+      <c r="A205" s="6"/>
+      <c r="B205" s="6"/>
       <c r="C205" s="6"/>
       <c r="D205" s="6"/>
       <c r="E205" s="6"/>
-      <c r="F205" s="7"/>
+      <c r="F205" s="6"/>
       <c r="G205" s="6"/>
       <c r="H205" s="6"/>
       <c r="I205" s="6"/>
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A206" s="5"/>
-      <c r="B206" s="5"/>
+      <c r="A206" s="6"/>
+      <c r="B206" s="6"/>
       <c r="C206" s="6"/>
       <c r="D206" s="6"/>
       <c r="E206" s="6"/>
-      <c r="F206" s="7"/>
+      <c r="F206" s="6"/>
       <c r="G206" s="6"/>
       <c r="H206" s="6"/>
       <c r="I206" s="6"/>
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A207" s="5"/>
-      <c r="B207" s="5"/>
+      <c r="A207" s="6"/>
+      <c r="B207" s="6"/>
       <c r="C207" s="6"/>
       <c r="D207" s="6"/>
       <c r="E207" s="6"/>
-      <c r="F207" s="7"/>
+      <c r="F207" s="6"/>
       <c r="G207" s="6"/>
       <c r="H207" s="6"/>
       <c r="I207" s="6"/>
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A208" s="5"/>
-      <c r="B208" s="5"/>
+      <c r="A208" s="6"/>
+      <c r="B208" s="6"/>
       <c r="C208" s="6"/>
       <c r="D208" s="6"/>
       <c r="E208" s="6"/>
-      <c r="F208" s="7"/>
+      <c r="F208" s="6"/>
       <c r="G208" s="6"/>
       <c r="H208" s="6"/>
       <c r="I208" s="6"/>
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A209" s="5"/>
-      <c r="B209" s="5"/>
+      <c r="A209" s="6"/>
+      <c r="B209" s="6"/>
       <c r="C209" s="6"/>
       <c r="D209" s="6"/>
       <c r="E209" s="6"/>
-      <c r="F209" s="7"/>
+      <c r="F209" s="6"/>
       <c r="G209" s="6"/>
       <c r="H209" s="6"/>
       <c r="I209" s="6"/>
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A210" s="5"/>
-      <c r="B210" s="5"/>
+      <c r="A210" s="6"/>
+      <c r="B210" s="6"/>
       <c r="C210" s="6"/>
       <c r="D210" s="6"/>
       <c r="E210" s="6"/>
-      <c r="F210" s="7"/>
+      <c r="F210" s="6"/>
       <c r="G210" s="6"/>
       <c r="H210" s="6"/>
       <c r="I210" s="6"/>
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A211" s="5"/>
-      <c r="B211" s="5"/>
+      <c r="A211" s="6"/>
+      <c r="B211" s="6"/>
       <c r="C211" s="6"/>
       <c r="D211" s="6"/>
       <c r="E211" s="6"/>
-      <c r="F211" s="7"/>
+      <c r="F211" s="6"/>
       <c r="G211" s="6"/>
       <c r="H211" s="6"/>
       <c r="I211" s="6"/>
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A212" s="5"/>
-      <c r="B212" s="5"/>
+      <c r="A212" s="6"/>
+      <c r="B212" s="6"/>
       <c r="C212" s="6"/>
       <c r="D212" s="6"/>
       <c r="E212" s="6"/>
-      <c r="F212" s="7"/>
+      <c r="F212" s="6"/>
       <c r="G212" s="6"/>
       <c r="H212" s="6"/>
       <c r="I212" s="6"/>
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A213" s="5"/>
-      <c r="B213" s="5"/>
+      <c r="A213" s="6"/>
+      <c r="B213" s="6"/>
       <c r="C213" s="6"/>
       <c r="D213" s="6"/>
       <c r="E213" s="6"/>
-      <c r="F213" s="7"/>
+      <c r="F213" s="6"/>
       <c r="G213" s="6"/>
       <c r="H213" s="6"/>
       <c r="I213" s="6"/>
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A214" s="5"/>
-      <c r="B214" s="5"/>
+      <c r="A214" s="6"/>
+      <c r="B214" s="6"/>
       <c r="C214" s="6"/>
       <c r="D214" s="6"/>
       <c r="E214" s="6"/>
-      <c r="F214" s="7"/>
+      <c r="F214" s="6"/>
       <c r="G214" s="6"/>
       <c r="H214" s="6"/>
       <c r="I214" s="6"/>
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A215" s="5"/>
-      <c r="B215" s="5"/>
+      <c r="A215" s="6"/>
+      <c r="B215" s="6"/>
       <c r="C215" s="6"/>
       <c r="D215" s="6"/>
       <c r="E215" s="6"/>
-      <c r="F215" s="7"/>
+      <c r="F215" s="6"/>
       <c r="G215" s="6"/>
       <c r="H215" s="6"/>
       <c r="I215" s="6"/>
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A216" s="5"/>
-      <c r="B216" s="5"/>
+      <c r="A216" s="6"/>
+      <c r="B216" s="6"/>
       <c r="C216" s="6"/>
       <c r="D216" s="6"/>
       <c r="E216" s="6"/>
-      <c r="F216" s="7"/>
+      <c r="F216" s="6"/>
       <c r="G216" s="6"/>
       <c r="H216" s="6"/>
       <c r="I216" s="6"/>
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A217" s="5"/>
-      <c r="B217" s="5"/>
+      <c r="A217" s="6"/>
+      <c r="B217" s="6"/>
       <c r="C217" s="6"/>
       <c r="D217" s="6"/>
       <c r="E217" s="6"/>
-      <c r="F217" s="7"/>
+      <c r="F217" s="6"/>
       <c r="G217" s="6"/>
       <c r="H217" s="6"/>
       <c r="I217" s="6"/>
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A218" s="5"/>
-      <c r="B218" s="5"/>
+      <c r="A218" s="6"/>
+      <c r="B218" s="6"/>
       <c r="C218" s="6"/>
       <c r="D218" s="6"/>
       <c r="E218" s="6"/>
-      <c r="F218" s="7"/>
+      <c r="F218" s="6"/>
       <c r="G218" s="6"/>
       <c r="H218" s="6"/>
       <c r="I218" s="6"/>
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A219" s="5"/>
-      <c r="B219" s="5"/>
+      <c r="A219" s="6"/>
+      <c r="B219" s="6"/>
       <c r="C219" s="6"/>
       <c r="D219" s="6"/>
       <c r="E219" s="6"/>
-      <c r="F219" s="7"/>
+      <c r="F219" s="6"/>
       <c r="G219" s="6"/>
       <c r="H219" s="6"/>
       <c r="I219" s="6"/>
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A220" s="5"/>
-      <c r="B220" s="5"/>
+      <c r="A220" s="6"/>
+      <c r="B220" s="6"/>
       <c r="C220" s="6"/>
       <c r="D220" s="6"/>
       <c r="E220" s="6"/>
-      <c r="F220" s="7"/>
+      <c r="F220" s="6"/>
       <c r="G220" s="6"/>
       <c r="H220" s="6"/>
       <c r="I220" s="6"/>
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A221" s="5"/>
-      <c r="B221" s="5"/>
+      <c r="A221" s="6"/>
+      <c r="B221" s="6"/>
       <c r="C221" s="6"/>
       <c r="D221" s="6"/>
       <c r="E221" s="6"/>
-      <c r="F221" s="7"/>
+      <c r="F221" s="6"/>
       <c r="G221" s="6"/>
       <c r="H221" s="6"/>
       <c r="I221" s="6"/>
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A222" s="5"/>
-      <c r="B222" s="5"/>
+      <c r="A222" s="6"/>
+      <c r="B222" s="6"/>
       <c r="C222" s="6"/>
       <c r="D222" s="6"/>
       <c r="E222" s="6"/>
-      <c r="F222" s="7"/>
+      <c r="F222" s="6"/>
       <c r="G222" s="6"/>
       <c r="H222" s="6"/>
       <c r="I222" s="6"/>
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A223" s="5"/>
-      <c r="B223" s="5"/>
+      <c r="A223" s="6"/>
+      <c r="B223" s="6"/>
       <c r="C223" s="6"/>
       <c r="D223" s="6"/>
       <c r="E223" s="6"/>
-      <c r="F223" s="7"/>
+      <c r="F223" s="6"/>
       <c r="G223" s="6"/>
       <c r="H223" s="6"/>
       <c r="I223" s="6"/>
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A224" s="5"/>
-      <c r="B224" s="5"/>
+      <c r="A224" s="6"/>
+      <c r="B224" s="6"/>
       <c r="C224" s="6"/>
       <c r="D224" s="6"/>
       <c r="E224" s="6"/>
-      <c r="F224" s="7"/>
+      <c r="F224" s="6"/>
       <c r="G224" s="6"/>
       <c r="H224" s="6"/>
       <c r="I224" s="6"/>
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A225" s="5"/>
-      <c r="B225" s="5"/>
+      <c r="A225" s="6"/>
+      <c r="B225" s="6"/>
       <c r="C225" s="6"/>
       <c r="D225" s="6"/>
       <c r="E225" s="6"/>
-      <c r="F225" s="7"/>
+      <c r="F225" s="6"/>
       <c r="G225" s="6"/>
       <c r="H225" s="6"/>
       <c r="I225" s="6"/>
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A226" s="5"/>
-      <c r="B226" s="5"/>
+      <c r="A226" s="6"/>
+      <c r="B226" s="6"/>
       <c r="C226" s="6"/>
       <c r="D226" s="6"/>
       <c r="E226" s="6"/>
-      <c r="F226" s="7"/>
+      <c r="F226" s="6"/>
       <c r="G226" s="6"/>
       <c r="H226" s="6"/>
       <c r="I226" s="6"/>
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A227" s="5"/>
-      <c r="B227" s="5"/>
+      <c r="A227" s="6"/>
+      <c r="B227" s="6"/>
       <c r="C227" s="6"/>
       <c r="D227" s="6"/>
       <c r="E227" s="6"/>
-      <c r="F227" s="7"/>
+      <c r="F227" s="6"/>
       <c r="G227" s="6"/>
       <c r="H227" s="6"/>
       <c r="I227" s="6"/>
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A228" s="5"/>
-      <c r="B228" s="5"/>
+      <c r="A228" s="6"/>
+      <c r="B228" s="6"/>
       <c r="C228" s="6"/>
       <c r="D228" s="6"/>
       <c r="E228" s="6"/>
-      <c r="F228" s="7"/>
+      <c r="F228" s="6"/>
       <c r="G228" s="6"/>
       <c r="H228" s="6"/>
       <c r="I228" s="6"/>
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A229" s="5"/>
-      <c r="B229" s="5"/>
+      <c r="A229" s="6"/>
+      <c r="B229" s="6"/>
       <c r="C229" s="6"/>
       <c r="D229" s="6"/>
       <c r="E229" s="6"/>
-      <c r="F229" s="7"/>
+      <c r="F229" s="6"/>
       <c r="G229" s="6"/>
       <c r="H229" s="6"/>
       <c r="I229" s="6"/>
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A230" s="5"/>
-      <c r="B230" s="5"/>
+      <c r="A230" s="6"/>
+      <c r="B230" s="6"/>
       <c r="C230" s="6"/>
       <c r="D230" s="6"/>
       <c r="E230" s="6"/>
-      <c r="F230" s="7"/>
+      <c r="F230" s="6"/>
       <c r="G230" s="6"/>
       <c r="H230" s="6"/>
       <c r="I230" s="6"/>
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A231" s="5"/>
-      <c r="B231" s="5"/>
+      <c r="A231" s="6"/>
+      <c r="B231" s="6"/>
       <c r="C231" s="6"/>
       <c r="D231" s="6"/>
       <c r="E231" s="6"/>
-      <c r="F231" s="7"/>
+      <c r="F231" s="6"/>
       <c r="G231" s="6"/>
       <c r="H231" s="6"/>
       <c r="I231" s="6"/>
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A232" s="5"/>
-      <c r="B232" s="5"/>
+      <c r="A232" s="6"/>
+      <c r="B232" s="6"/>
       <c r="C232" s="6"/>
       <c r="D232" s="6"/>
       <c r="E232" s="6"/>
-      <c r="F232" s="7"/>
+      <c r="F232" s="6"/>
       <c r="G232" s="6"/>
       <c r="H232" s="6"/>
       <c r="I232" s="6"/>
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A233" s="5"/>
-      <c r="B233" s="5"/>
+      <c r="A233" s="6"/>
+      <c r="B233" s="6"/>
       <c r="C233" s="6"/>
       <c r="D233" s="6"/>
       <c r="E233" s="6"/>
-      <c r="F233" s="7"/>
+      <c r="F233" s="6"/>
       <c r="G233" s="6"/>
       <c r="H233" s="6"/>
       <c r="I233" s="6"/>
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A234" s="5"/>
-      <c r="B234" s="5"/>
+      <c r="A234" s="6"/>
+      <c r="B234" s="6"/>
       <c r="C234" s="6"/>
       <c r="D234" s="6"/>
       <c r="E234" s="6"/>
-      <c r="F234" s="7"/>
+      <c r="F234" s="6"/>
       <c r="G234" s="6"/>
       <c r="H234" s="6"/>
       <c r="I234" s="6"/>
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A235" s="5"/>
-      <c r="B235" s="5"/>
+      <c r="A235" s="6"/>
+      <c r="B235" s="6"/>
       <c r="C235" s="6"/>
       <c r="D235" s="6"/>
       <c r="E235" s="6"/>
-      <c r="F235" s="7"/>
+      <c r="F235" s="6"/>
       <c r="G235" s="6"/>
       <c r="H235" s="6"/>
       <c r="I235" s="6"/>
     </row>
     <row r="236" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A236" s="5"/>
-      <c r="B236" s="5"/>
+      <c r="A236" s="6"/>
+      <c r="B236" s="6"/>
       <c r="C236" s="6"/>
       <c r="D236" s="6"/>
       <c r="E236" s="6"/>
-      <c r="F236" s="7"/>
+      <c r="F236" s="6"/>
       <c r="G236" s="6"/>
       <c r="H236" s="6"/>
       <c r="I236" s="6"/>
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A237" s="5"/>
-      <c r="B237" s="5"/>
+      <c r="A237" s="6"/>
+      <c r="B237" s="6"/>
       <c r="C237" s="6"/>
       <c r="D237" s="6"/>
       <c r="E237" s="6"/>
-      <c r="F237" s="7"/>
+      <c r="F237" s="6"/>
       <c r="G237" s="6"/>
       <c r="H237" s="6"/>
       <c r="I237" s="6"/>
     </row>
     <row r="238" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A238" s="5"/>
-      <c r="B238" s="5"/>
+      <c r="A238" s="6"/>
+      <c r="B238" s="6"/>
       <c r="C238" s="6"/>
       <c r="D238" s="6"/>
       <c r="E238" s="6"/>
-      <c r="F238" s="7"/>
+      <c r="F238" s="6"/>
       <c r="G238" s="6"/>
       <c r="H238" s="6"/>
       <c r="I238" s="6"/>
     </row>
     <row r="239" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A239" s="5"/>
-      <c r="B239" s="5"/>
+      <c r="A239" s="6"/>
+      <c r="B239" s="6"/>
       <c r="C239" s="6"/>
       <c r="D239" s="6"/>
       <c r="E239" s="6"/>
-      <c r="F239" s="7"/>
+      <c r="F239" s="6"/>
       <c r="G239" s="6"/>
       <c r="H239" s="6"/>
       <c r="I239" s="6"/>
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A240" s="5"/>
-      <c r="B240" s="5"/>
+      <c r="A240" s="6"/>
+      <c r="B240" s="6"/>
       <c r="C240" s="6"/>
       <c r="D240" s="6"/>
       <c r="E240" s="6"/>
-      <c r="F240" s="7"/>
+      <c r="F240" s="6"/>
       <c r="G240" s="6"/>
       <c r="H240" s="6"/>
       <c r="I240" s="6"/>
     </row>
     <row r="241" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A241" s="5"/>
-      <c r="B241" s="5"/>
+      <c r="A241" s="6"/>
+      <c r="B241" s="6"/>
       <c r="C241" s="6"/>
       <c r="D241" s="6"/>
       <c r="E241" s="6"/>
-      <c r="F241" s="7"/>
+      <c r="F241" s="6"/>
       <c r="G241" s="6"/>
       <c r="H241" s="6"/>
       <c r="I241" s="6"/>
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A242" s="5"/>
-      <c r="B242" s="5"/>
+      <c r="A242" s="6"/>
+      <c r="B242" s="6"/>
       <c r="C242" s="6"/>
       <c r="D242" s="6"/>
       <c r="E242" s="6"/>
-      <c r="F242" s="7"/>
+      <c r="F242" s="6"/>
       <c r="G242" s="6"/>
       <c r="H242" s="6"/>
       <c r="I242" s="6"/>
     </row>
     <row r="243" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A243" s="5"/>
-      <c r="B243" s="5"/>
+      <c r="A243" s="6"/>
+      <c r="B243" s="6"/>
       <c r="C243" s="6"/>
       <c r="D243" s="6"/>
       <c r="E243" s="6"/>
-      <c r="F243" s="7"/>
+      <c r="F243" s="6"/>
       <c r="G243" s="6"/>
       <c r="H243" s="6"/>
       <c r="I243" s="6"/>
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A244" s="5"/>
-      <c r="B244" s="5"/>
+      <c r="A244" s="6"/>
+      <c r="B244" s="6"/>
       <c r="C244" s="6"/>
       <c r="D244" s="6"/>
       <c r="E244" s="6"/>
-      <c r="F244" s="7"/>
+      <c r="F244" s="6"/>
       <c r="G244" s="6"/>
       <c r="H244" s="6"/>
       <c r="I244" s="6"/>
     </row>
     <row r="245" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A245" s="5"/>
-      <c r="B245" s="5"/>
+      <c r="A245" s="6"/>
+      <c r="B245" s="6"/>
       <c r="C245" s="6"/>
       <c r="D245" s="6"/>
       <c r="E245" s="6"/>
-      <c r="F245" s="7"/>
+      <c r="F245" s="6"/>
       <c r="G245" s="6"/>
       <c r="H245" s="6"/>
       <c r="I245" s="6"/>
     </row>
     <row r="246" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A246" s="5"/>
-      <c r="B246" s="5"/>
+      <c r="A246" s="6"/>
+      <c r="B246" s="6"/>
       <c r="C246" s="6"/>
       <c r="D246" s="6"/>
       <c r="E246" s="6"/>
-      <c r="F246" s="7"/>
+      <c r="F246" s="6"/>
       <c r="G246" s="6"/>
       <c r="H246" s="6"/>
       <c r="I246" s="6"/>
     </row>
     <row r="247" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A247" s="5"/>
-      <c r="B247" s="5"/>
+      <c r="A247" s="6"/>
+      <c r="B247" s="6"/>
       <c r="C247" s="6"/>
       <c r="D247" s="6"/>
       <c r="E247" s="6"/>
-      <c r="F247" s="7"/>
+      <c r="F247" s="6"/>
       <c r="G247" s="6"/>
       <c r="H247" s="6"/>
       <c r="I247" s="6"/>
     </row>
     <row r="248" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A248" s="5"/>
-      <c r="B248" s="5"/>
+      <c r="A248" s="6"/>
+      <c r="B248" s="6"/>
       <c r="C248" s="6"/>
       <c r="D248" s="6"/>
       <c r="E248" s="6"/>
-      <c r="F248" s="7"/>
+      <c r="F248" s="6"/>
       <c r="G248" s="6"/>
       <c r="H248" s="6"/>
       <c r="I248" s="6"/>
     </row>
     <row r="249" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A249" s="5"/>
-      <c r="B249" s="5"/>
+      <c r="A249" s="6"/>
+      <c r="B249" s="6"/>
       <c r="C249" s="6"/>
       <c r="D249" s="6"/>
       <c r="E249" s="6"/>
-      <c r="F249" s="7"/>
+      <c r="F249" s="6"/>
       <c r="G249" s="6"/>
       <c r="H249" s="6"/>
       <c r="I249" s="6"/>
     </row>
     <row r="250" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A250" s="5"/>
-      <c r="B250" s="5"/>
+      <c r="A250" s="6"/>
+      <c r="B250" s="6"/>
       <c r="C250" s="6"/>
       <c r="D250" s="6"/>
       <c r="E250" s="6"/>
-      <c r="F250" s="7"/>
+      <c r="F250" s="6"/>
       <c r="G250" s="6"/>
       <c r="H250" s="6"/>
       <c r="I250" s="6"/>
     </row>
     <row r="251" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A251" s="5"/>
-      <c r="B251" s="5"/>
+      <c r="A251" s="6"/>
+      <c r="B251" s="6"/>
       <c r="C251" s="6"/>
       <c r="D251" s="6"/>
       <c r="E251" s="6"/>
-      <c r="F251" s="7"/>
+      <c r="F251" s="6"/>
       <c r="G251" s="6"/>
       <c r="H251" s="6"/>
       <c r="I251" s="6"/>
     </row>
     <row r="252" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A252" s="5"/>
-      <c r="B252" s="5"/>
+      <c r="A252" s="6"/>
+      <c r="B252" s="6"/>
       <c r="C252" s="6"/>
       <c r="D252" s="6"/>
       <c r="E252" s="6"/>
-      <c r="F252" s="7"/>
+      <c r="F252" s="6"/>
       <c r="G252" s="6"/>
       <c r="H252" s="6"/>
       <c r="I252" s="6"/>
     </row>
     <row r="253" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A253" s="5"/>
-      <c r="B253" s="5"/>
+      <c r="A253" s="6"/>
+      <c r="B253" s="6"/>
       <c r="C253" s="6"/>
       <c r="D253" s="6"/>
       <c r="E253" s="6"/>
-      <c r="F253" s="7"/>
+      <c r="F253" s="6"/>
       <c r="G253" s="6"/>
       <c r="H253" s="6"/>
       <c r="I253" s="6"/>
     </row>
     <row r="254" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A254" s="5"/>
-      <c r="B254" s="5"/>
+      <c r="A254" s="6"/>
+      <c r="B254" s="6"/>
       <c r="C254" s="6"/>
       <c r="D254" s="6"/>
       <c r="E254" s="6"/>
-      <c r="F254" s="7"/>
+      <c r="F254" s="6"/>
       <c r="G254" s="6"/>
       <c r="H254" s="6"/>
       <c r="I254" s="6"/>
     </row>
     <row r="255" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A255" s="5"/>
-      <c r="B255" s="5"/>
+      <c r="A255" s="6"/>
+      <c r="B255" s="6"/>
       <c r="C255" s="6"/>
       <c r="D255" s="6"/>
       <c r="E255" s="6"/>
-      <c r="F255" s="7"/>
+      <c r="F255" s="6"/>
       <c r="G255" s="6"/>
       <c r="H255" s="6"/>
       <c r="I255" s="6"/>
     </row>
     <row r="256" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A256" s="5"/>
-      <c r="B256" s="5"/>
+      <c r="A256" s="6"/>
+      <c r="B256" s="6"/>
       <c r="C256" s="6"/>
       <c r="D256" s="6"/>
       <c r="E256" s="6"/>
-      <c r="F256" s="7"/>
+      <c r="F256" s="6"/>
       <c r="G256" s="6"/>
       <c r="H256" s="6"/>
       <c r="I256" s="6"/>
     </row>
     <row r="257" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A257" s="5"/>
-      <c r="B257" s="5"/>
+      <c r="A257" s="6"/>
+      <c r="B257" s="6"/>
       <c r="C257" s="6"/>
       <c r="D257" s="6"/>
       <c r="E257" s="6"/>
-      <c r="F257" s="7"/>
+      <c r="F257" s="6"/>
       <c r="G257" s="6"/>
       <c r="H257" s="6"/>
       <c r="I257" s="6"/>
     </row>
     <row r="258" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A258" s="5"/>
-      <c r="B258" s="5"/>
+      <c r="A258" s="6"/>
+      <c r="B258" s="6"/>
       <c r="C258" s="6"/>
       <c r="D258" s="6"/>
       <c r="E258" s="6"/>
-      <c r="F258" s="7"/>
+      <c r="F258" s="6"/>
       <c r="G258" s="6"/>
       <c r="H258" s="6"/>
       <c r="I258" s="6"/>
     </row>
     <row r="259" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A259" s="5"/>
-      <c r="B259" s="5"/>
+      <c r="A259" s="6"/>
+      <c r="B259" s="6"/>
       <c r="C259" s="6"/>
       <c r="D259" s="6"/>
       <c r="E259" s="6"/>
-      <c r="F259" s="7"/>
+      <c r="F259" s="6"/>
       <c r="G259" s="6"/>
       <c r="H259" s="6"/>
       <c r="I259" s="6"/>
     </row>
     <row r="260" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A260" s="5"/>
-      <c r="B260" s="5"/>
+      <c r="A260" s="6"/>
+      <c r="B260" s="6"/>
       <c r="C260" s="6"/>
       <c r="D260" s="6"/>
       <c r="E260" s="6"/>
-      <c r="F260" s="7"/>
+      <c r="F260" s="6"/>
       <c r="G260" s="6"/>
       <c r="H260" s="6"/>
       <c r="I260" s="6"/>
     </row>
     <row r="261" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A261" s="5"/>
-      <c r="B261" s="5"/>
+      <c r="A261" s="6"/>
+      <c r="B261" s="6"/>
       <c r="C261" s="6"/>
       <c r="D261" s="6"/>
       <c r="E261" s="6"/>
-      <c r="F261" s="7"/>
+      <c r="F261" s="6"/>
       <c r="G261" s="6"/>
       <c r="H261" s="6"/>
       <c r="I261" s="6"/>
     </row>
     <row r="262" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A262" s="5"/>
-      <c r="B262" s="5"/>
+      <c r="A262" s="6"/>
+      <c r="B262" s="6"/>
       <c r="C262" s="6"/>
       <c r="D262" s="6"/>
       <c r="E262" s="6"/>
-      <c r="F262" s="7"/>
+      <c r="F262" s="6"/>
       <c r="G262" s="6"/>
       <c r="H262" s="6"/>
       <c r="I262" s="6"/>
     </row>
     <row r="263" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A263" s="5"/>
-      <c r="B263" s="5"/>
+      <c r="A263" s="6"/>
+      <c r="B263" s="6"/>
       <c r="C263" s="6"/>
       <c r="D263" s="6"/>
       <c r="E263" s="6"/>
-      <c r="F263" s="7"/>
+      <c r="F263" s="6"/>
       <c r="G263" s="6"/>
       <c r="H263" s="6"/>
       <c r="I263" s="6"/>
     </row>
     <row r="264" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A264" s="5"/>
-      <c r="B264" s="5"/>
+      <c r="A264" s="6"/>
+      <c r="B264" s="6"/>
       <c r="C264" s="6"/>
       <c r="D264" s="6"/>
       <c r="E264" s="6"/>
-      <c r="F264" s="7"/>
+      <c r="F264" s="6"/>
       <c r="G264" s="6"/>
       <c r="H264" s="6"/>
       <c r="I264" s="6"/>
     </row>
     <row r="265" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A265" s="5"/>
-      <c r="B265" s="5"/>
+      <c r="A265" s="6"/>
+      <c r="B265" s="6"/>
       <c r="C265" s="6"/>
       <c r="D265" s="6"/>
       <c r="E265" s="6"/>
-      <c r="F265" s="7"/>
+      <c r="F265" s="6"/>
       <c r="G265" s="6"/>
       <c r="H265" s="6"/>
       <c r="I265" s="6"/>
     </row>
     <row r="266" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A266" s="5"/>
-      <c r="B266" s="5"/>
+      <c r="A266" s="6"/>
+      <c r="B266" s="6"/>
       <c r="C266" s="6"/>
       <c r="D266" s="6"/>
       <c r="E266" s="6"/>
-      <c r="F266" s="7"/>
+      <c r="F266" s="6"/>
       <c r="G266" s="6"/>
       <c r="H266" s="6"/>
       <c r="I266" s="6"/>
     </row>
     <row r="267" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A267" s="5"/>
-      <c r="B267" s="5"/>
+      <c r="A267" s="6"/>
+      <c r="B267" s="6"/>
       <c r="C267" s="6"/>
       <c r="D267" s="6"/>
       <c r="E267" s="6"/>
-      <c r="F267" s="7"/>
+      <c r="F267" s="6"/>
       <c r="G267" s="6"/>
       <c r="H267" s="6"/>
       <c r="I267" s="6"/>
     </row>
     <row r="268" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A268" s="5"/>
-      <c r="B268" s="5"/>
+      <c r="A268" s="6"/>
+      <c r="B268" s="6"/>
       <c r="C268" s="6"/>
       <c r="D268" s="6"/>
       <c r="E268" s="6"/>
-      <c r="F268" s="7"/>
+      <c r="F268" s="6"/>
       <c r="G268" s="6"/>
       <c r="H268" s="6"/>
       <c r="I268" s="6"/>
     </row>
     <row r="269" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A269" s="5"/>
-      <c r="B269" s="5"/>
+      <c r="A269" s="6"/>
+      <c r="B269" s="6"/>
       <c r="C269" s="6"/>
       <c r="D269" s="6"/>
       <c r="E269" s="6"/>
-      <c r="F269" s="7"/>
+      <c r="F269" s="6"/>
       <c r="G269" s="6"/>
       <c r="H269" s="6"/>
       <c r="I269" s="6"/>
     </row>
     <row r="270" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A270" s="5"/>
-      <c r="B270" s="5"/>
+      <c r="A270" s="6"/>
+      <c r="B270" s="6"/>
       <c r="C270" s="6"/>
       <c r="D270" s="6"/>
       <c r="E270" s="6"/>
-      <c r="F270" s="7"/>
+      <c r="F270" s="6"/>
       <c r="G270" s="6"/>
       <c r="H270" s="6"/>
       <c r="I270" s="6"/>
     </row>
     <row r="271" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A271" s="5"/>
-      <c r="B271" s="5"/>
+      <c r="A271" s="6"/>
+      <c r="B271" s="6"/>
       <c r="C271" s="6"/>
       <c r="D271" s="6"/>
       <c r="E271" s="6"/>
-      <c r="F271" s="7"/>
+      <c r="F271" s="6"/>
       <c r="G271" s="6"/>
       <c r="H271" s="6"/>
       <c r="I271" s="6"/>
     </row>
     <row r="272" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A272" s="5"/>
-      <c r="B272" s="5"/>
+      <c r="A272" s="6"/>
+      <c r="B272" s="6"/>
       <c r="C272" s="6"/>
       <c r="D272" s="6"/>
       <c r="E272" s="6"/>
-      <c r="F272" s="7"/>
+      <c r="F272" s="6"/>
       <c r="G272" s="6"/>
       <c r="H272" s="6"/>
       <c r="I272" s="6"/>
     </row>
     <row r="273" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A273" s="5"/>
-      <c r="B273" s="5"/>
+      <c r="A273" s="6"/>
+      <c r="B273" s="6"/>
       <c r="C273" s="6"/>
       <c r="D273" s="6"/>
       <c r="E273" s="6"/>
-      <c r="F273" s="7"/>
+      <c r="F273" s="6"/>
       <c r="G273" s="6"/>
       <c r="H273" s="6"/>
       <c r="I273" s="6"/>
     </row>
     <row r="274" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A274" s="5"/>
-      <c r="B274" s="5"/>
+      <c r="A274" s="6"/>
+      <c r="B274" s="6"/>
       <c r="C274" s="6"/>
       <c r="D274" s="6"/>
       <c r="E274" s="6"/>
-      <c r="F274" s="7"/>
+      <c r="F274" s="6"/>
       <c r="G274" s="6"/>
       <c r="H274" s="6"/>
       <c r="I274" s="6"/>
     </row>
     <row r="275" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A275" s="5"/>
-      <c r="B275" s="5"/>
+      <c r="A275" s="6"/>
+      <c r="B275" s="6"/>
       <c r="C275" s="6"/>
       <c r="D275" s="6"/>
       <c r="E275" s="6"/>
-      <c r="F275" s="7"/>
+      <c r="F275" s="6"/>
       <c r="G275" s="6"/>
       <c r="H275" s="6"/>
       <c r="I275" s="6"/>
     </row>
     <row r="276" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A276" s="5"/>
-      <c r="B276" s="5"/>
+      <c r="A276" s="6"/>
+      <c r="B276" s="6"/>
       <c r="C276" s="6"/>
       <c r="D276" s="6"/>
       <c r="E276" s="6"/>
-      <c r="F276" s="7"/>
+      <c r="F276" s="6"/>
       <c r="G276" s="6"/>
       <c r="H276" s="6"/>
       <c r="I276" s="6"/>
     </row>
     <row r="277" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A277" s="5"/>
-      <c r="B277" s="5"/>
+      <c r="A277" s="6"/>
+      <c r="B277" s="6"/>
       <c r="C277" s="6"/>
       <c r="D277" s="6"/>
       <c r="E277" s="6"/>
-      <c r="F277" s="7"/>
+      <c r="F277" s="6"/>
       <c r="G277" s="6"/>
       <c r="H277" s="6"/>
       <c r="I277" s="6"/>
     </row>
     <row r="278" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A278" s="5"/>
-      <c r="B278" s="5"/>
+      <c r="A278" s="6"/>
+      <c r="B278" s="6"/>
       <c r="C278" s="6"/>
       <c r="D278" s="6"/>
       <c r="E278" s="6"/>
-      <c r="F278" s="7"/>
+      <c r="F278" s="6"/>
       <c r="G278" s="6"/>
       <c r="H278" s="6"/>
       <c r="I278" s="6"/>
     </row>
     <row r="279" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A279" s="5"/>
-      <c r="B279" s="5"/>
+      <c r="A279" s="6"/>
+      <c r="B279" s="6"/>
       <c r="C279" s="6"/>
       <c r="D279" s="6"/>
       <c r="E279" s="6"/>
-      <c r="F279" s="7"/>
+      <c r="F279" s="6"/>
       <c r="G279" s="6"/>
       <c r="H279" s="6"/>
       <c r="I279" s="6"/>
     </row>
     <row r="280" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A280" s="5"/>
-      <c r="B280" s="5"/>
+      <c r="A280" s="6"/>
+      <c r="B280" s="6"/>
       <c r="C280" s="6"/>
       <c r="D280" s="6"/>
       <c r="E280" s="6"/>
-      <c r="F280" s="7"/>
+      <c r="F280" s="6"/>
       <c r="G280" s="6"/>
       <c r="H280" s="6"/>
       <c r="I280" s="6"/>
     </row>
     <row r="281" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A281" s="5"/>
-      <c r="B281" s="5"/>
+      <c r="A281" s="6"/>
+      <c r="B281" s="6"/>
       <c r="C281" s="6"/>
       <c r="D281" s="6"/>
       <c r="E281" s="6"/>
-      <c r="F281" s="7"/>
+      <c r="F281" s="6"/>
       <c r="G281" s="6"/>
       <c r="H281" s="6"/>
       <c r="I281" s="6"/>
     </row>
     <row r="282" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A282" s="5"/>
-      <c r="B282" s="5"/>
+      <c r="A282" s="6"/>
+      <c r="B282" s="6"/>
       <c r="C282" s="6"/>
       <c r="D282" s="6"/>
       <c r="E282" s="6"/>
-      <c r="F282" s="7"/>
+      <c r="F282" s="6"/>
       <c r="G282" s="6"/>
       <c r="H282" s="6"/>
       <c r="I282" s="6"/>
     </row>
     <row r="283" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A283" s="5"/>
-      <c r="B283" s="5"/>
+      <c r="A283" s="6"/>
+      <c r="B283" s="6"/>
       <c r="C283" s="6"/>
       <c r="D283" s="6"/>
       <c r="E283" s="6"/>
-      <c r="F283" s="7"/>
+      <c r="F283" s="6"/>
       <c r="G283" s="6"/>
       <c r="H283" s="6"/>
       <c r="I283" s="6"/>
     </row>
     <row r="284" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A284" s="5"/>
-      <c r="B284" s="5"/>
+      <c r="A284" s="6"/>
+      <c r="B284" s="6"/>
       <c r="C284" s="6"/>
       <c r="D284" s="6"/>
       <c r="E284" s="6"/>
-      <c r="F284" s="7"/>
+      <c r="F284" s="6"/>
       <c r="G284" s="6"/>
       <c r="H284" s="6"/>
       <c r="I284" s="6"/>
     </row>
     <row r="285" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A285" s="5"/>
-      <c r="B285" s="5"/>
+      <c r="A285" s="6"/>
+      <c r="B285" s="6"/>
       <c r="C285" s="6"/>
       <c r="D285" s="6"/>
       <c r="E285" s="6"/>
-      <c r="F285" s="7"/>
+      <c r="F285" s="6"/>
       <c r="G285" s="6"/>
       <c r="H285" s="6"/>
       <c r="I285" s="6"/>
     </row>
     <row r="286" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A286" s="5"/>
-      <c r="B286" s="5"/>
+      <c r="A286" s="6"/>
+      <c r="B286" s="6"/>
       <c r="C286" s="6"/>
       <c r="D286" s="6"/>
       <c r="E286" s="6"/>
-      <c r="F286" s="7"/>
+      <c r="F286" s="6"/>
       <c r="G286" s="6"/>
       <c r="H286" s="6"/>
       <c r="I286" s="6"/>
     </row>
     <row r="287" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A287" s="5"/>
-      <c r="B287" s="5"/>
+      <c r="A287" s="6"/>
+      <c r="B287" s="6"/>
       <c r="C287" s="6"/>
       <c r="D287" s="6"/>
       <c r="E287" s="6"/>
-      <c r="F287" s="7"/>
+      <c r="F287" s="6"/>
       <c r="G287" s="6"/>
       <c r="H287" s="6"/>
       <c r="I287" s="6"/>
     </row>
     <row r="288" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A288" s="5"/>
-      <c r="B288" s="5"/>
+      <c r="A288" s="6"/>
+      <c r="B288" s="6"/>
       <c r="C288" s="6"/>
       <c r="D288" s="6"/>
       <c r="E288" s="6"/>
-      <c r="F288" s="7"/>
+      <c r="F288" s="6"/>
       <c r="G288" s="6"/>
       <c r="H288" s="6"/>
       <c r="I288" s="6"/>
     </row>
     <row r="289" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A289" s="5"/>
-      <c r="B289" s="5"/>
+      <c r="A289" s="6"/>
+      <c r="B289" s="6"/>
       <c r="C289" s="6"/>
       <c r="D289" s="6"/>
       <c r="E289" s="6"/>
-      <c r="F289" s="7"/>
+      <c r="F289" s="6"/>
       <c r="G289" s="6"/>
       <c r="H289" s="6"/>
       <c r="I289" s="6"/>
     </row>
     <row r="290" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A290" s="5"/>
-      <c r="B290" s="5"/>
+      <c r="A290" s="6"/>
+      <c r="B290" s="6"/>
       <c r="C290" s="6"/>
       <c r="D290" s="6"/>
       <c r="E290" s="6"/>
-      <c r="F290" s="7"/>
+      <c r="F290" s="6"/>
       <c r="G290" s="6"/>
       <c r="H290" s="6"/>
       <c r="I290" s="6"/>
     </row>
     <row r="291" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A291" s="5"/>
-      <c r="B291" s="5"/>
+      <c r="A291" s="6"/>
+      <c r="B291" s="6"/>
       <c r="C291" s="6"/>
       <c r="D291" s="6"/>
       <c r="E291" s="6"/>
-      <c r="F291" s="7"/>
+      <c r="F291" s="6"/>
       <c r="G291" s="6"/>
       <c r="H291" s="6"/>
       <c r="I291" s="6"/>
     </row>
     <row r="292" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A292" s="5"/>
-      <c r="B292" s="5"/>
+      <c r="A292" s="6"/>
+      <c r="B292" s="6"/>
       <c r="C292" s="6"/>
       <c r="D292" s="6"/>
       <c r="E292" s="6"/>
-      <c r="F292" s="7"/>
+      <c r="F292" s="6"/>
       <c r="G292" s="6"/>
       <c r="H292" s="6"/>
       <c r="I292" s="6"/>
     </row>
     <row r="293" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A293" s="5"/>
-      <c r="B293" s="5"/>
+      <c r="A293" s="6"/>
+      <c r="B293" s="6"/>
       <c r="C293" s="6"/>
       <c r="D293" s="6"/>
       <c r="E293" s="6"/>
-      <c r="F293" s="7"/>
+      <c r="F293" s="6"/>
       <c r="G293" s="6"/>
       <c r="H293" s="6"/>
       <c r="I293" s="6"/>
     </row>
     <row r="294" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A294" s="5"/>
-      <c r="B294" s="5"/>
+      <c r="A294" s="6"/>
+      <c r="B294" s="6"/>
       <c r="C294" s="6"/>
       <c r="D294" s="6"/>
       <c r="E294" s="6"/>
-      <c r="F294" s="7"/>
+      <c r="F294" s="6"/>
       <c r="G294" s="6"/>
       <c r="H294" s="6"/>
       <c r="I294" s="6"/>
     </row>
     <row r="295" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A295" s="5"/>
-      <c r="B295" s="5"/>
+      <c r="A295" s="6"/>
+      <c r="B295" s="6"/>
       <c r="C295" s="6"/>
       <c r="D295" s="6"/>
       <c r="E295" s="6"/>
-      <c r="F295" s="7"/>
+      <c r="F295" s="6"/>
       <c r="G295" s="6"/>
       <c r="H295" s="6"/>
       <c r="I295" s="6"/>
@@ -4363,13 +4419,24 @@
       <c r="H302" s="6"/>
       <c r="I302" s="6"/>
     </row>
+    <row r="303" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A303" s="5"/>
+      <c r="B303" s="5"/>
+      <c r="C303" s="6"/>
+      <c r="D303" s="6"/>
+      <c r="E303" s="6"/>
+      <c r="F303" s="7"/>
+      <c r="G303" s="6"/>
+      <c r="H303" s="6"/>
+      <c r="I303" s="6"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I302" xr:uid="{00000000-0009-0000-0000-000001000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I302">
-      <sortCondition ref="B1:B302"/>
+  <autoFilter ref="A1:I303" xr:uid="{00000000-0009-0000-0000-000001000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I303">
+      <sortCondition ref="B1:B303"/>
     </sortState>
   </autoFilter>
-  <conditionalFormatting sqref="E23:E302 E2:E20">
+  <conditionalFormatting sqref="E2:E303">
     <cfRule type="expression" dxfId="6" priority="1">
       <formula>$E2="Competición FPCV"</formula>
     </cfRule>
@@ -4393,16 +4460,16 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" errorTitle="Valor no válido" error="Elige una categoría de la lista" sqref="E2:E20 E23:E302" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" errorTitle="Valor no válido" error="Elige una categoría de la lista" sqref="E2:E21 E24:E303" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Competición FPCV,Campeonato de España,Competición Internacional,Trofeo Club,Curso,Reunión,Prueba de Acceso"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" errorTitle="Valor no válido" error="Huecos: pon 0, 1 o 2" sqref="F2:F20 F23:F302" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" errorTitle="Valor no válido" error="Huecos: pon 0, 1 o 2" sqref="F2:F21 F24:F303" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"0,1,2"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" errorTitle="Valor no válido" error="Elige Mañana, Tarde o Todo el día" sqref="G2:I20 G23:I302" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" errorTitle="Valor no válido" error="Elige Mañana, Tarde o Todo el día" sqref="G2:I21 G24:I303 H22" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"Mañana,Tarde,Todo el día"</formula1>
     </dataValidation>
-    <dataValidation type="date" operator="greaterThan" allowBlank="1" errorTitle="Fecha" error="Escribe una fecha, por ejemplo 17/10/2026" sqref="A2:B20 A23:B302" xr:uid="{00000000-0002-0000-0100-000003000000}">
+    <dataValidation type="date" operator="greaterThan" allowBlank="1" errorTitle="Fecha" error="Escribe una fecha, por ejemplo 17/10/2026" sqref="A24:B303 A2:B21" xr:uid="{00000000-0002-0000-0100-000003000000}">
       <formula1>36526</formula1>
     </dataValidation>
   </dataValidations>

--- a/calendario-fpcv-eventos.xlsx
+++ b/calendario-fpcv-eventos.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5bbe44e6a3b5fd34/Federación/EVENTOS AÑO 2027/Calendario/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5bbe44e6a3b5fd34/Federación/EVENTOS AÑO 2026/Trofeos Clubes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="13_ncr:1_{BBF296C7-BF25-459F-891A-95BF6B966FB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D3342B2D-270A-4FE0-BC5B-3E767710CEF9}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{BBF296C7-BF25-459F-891A-95BF6B966FB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B3DDE2E-28E6-4B36-BE94-9136A1EC5550}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="70">
   <si>
     <t>Inicio</t>
   </si>
@@ -231,6 +231,9 @@
   </si>
   <si>
     <t>Castelló de la Plana</t>
+  </si>
+  <si>
+    <t>Elecciones Generales</t>
   </si>
 </sst>
 </file>
@@ -391,6 +394,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1276,16 +1283,12 @@
         <v>46355</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>11</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
       <c r="F20" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G20" s="6"/>
       <c r="H20" s="6" t="s">

--- a/calendario-fpcv-eventos.xlsx
+++ b/calendario-fpcv-eventos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5bbe44e6a3b5fd34/Federación/EVENTOS AÑO 2026/Trofeos Clubes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{BBF296C7-BF25-459F-891A-95BF6B966FB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B3DDE2E-28E6-4B36-BE94-9136A1EC5550}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="13_ncr:1_{BBF296C7-BF25-459F-891A-95BF6B966FB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF690139-F801-4E98-9BC8-F43370FD9603}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="70">
   <si>
     <t>Inicio</t>
   </si>
@@ -1286,7 +1286,9 @@
         <v>69</v>
       </c>
       <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
+      <c r="E20" s="6" t="s">
+        <v>28</v>
+      </c>
       <c r="F20" s="7">
         <v>2</v>
       </c>

--- a/calendario-fpcv-eventos.xlsx
+++ b/calendario-fpcv-eventos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5bbe44e6a3b5fd34/Federación/EVENTOS AÑO 2026/Trofeos Clubes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="13_ncr:1_{BBF296C7-BF25-459F-891A-95BF6B966FB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF690139-F801-4E98-9BC8-F43370FD9603}"/>
+  <xr:revisionPtr revIDLastSave="29" documentId="13_ncr:1_{BBF296C7-BF25-459F-891A-95BF6B966FB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EBFDF39A-C782-4B2E-B4A8-5BEBDE21420F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -995,10 +995,10 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="B8" s="5">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>18</v>

--- a/calendario-fpcv-eventos.xlsx
+++ b/calendario-fpcv-eventos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5bbe44e6a3b5fd34/Federación/EVENTOS AÑO 2026/Trofeos Clubes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="29" documentId="13_ncr:1_{BBF296C7-BF25-459F-891A-95BF6B966FB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EBFDF39A-C782-4B2E-B4A8-5BEBDE21420F}"/>
+  <xr:revisionPtr revIDLastSave="42" documentId="13_ncr:1_{BBF296C7-BF25-459F-891A-95BF6B966FB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CFBE9F20-055F-4236-A73C-B16B0C140DA2}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="72">
   <si>
     <t>Inicio</t>
   </si>
@@ -56,9 +56,6 @@
     <t>Prueba Danza y Libre</t>
   </si>
   <si>
-    <t>L'Alcudia</t>
-  </si>
-  <si>
     <t>Trofeo Club</t>
   </si>
   <si>
@@ -203,9 +200,6 @@
     <t>Trofeo Iniciación Rafelbunyol</t>
   </si>
   <si>
-    <t>Trofeo Iniciación Llombai o Llocnou</t>
-  </si>
-  <si>
     <t>Trofeo Iniciación 8Rodes Barxeta</t>
   </si>
   <si>
@@ -234,6 +228,18 @@
   </si>
   <si>
     <t>Elecciones Generales</t>
+  </si>
+  <si>
+    <t>Castelló de la Ribera</t>
+  </si>
+  <si>
+    <t>Trofeo Iniciación Llombai</t>
+  </si>
+  <si>
+    <t>Llombai</t>
+  </si>
+  <si>
+    <t>L'Alcudia de Crespins</t>
   </si>
 </sst>
 </file>
@@ -694,7 +700,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B1" s="2"/>
     </row>
@@ -704,10 +710,10 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -715,7 +721,7 @@
         <v>0</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -723,7 +729,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -731,7 +737,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -739,7 +745,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
@@ -747,7 +753,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
@@ -755,15 +761,15 @@
         <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
@@ -772,34 +778,34 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>47</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -860,10 +866,10 @@
         <v>9</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>10</v>
+        <v>71</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F2" s="7">
         <v>0</v>
@@ -880,19 +886,21 @@
         <v>46313</v>
       </c>
       <c r="C3" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>62</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>64</v>
       </c>
       <c r="F3" s="7">
         <v>0</v>
       </c>
       <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
+      <c r="H3" s="6" t="s">
+        <v>48</v>
+      </c>
       <c r="I3" s="6"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
@@ -903,20 +911,20 @@
         <v>46312</v>
       </c>
       <c r="C4" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="E4" s="6" t="s">
         <v>16</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>17</v>
       </c>
       <c r="F4" s="7">
         <v>1</v>
       </c>
       <c r="G4" s="6"/>
       <c r="H4" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I4" s="6"/>
     </row>
@@ -928,19 +936,21 @@
         <v>46313</v>
       </c>
       <c r="C5" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="6" t="s">
-        <v>13</v>
-      </c>
       <c r="E5" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F5" s="7">
         <v>0</v>
       </c>
       <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
+      <c r="H5" s="6" t="s">
+        <v>48</v>
+      </c>
       <c r="I5" s="6"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
@@ -951,19 +961,21 @@
         <v>46319</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F6" s="7">
         <v>0</v>
       </c>
       <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
+      <c r="H6" s="6" t="s">
+        <v>48</v>
+      </c>
       <c r="I6" s="6"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -974,23 +986,23 @@
         <v>46313</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F7" s="7">
         <v>1</v>
       </c>
       <c r="G7" s="6"/>
       <c r="H7" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="I7" s="6" t="s">
         <v>49</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
@@ -1001,17 +1013,21 @@
         <v>46320</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" s="6"/>
+        <v>17</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>68</v>
+      </c>
       <c r="E8" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F8" s="7">
         <v>0</v>
       </c>
       <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
+      <c r="H8" s="6" t="s">
+        <v>48</v>
+      </c>
       <c r="I8" s="6"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
@@ -1022,20 +1038,20 @@
         <v>46319</v>
       </c>
       <c r="C9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="E9" s="6" t="s">
         <v>20</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>21</v>
       </c>
       <c r="F9" s="7">
         <v>2</v>
       </c>
       <c r="G9" s="6"/>
       <c r="H9" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I9" s="6"/>
     </row>
@@ -1047,20 +1063,20 @@
         <v>46333</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F10" s="7">
         <v>1</v>
       </c>
       <c r="G10" s="6"/>
       <c r="H10" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I10" s="6"/>
     </row>
@@ -1072,18 +1088,20 @@
         <v>46333</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="D11" s="6"/>
+        <v>69</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>70</v>
+      </c>
       <c r="E11" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F11" s="7">
         <v>1</v>
       </c>
       <c r="G11" s="6"/>
       <c r="H11" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I11" s="6"/>
     </row>
@@ -1095,17 +1113,21 @@
         <v>46334</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" s="6"/>
+        <v>21</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>55</v>
+      </c>
       <c r="E12" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F12" s="7">
         <v>0</v>
       </c>
       <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
+      <c r="H12" s="6" t="s">
+        <v>48</v>
+      </c>
       <c r="I12" s="6"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
@@ -1116,19 +1138,19 @@
         <v>46339</v>
       </c>
       <c r="C13" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="D13" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="D13" s="6" t="s">
-        <v>53</v>
-      </c>
       <c r="E13" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F13" s="7">
         <v>1</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H13" s="6"/>
       <c r="I13" s="6"/>
@@ -1141,20 +1163,20 @@
         <v>46340</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D14" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" s="6" t="s">
         <v>13</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>14</v>
       </c>
       <c r="F14" s="7">
         <v>2</v>
       </c>
       <c r="G14" s="6"/>
       <c r="H14" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I14" s="6"/>
     </row>
@@ -1166,20 +1188,20 @@
         <v>46347</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F15" s="7">
         <v>1</v>
       </c>
       <c r="G15" s="6"/>
       <c r="H15" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I15" s="6"/>
     </row>
@@ -1191,20 +1213,20 @@
         <v>46347</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F16" s="7">
         <v>1</v>
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I16" s="6"/>
     </row>
@@ -1216,17 +1238,19 @@
         <v>46348</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D17" s="6"/>
       <c r="E17" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F17" s="7">
         <v>0</v>
       </c>
       <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
+      <c r="H17" s="6" t="s">
+        <v>48</v>
+      </c>
       <c r="I17" s="6"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
@@ -1237,20 +1261,20 @@
         <v>46354</v>
       </c>
       <c r="C18" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D18" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="E18" s="6" t="s">
         <v>27</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>28</v>
       </c>
       <c r="F18" s="7">
         <v>2</v>
       </c>
       <c r="G18" s="6"/>
       <c r="H18" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I18" s="6"/>
     </row>
@@ -1262,17 +1286,19 @@
         <v>46355</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D19" s="6"/>
       <c r="E19" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F19" s="7">
         <v>0</v>
       </c>
       <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
+      <c r="H19" s="6" t="s">
+        <v>48</v>
+      </c>
       <c r="I19" s="6"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
@@ -1283,18 +1309,18 @@
         <v>46355</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D20" s="6"/>
       <c r="E20" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F20" s="7">
         <v>2</v>
       </c>
       <c r="G20" s="6"/>
       <c r="H20" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I20" s="6"/>
     </row>
@@ -1306,17 +1332,19 @@
         <v>46368</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D21" s="6"/>
       <c r="E21" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F21" s="7">
         <v>1</v>
       </c>
       <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
+      <c r="H21" s="6" t="s">
+        <v>48</v>
+      </c>
       <c r="I21" s="6"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
@@ -1327,20 +1355,20 @@
         <v>46397</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F22" s="7">
         <v>1</v>
       </c>
       <c r="G22" s="6"/>
       <c r="H22" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I22" s="6"/>
     </row>

--- a/calendario-fpcv-eventos.xlsx
+++ b/calendario-fpcv-eventos.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5bbe44e6a3b5fd34/Federación/EVENTOS AÑO 2026/Trofeos Clubes/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bea Pallero\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="42" documentId="13_ncr:1_{BBF296C7-BF25-459F-891A-95BF6B966FB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CFBE9F20-055F-4236-A73C-B16B0C140DA2}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D398B8E-8F88-483F-8CEF-2E75185AB50A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,14 +17,14 @@
     <sheet name="Eventos" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Eventos!$A$1:$I$303</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Eventos!$A$1:$I$302</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="69">
   <si>
     <t>Inicio</t>
   </si>
@@ -53,9 +53,6 @@
     <t>Horario domingo</t>
   </si>
   <si>
-    <t>Prueba Danza y Libre</t>
-  </si>
-  <si>
     <t>Trofeo Club</t>
   </si>
   <si>
@@ -68,12 +65,6 @@
     <t>Competición FPCV</t>
   </si>
   <si>
-    <t>3ª Prueba Acceso Categoría Territorial</t>
-  </si>
-  <si>
-    <t>Quart</t>
-  </si>
-  <si>
     <t>Prueba de Acceso</t>
   </si>
   <si>
@@ -134,12 +125,18 @@
     <t>Localidad o pabellón. Puede quedar vacío.</t>
   </si>
   <si>
-    <t>Elige de la lista. Decide el color y el botón de filtro: Competición FPCV, Campeonato de España, Competición Internacional, Trofeo Club, Curso, Reunión y Prueba de Acceso.</t>
+    <t>Elige de la lista. Decide el color y el botón de filtro: Competición FPCV, Campeonato de España, Competición Internacional, Trofeo Club, Curso, Reunión Prueba de Acceso y Día festivo.</t>
   </si>
   <si>
     <t>0 = no ocupa hueco. 1 = ocupa un hueco. 2 = ocupa los dos huecos. Cuando la suma de un día llega a 2, ese día aparece como Completo. Si lo dejas vacío, se entiende 1 (y 0 en Curso y Reunión).</t>
   </si>
   <si>
+    <t>Día festivo</t>
+  </si>
+  <si>
+    <t>Marca un festivo. Ocupa siempre los 2 huecos (ese día sale Completo) y no admite competiciones. Pon Inicio, Fin y el nombre del festivo; el resto puede quedar vacío.</t>
+  </si>
+  <si>
     <t>Horario viernes / sábado / domingo</t>
   </si>
   <si>
@@ -173,12 +170,39 @@
     <t>Todo el día</t>
   </si>
   <si>
+    <t>Copa Europa Libre-Danza-Parejas Artístico</t>
+  </si>
+  <si>
+    <t>Stade (Alemania)</t>
+  </si>
+  <si>
+    <t>Competición Internacional</t>
+  </si>
+  <si>
+    <t>Trofeo Iniciación Skid Xeraco</t>
+  </si>
+  <si>
     <t>Mañana</t>
   </si>
   <si>
+    <t>Castelló de la Ribera</t>
+  </si>
+  <si>
+    <t>Trofeo Iniciación Rafelbunyol</t>
+  </si>
+  <si>
     <t>Rafelbunyol</t>
   </si>
   <si>
+    <t>Trofeo Iniciación Llombai</t>
+  </si>
+  <si>
+    <t>Llombai</t>
+  </si>
+  <si>
+    <t>L'Alcúdia de Crespins</t>
+  </si>
+  <si>
     <t>Trofeo Territorial Alginet</t>
   </si>
   <si>
@@ -188,37 +212,16 @@
     <t>Tarde</t>
   </si>
   <si>
+    <t>Trofeo Iniciación 8Rodes Barxeta</t>
+  </si>
+  <si>
     <t>Llocnou de Sant Jeroni</t>
   </si>
   <si>
-    <t>L'Alcúdia de Crespins</t>
-  </si>
-  <si>
-    <t>Trofeo Iniciación Skid Xeraco</t>
-  </si>
-  <si>
-    <t>Trofeo Iniciación Rafelbunyol</t>
-  </si>
-  <si>
-    <t>Trofeo Iniciación 8Rodes Barxeta</t>
-  </si>
-  <si>
     <t>Trofeo Iniciación L'Alcúdia de Crespins</t>
   </si>
   <si>
-    <t>World Skate Games</t>
-  </si>
-  <si>
-    <t>Asunción</t>
-  </si>
-  <si>
-    <t>Competición Internacional</t>
-  </si>
-  <si>
-    <t>Copa Europa Libre-Danza-Parejas Artístico</t>
-  </si>
-  <si>
-    <t>Stade (Alemania)</t>
+    <t>Elecciones Generales</t>
   </si>
   <si>
     <t>Trofeo Iniciación Azalea</t>
@@ -227,19 +230,7 @@
     <t>Castelló de la Plana</t>
   </si>
   <si>
-    <t>Elecciones Generales</t>
-  </si>
-  <si>
-    <t>Castelló de la Ribera</t>
-  </si>
-  <si>
-    <t>Trofeo Iniciación Llombai</t>
-  </si>
-  <si>
-    <t>Llombai</t>
-  </si>
-  <si>
-    <t>L'Alcudia de Crespins</t>
+    <t>Día de la Constitución</t>
   </si>
 </sst>
 </file>
@@ -332,7 +323,351 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="50">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE3EBCB"/>
+          <bgColor rgb="FFE3EBCB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE1E6EB"/>
+          <bgColor rgb="FFE1E6EB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFCDEBE7"/>
+          <bgColor rgb="FFCDEBE7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFCEBCB"/>
+          <bgColor rgb="FFFCEBCB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE8D5F5"/>
+          <bgColor rgb="FFE8D5F5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD5E3FA"/>
+          <bgColor rgb="FFD5E3FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFBD9DF"/>
+          <bgColor rgb="FFFBD9DF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE3EBCB"/>
+          <bgColor rgb="FFE3EBCB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE1E6EB"/>
+          <bgColor rgb="FFE1E6EB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFCDEBE7"/>
+          <bgColor rgb="FFCDEBE7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFCEBCB"/>
+          <bgColor rgb="FFFCEBCB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE8D5F5"/>
+          <bgColor rgb="FFE8D5F5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD5E3FA"/>
+          <bgColor rgb="FFD5E3FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFBD9DF"/>
+          <bgColor rgb="FFFBD9DF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE3EBCB"/>
+          <bgColor rgb="FFE3EBCB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE1E6EB"/>
+          <bgColor rgb="FFE1E6EB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFCDEBE7"/>
+          <bgColor rgb="FFCDEBE7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFCEBCB"/>
+          <bgColor rgb="FFFCEBCB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE8D5F5"/>
+          <bgColor rgb="FFE8D5F5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD5E3FA"/>
+          <bgColor rgb="FFD5E3FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFBD9DF"/>
+          <bgColor rgb="FFFBD9DF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE3EBCB"/>
+          <bgColor rgb="FFE3EBCB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE1E6EB"/>
+          <bgColor rgb="FFE1E6EB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFCDEBE7"/>
+          <bgColor rgb="FFCDEBE7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFCEBCB"/>
+          <bgColor rgb="FFFCEBCB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE8D5F5"/>
+          <bgColor rgb="FFE8D5F5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD5E3FA"/>
+          <bgColor rgb="FFD5E3FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFBD9DF"/>
+          <bgColor rgb="FFFBD9DF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE3EBCB"/>
+          <bgColor rgb="FFE3EBCB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE1E6EB"/>
+          <bgColor rgb="FFE1E6EB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFCDEBE7"/>
+          <bgColor rgb="FFCDEBE7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFCEBCB"/>
+          <bgColor rgb="FFFCEBCB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE8D5F5"/>
+          <bgColor rgb="FFE8D5F5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD5E3FA"/>
+          <bgColor rgb="FFD5E3FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFBD9DF"/>
+          <bgColor rgb="FFFBD9DF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE3EBCB"/>
+          <bgColor rgb="FFE3EBCB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE1E6EB"/>
+          <bgColor rgb="FFE1E6EB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFCDEBE7"/>
+          <bgColor rgb="FFCDEBE7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFCEBCB"/>
+          <bgColor rgb="FFFCEBCB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE8D5F5"/>
+          <bgColor rgb="FFE8D5F5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD5E3FA"/>
+          <bgColor rgb="FFD5E3FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFBD9DF"/>
+          <bgColor rgb="FFFBD9DF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF1DDD0"/>
+          <bgColor rgb="FFF1DDD0"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -400,10 +735,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -691,8 +1022,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:B16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="100" customWidth="1"/>
@@ -700,7 +1031,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B1" s="2"/>
     </row>
@@ -710,10 +1041,10 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -721,7 +1052,7 @@
         <v>0</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -729,7 +1060,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -737,7 +1068,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -745,7 +1076,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
@@ -753,7 +1084,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
@@ -761,51 +1092,59 @@
         <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="3"/>
-      <c r="B11" s="2"/>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>41</v>
-      </c>
+      <c r="A12" s="3"/>
+      <c r="B12" s="2"/>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="2" t="s">
+    </row>
+    <row r="16" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
+      <c r="B16" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -815,8 +1154,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I303"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:I302"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="13" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
@@ -857,49 +1196,51 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="5">
-        <v>46298</v>
+        <v>46311</v>
       </c>
       <c r="B2" s="5">
-        <v>46298</v>
+        <v>46313</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>71</v>
+        <v>11</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F2" s="7">
         <v>0</v>
       </c>
       <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
+      <c r="H2" s="6" t="s">
+        <v>47</v>
+      </c>
       <c r="I2" s="6"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
-        <v>46301</v>
+        <v>46312</v>
       </c>
       <c r="B3" s="5">
-        <v>46313</v>
+        <v>46319</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="F3" s="7">
         <v>0</v>
       </c>
       <c r="G3" s="6"/>
       <c r="H3" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I3" s="6"/>
     </row>
@@ -908,150 +1249,148 @@
         <v>46312</v>
       </c>
       <c r="B4" s="5">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F4" s="7">
         <v>1</v>
       </c>
       <c r="G4" s="6"/>
       <c r="H4" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="I4" s="6"/>
+        <v>47</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
-        <v>46311</v>
+        <v>46320</v>
       </c>
       <c r="B5" s="5">
-        <v>46313</v>
+        <v>46320</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>12</v>
+        <v>53</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F5" s="7">
         <v>0</v>
       </c>
       <c r="G5" s="6"/>
       <c r="H5" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I5" s="6"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
-        <v>46312</v>
+        <v>46319</v>
       </c>
       <c r="B6" s="5">
         <v>46319</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>63</v>
+        <v>15</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>62</v>
+        <v>17</v>
       </c>
       <c r="F6" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G6" s="6"/>
       <c r="H6" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I6" s="6"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
-        <v>46312</v>
+        <v>46327</v>
       </c>
       <c r="B7" s="5">
-        <v>46313</v>
+        <v>46327</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>19</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="D7" s="6"/>
       <c r="E7" s="6" t="s">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="F7" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7" s="6"/>
       <c r="H7" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>49</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="I7" s="6"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
-        <v>46320</v>
+        <v>46333</v>
       </c>
       <c r="B8" s="5">
-        <v>46320</v>
+        <v>46333</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F8" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" s="6"/>
       <c r="H8" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I8" s="6"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
-        <v>46319</v>
+        <v>46333</v>
       </c>
       <c r="B9" s="5">
-        <v>46319</v>
+        <v>46333</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F9" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G9" s="6"/>
       <c r="H9" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I9" s="6"/>
     </row>
@@ -1060,123 +1399,123 @@
         <v>46333</v>
       </c>
       <c r="B10" s="5">
-        <v>46333</v>
+        <v>46334</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>57</v>
+        <v>18</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F10" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" s="6"/>
       <c r="H10" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I10" s="6"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
-        <v>46333</v>
+        <v>46339</v>
       </c>
       <c r="B11" s="5">
-        <v>46333</v>
+        <v>46339</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F11" s="7">
         <v>1</v>
       </c>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6" t="s">
-        <v>48</v>
-      </c>
+      <c r="G11" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="H11" s="6"/>
       <c r="I11" s="6"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
-        <v>46333</v>
+        <v>46340</v>
       </c>
       <c r="B12" s="5">
-        <v>46334</v>
+        <v>46340</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F12" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G12" s="6"/>
       <c r="H12" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I12" s="6"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
-        <v>46339</v>
+        <v>46347</v>
       </c>
       <c r="B13" s="5">
-        <v>46339</v>
+        <v>46347</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F13" s="7">
         <v>1</v>
       </c>
-      <c r="G13" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="H13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6" t="s">
+        <v>47</v>
+      </c>
       <c r="I13" s="6"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="5">
-        <v>46340</v>
+        <v>46347</v>
       </c>
       <c r="B14" s="5">
-        <v>46340</v>
+        <v>46347</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>12</v>
+        <v>58</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F14" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G14" s="6"/>
       <c r="H14" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I14" s="6"/>
     </row>
@@ -1185,191 +1524,175 @@
         <v>46347</v>
       </c>
       <c r="B15" s="5">
-        <v>46347</v>
+        <v>46348</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>54</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="D15" s="6"/>
       <c r="E15" s="6" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F15" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" s="6"/>
       <c r="H15" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I15" s="6"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="5">
-        <v>46347</v>
+        <v>46354</v>
       </c>
       <c r="B16" s="5">
-        <v>46347</v>
+        <v>46354</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="F16" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="6" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="I16" s="6"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
-        <v>46347</v>
+        <v>46354</v>
       </c>
       <c r="B17" s="5">
-        <v>46348</v>
+        <v>46355</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D17" s="6"/>
       <c r="E17" s="6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F17" s="7">
         <v>0</v>
       </c>
       <c r="G17" s="6"/>
       <c r="H17" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I17" s="6"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="5">
-        <v>46354</v>
+        <v>46355</v>
       </c>
       <c r="B18" s="5">
-        <v>46354</v>
+        <v>46355</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>26</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="D18" s="6"/>
       <c r="E18" s="6" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F18" s="7">
         <v>2</v>
       </c>
       <c r="G18" s="6"/>
       <c r="H18" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I18" s="6"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
-        <v>46354</v>
+        <v>46362</v>
       </c>
       <c r="B19" s="5">
-        <v>46355</v>
+        <v>46362</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="D19" s="6"/>
       <c r="E19" s="6" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="F19" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G19" s="6"/>
       <c r="H19" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I19" s="6"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="5">
-        <v>46355</v>
+        <v>46368</v>
       </c>
       <c r="B20" s="5">
-        <v>46355</v>
+        <v>46368</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>67</v>
+        <v>25</v>
       </c>
       <c r="D20" s="6"/>
       <c r="E20" s="6" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="F20" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G20" s="6"/>
       <c r="H20" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I20" s="6"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
-        <v>46368</v>
+        <v>46397</v>
       </c>
       <c r="B21" s="5">
-        <v>46368</v>
+        <v>46397</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D21" s="6"/>
+        <v>66</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>67</v>
+      </c>
       <c r="E21" s="6" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F21" s="7">
         <v>1</v>
       </c>
       <c r="G21" s="6"/>
       <c r="H21" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I21" s="6"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="5">
-        <v>46397</v>
-      </c>
-      <c r="B22" s="5">
-        <v>46397</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22" s="7">
-        <v>1</v>
-      </c>
+      <c r="A22" s="5"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="7"/>
       <c r="G22" s="6"/>
-      <c r="H22" s="6" t="s">
-        <v>48</v>
-      </c>
+      <c r="H22" s="6"/>
       <c r="I22" s="6"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
@@ -2154,2223 +2477,2223 @@
       <c r="I93" s="6"/>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A94" s="6"/>
-      <c r="B94" s="6"/>
+      <c r="A94" s="5"/>
+      <c r="B94" s="5"/>
       <c r="C94" s="6"/>
       <c r="D94" s="6"/>
       <c r="E94" s="6"/>
-      <c r="F94" s="6"/>
+      <c r="F94" s="7"/>
       <c r="G94" s="6"/>
       <c r="H94" s="6"/>
       <c r="I94" s="6"/>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A95" s="6"/>
-      <c r="B95" s="6"/>
+      <c r="A95" s="5"/>
+      <c r="B95" s="5"/>
       <c r="C95" s="6"/>
       <c r="D95" s="6"/>
       <c r="E95" s="6"/>
-      <c r="F95" s="6"/>
+      <c r="F95" s="7"/>
       <c r="G95" s="6"/>
       <c r="H95" s="6"/>
       <c r="I95" s="6"/>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A96" s="6"/>
-      <c r="B96" s="6"/>
+      <c r="A96" s="5"/>
+      <c r="B96" s="5"/>
       <c r="C96" s="6"/>
       <c r="D96" s="6"/>
       <c r="E96" s="6"/>
-      <c r="F96" s="6"/>
+      <c r="F96" s="7"/>
       <c r="G96" s="6"/>
       <c r="H96" s="6"/>
       <c r="I96" s="6"/>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A97" s="6"/>
-      <c r="B97" s="6"/>
+      <c r="A97" s="5"/>
+      <c r="B97" s="5"/>
       <c r="C97" s="6"/>
       <c r="D97" s="6"/>
       <c r="E97" s="6"/>
-      <c r="F97" s="6"/>
+      <c r="F97" s="7"/>
       <c r="G97" s="6"/>
       <c r="H97" s="6"/>
       <c r="I97" s="6"/>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A98" s="6"/>
-      <c r="B98" s="6"/>
+      <c r="A98" s="5"/>
+      <c r="B98" s="5"/>
       <c r="C98" s="6"/>
       <c r="D98" s="6"/>
       <c r="E98" s="6"/>
-      <c r="F98" s="6"/>
+      <c r="F98" s="7"/>
       <c r="G98" s="6"/>
       <c r="H98" s="6"/>
       <c r="I98" s="6"/>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A99" s="6"/>
-      <c r="B99" s="6"/>
+      <c r="A99" s="5"/>
+      <c r="B99" s="5"/>
       <c r="C99" s="6"/>
       <c r="D99" s="6"/>
       <c r="E99" s="6"/>
-      <c r="F99" s="6"/>
+      <c r="F99" s="7"/>
       <c r="G99" s="6"/>
       <c r="H99" s="6"/>
       <c r="I99" s="6"/>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A100" s="6"/>
-      <c r="B100" s="6"/>
+      <c r="A100" s="5"/>
+      <c r="B100" s="5"/>
       <c r="C100" s="6"/>
       <c r="D100" s="6"/>
       <c r="E100" s="6"/>
-      <c r="F100" s="6"/>
+      <c r="F100" s="7"/>
       <c r="G100" s="6"/>
       <c r="H100" s="6"/>
       <c r="I100" s="6"/>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A101" s="6"/>
-      <c r="B101" s="6"/>
+      <c r="A101" s="5"/>
+      <c r="B101" s="5"/>
       <c r="C101" s="6"/>
       <c r="D101" s="6"/>
       <c r="E101" s="6"/>
-      <c r="F101" s="6"/>
+      <c r="F101" s="7"/>
       <c r="G101" s="6"/>
       <c r="H101" s="6"/>
       <c r="I101" s="6"/>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A102" s="6"/>
-      <c r="B102" s="6"/>
+      <c r="A102" s="5"/>
+      <c r="B102" s="5"/>
       <c r="C102" s="6"/>
       <c r="D102" s="6"/>
       <c r="E102" s="6"/>
-      <c r="F102" s="6"/>
+      <c r="F102" s="7"/>
       <c r="G102" s="6"/>
       <c r="H102" s="6"/>
       <c r="I102" s="6"/>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A103" s="6"/>
-      <c r="B103" s="6"/>
+      <c r="A103" s="5"/>
+      <c r="B103" s="5"/>
       <c r="C103" s="6"/>
       <c r="D103" s="6"/>
       <c r="E103" s="6"/>
-      <c r="F103" s="6"/>
+      <c r="F103" s="7"/>
       <c r="G103" s="6"/>
       <c r="H103" s="6"/>
       <c r="I103" s="6"/>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A104" s="6"/>
-      <c r="B104" s="6"/>
+      <c r="A104" s="5"/>
+      <c r="B104" s="5"/>
       <c r="C104" s="6"/>
       <c r="D104" s="6"/>
       <c r="E104" s="6"/>
-      <c r="F104" s="6"/>
+      <c r="F104" s="7"/>
       <c r="G104" s="6"/>
       <c r="H104" s="6"/>
       <c r="I104" s="6"/>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A105" s="6"/>
-      <c r="B105" s="6"/>
+      <c r="A105" s="5"/>
+      <c r="B105" s="5"/>
       <c r="C105" s="6"/>
       <c r="D105" s="6"/>
       <c r="E105" s="6"/>
-      <c r="F105" s="6"/>
+      <c r="F105" s="7"/>
       <c r="G105" s="6"/>
       <c r="H105" s="6"/>
       <c r="I105" s="6"/>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A106" s="6"/>
-      <c r="B106" s="6"/>
+      <c r="A106" s="5"/>
+      <c r="B106" s="5"/>
       <c r="C106" s="6"/>
       <c r="D106" s="6"/>
       <c r="E106" s="6"/>
-      <c r="F106" s="6"/>
+      <c r="F106" s="7"/>
       <c r="G106" s="6"/>
       <c r="H106" s="6"/>
       <c r="I106" s="6"/>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A107" s="6"/>
-      <c r="B107" s="6"/>
+      <c r="A107" s="5"/>
+      <c r="B107" s="5"/>
       <c r="C107" s="6"/>
       <c r="D107" s="6"/>
       <c r="E107" s="6"/>
-      <c r="F107" s="6"/>
+      <c r="F107" s="7"/>
       <c r="G107" s="6"/>
       <c r="H107" s="6"/>
       <c r="I107" s="6"/>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A108" s="6"/>
-      <c r="B108" s="6"/>
+      <c r="A108" s="5"/>
+      <c r="B108" s="5"/>
       <c r="C108" s="6"/>
       <c r="D108" s="6"/>
       <c r="E108" s="6"/>
-      <c r="F108" s="6"/>
+      <c r="F108" s="7"/>
       <c r="G108" s="6"/>
       <c r="H108" s="6"/>
       <c r="I108" s="6"/>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A109" s="6"/>
-      <c r="B109" s="6"/>
+      <c r="A109" s="5"/>
+      <c r="B109" s="5"/>
       <c r="C109" s="6"/>
       <c r="D109" s="6"/>
       <c r="E109" s="6"/>
-      <c r="F109" s="6"/>
+      <c r="F109" s="7"/>
       <c r="G109" s="6"/>
       <c r="H109" s="6"/>
       <c r="I109" s="6"/>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A110" s="6"/>
-      <c r="B110" s="6"/>
+      <c r="A110" s="5"/>
+      <c r="B110" s="5"/>
       <c r="C110" s="6"/>
       <c r="D110" s="6"/>
       <c r="E110" s="6"/>
-      <c r="F110" s="6"/>
+      <c r="F110" s="7"/>
       <c r="G110" s="6"/>
       <c r="H110" s="6"/>
       <c r="I110" s="6"/>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A111" s="6"/>
-      <c r="B111" s="6"/>
+      <c r="A111" s="5"/>
+      <c r="B111" s="5"/>
       <c r="C111" s="6"/>
       <c r="D111" s="6"/>
       <c r="E111" s="6"/>
-      <c r="F111" s="6"/>
+      <c r="F111" s="7"/>
       <c r="G111" s="6"/>
       <c r="H111" s="6"/>
       <c r="I111" s="6"/>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A112" s="6"/>
-      <c r="B112" s="6"/>
+      <c r="A112" s="5"/>
+      <c r="B112" s="5"/>
       <c r="C112" s="6"/>
       <c r="D112" s="6"/>
       <c r="E112" s="6"/>
-      <c r="F112" s="6"/>
+      <c r="F112" s="7"/>
       <c r="G112" s="6"/>
       <c r="H112" s="6"/>
       <c r="I112" s="6"/>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A113" s="6"/>
-      <c r="B113" s="6"/>
+      <c r="A113" s="5"/>
+      <c r="B113" s="5"/>
       <c r="C113" s="6"/>
       <c r="D113" s="6"/>
       <c r="E113" s="6"/>
-      <c r="F113" s="6"/>
+      <c r="F113" s="7"/>
       <c r="G113" s="6"/>
       <c r="H113" s="6"/>
       <c r="I113" s="6"/>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A114" s="6"/>
-      <c r="B114" s="6"/>
+      <c r="A114" s="5"/>
+      <c r="B114" s="5"/>
       <c r="C114" s="6"/>
       <c r="D114" s="6"/>
       <c r="E114" s="6"/>
-      <c r="F114" s="6"/>
+      <c r="F114" s="7"/>
       <c r="G114" s="6"/>
       <c r="H114" s="6"/>
       <c r="I114" s="6"/>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A115" s="6"/>
-      <c r="B115" s="6"/>
+      <c r="A115" s="5"/>
+      <c r="B115" s="5"/>
       <c r="C115" s="6"/>
       <c r="D115" s="6"/>
       <c r="E115" s="6"/>
-      <c r="F115" s="6"/>
+      <c r="F115" s="7"/>
       <c r="G115" s="6"/>
       <c r="H115" s="6"/>
       <c r="I115" s="6"/>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A116" s="6"/>
-      <c r="B116" s="6"/>
+      <c r="A116" s="5"/>
+      <c r="B116" s="5"/>
       <c r="C116" s="6"/>
       <c r="D116" s="6"/>
       <c r="E116" s="6"/>
-      <c r="F116" s="6"/>
+      <c r="F116" s="7"/>
       <c r="G116" s="6"/>
       <c r="H116" s="6"/>
       <c r="I116" s="6"/>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A117" s="6"/>
-      <c r="B117" s="6"/>
+      <c r="A117" s="5"/>
+      <c r="B117" s="5"/>
       <c r="C117" s="6"/>
       <c r="D117" s="6"/>
       <c r="E117" s="6"/>
-      <c r="F117" s="6"/>
+      <c r="F117" s="7"/>
       <c r="G117" s="6"/>
       <c r="H117" s="6"/>
       <c r="I117" s="6"/>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A118" s="6"/>
-      <c r="B118" s="6"/>
+      <c r="A118" s="5"/>
+      <c r="B118" s="5"/>
       <c r="C118" s="6"/>
       <c r="D118" s="6"/>
       <c r="E118" s="6"/>
-      <c r="F118" s="6"/>
+      <c r="F118" s="7"/>
       <c r="G118" s="6"/>
       <c r="H118" s="6"/>
       <c r="I118" s="6"/>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A119" s="6"/>
-      <c r="B119" s="6"/>
+      <c r="A119" s="5"/>
+      <c r="B119" s="5"/>
       <c r="C119" s="6"/>
       <c r="D119" s="6"/>
       <c r="E119" s="6"/>
-      <c r="F119" s="6"/>
+      <c r="F119" s="7"/>
       <c r="G119" s="6"/>
       <c r="H119" s="6"/>
       <c r="I119" s="6"/>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A120" s="6"/>
-      <c r="B120" s="6"/>
+      <c r="A120" s="5"/>
+      <c r="B120" s="5"/>
       <c r="C120" s="6"/>
       <c r="D120" s="6"/>
       <c r="E120" s="6"/>
-      <c r="F120" s="6"/>
+      <c r="F120" s="7"/>
       <c r="G120" s="6"/>
       <c r="H120" s="6"/>
       <c r="I120" s="6"/>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A121" s="6"/>
-      <c r="B121" s="6"/>
+      <c r="A121" s="5"/>
+      <c r="B121" s="5"/>
       <c r="C121" s="6"/>
       <c r="D121" s="6"/>
       <c r="E121" s="6"/>
-      <c r="F121" s="6"/>
+      <c r="F121" s="7"/>
       <c r="G121" s="6"/>
       <c r="H121" s="6"/>
       <c r="I121" s="6"/>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A122" s="6"/>
-      <c r="B122" s="6"/>
+      <c r="A122" s="5"/>
+      <c r="B122" s="5"/>
       <c r="C122" s="6"/>
       <c r="D122" s="6"/>
       <c r="E122" s="6"/>
-      <c r="F122" s="6"/>
+      <c r="F122" s="7"/>
       <c r="G122" s="6"/>
       <c r="H122" s="6"/>
       <c r="I122" s="6"/>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A123" s="6"/>
-      <c r="B123" s="6"/>
+      <c r="A123" s="5"/>
+      <c r="B123" s="5"/>
       <c r="C123" s="6"/>
       <c r="D123" s="6"/>
       <c r="E123" s="6"/>
-      <c r="F123" s="6"/>
+      <c r="F123" s="7"/>
       <c r="G123" s="6"/>
       <c r="H123" s="6"/>
       <c r="I123" s="6"/>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A124" s="6"/>
-      <c r="B124" s="6"/>
+      <c r="A124" s="5"/>
+      <c r="B124" s="5"/>
       <c r="C124" s="6"/>
       <c r="D124" s="6"/>
       <c r="E124" s="6"/>
-      <c r="F124" s="6"/>
+      <c r="F124" s="7"/>
       <c r="G124" s="6"/>
       <c r="H124" s="6"/>
       <c r="I124" s="6"/>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A125" s="6"/>
-      <c r="B125" s="6"/>
+      <c r="A125" s="5"/>
+      <c r="B125" s="5"/>
       <c r="C125" s="6"/>
       <c r="D125" s="6"/>
       <c r="E125" s="6"/>
-      <c r="F125" s="6"/>
+      <c r="F125" s="7"/>
       <c r="G125" s="6"/>
       <c r="H125" s="6"/>
       <c r="I125" s="6"/>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A126" s="6"/>
-      <c r="B126" s="6"/>
+      <c r="A126" s="5"/>
+      <c r="B126" s="5"/>
       <c r="C126" s="6"/>
       <c r="D126" s="6"/>
       <c r="E126" s="6"/>
-      <c r="F126" s="6"/>
+      <c r="F126" s="7"/>
       <c r="G126" s="6"/>
       <c r="H126" s="6"/>
       <c r="I126" s="6"/>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A127" s="6"/>
-      <c r="B127" s="6"/>
+      <c r="A127" s="5"/>
+      <c r="B127" s="5"/>
       <c r="C127" s="6"/>
       <c r="D127" s="6"/>
       <c r="E127" s="6"/>
-      <c r="F127" s="6"/>
+      <c r="F127" s="7"/>
       <c r="G127" s="6"/>
       <c r="H127" s="6"/>
       <c r="I127" s="6"/>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A128" s="6"/>
-      <c r="B128" s="6"/>
+      <c r="A128" s="5"/>
+      <c r="B128" s="5"/>
       <c r="C128" s="6"/>
       <c r="D128" s="6"/>
       <c r="E128" s="6"/>
-      <c r="F128" s="6"/>
+      <c r="F128" s="7"/>
       <c r="G128" s="6"/>
       <c r="H128" s="6"/>
       <c r="I128" s="6"/>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A129" s="6"/>
-      <c r="B129" s="6"/>
+      <c r="A129" s="5"/>
+      <c r="B129" s="5"/>
       <c r="C129" s="6"/>
       <c r="D129" s="6"/>
       <c r="E129" s="6"/>
-      <c r="F129" s="6"/>
+      <c r="F129" s="7"/>
       <c r="G129" s="6"/>
       <c r="H129" s="6"/>
       <c r="I129" s="6"/>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A130" s="6"/>
-      <c r="B130" s="6"/>
+      <c r="A130" s="5"/>
+      <c r="B130" s="5"/>
       <c r="C130" s="6"/>
       <c r="D130" s="6"/>
       <c r="E130" s="6"/>
-      <c r="F130" s="6"/>
+      <c r="F130" s="7"/>
       <c r="G130" s="6"/>
       <c r="H130" s="6"/>
       <c r="I130" s="6"/>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A131" s="6"/>
-      <c r="B131" s="6"/>
+      <c r="A131" s="5"/>
+      <c r="B131" s="5"/>
       <c r="C131" s="6"/>
       <c r="D131" s="6"/>
       <c r="E131" s="6"/>
-      <c r="F131" s="6"/>
+      <c r="F131" s="7"/>
       <c r="G131" s="6"/>
       <c r="H131" s="6"/>
       <c r="I131" s="6"/>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A132" s="6"/>
-      <c r="B132" s="6"/>
+      <c r="A132" s="5"/>
+      <c r="B132" s="5"/>
       <c r="C132" s="6"/>
       <c r="D132" s="6"/>
       <c r="E132" s="6"/>
-      <c r="F132" s="6"/>
+      <c r="F132" s="7"/>
       <c r="G132" s="6"/>
       <c r="H132" s="6"/>
       <c r="I132" s="6"/>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A133" s="6"/>
-      <c r="B133" s="6"/>
+      <c r="A133" s="5"/>
+      <c r="B133" s="5"/>
       <c r="C133" s="6"/>
       <c r="D133" s="6"/>
       <c r="E133" s="6"/>
-      <c r="F133" s="6"/>
+      <c r="F133" s="7"/>
       <c r="G133" s="6"/>
       <c r="H133" s="6"/>
       <c r="I133" s="6"/>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A134" s="6"/>
-      <c r="B134" s="6"/>
+      <c r="A134" s="5"/>
+      <c r="B134" s="5"/>
       <c r="C134" s="6"/>
       <c r="D134" s="6"/>
       <c r="E134" s="6"/>
-      <c r="F134" s="6"/>
+      <c r="F134" s="7"/>
       <c r="G134" s="6"/>
       <c r="H134" s="6"/>
       <c r="I134" s="6"/>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A135" s="6"/>
-      <c r="B135" s="6"/>
+      <c r="A135" s="5"/>
+      <c r="B135" s="5"/>
       <c r="C135" s="6"/>
       <c r="D135" s="6"/>
       <c r="E135" s="6"/>
-      <c r="F135" s="6"/>
+      <c r="F135" s="7"/>
       <c r="G135" s="6"/>
       <c r="H135" s="6"/>
       <c r="I135" s="6"/>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A136" s="6"/>
-      <c r="B136" s="6"/>
+      <c r="A136" s="5"/>
+      <c r="B136" s="5"/>
       <c r="C136" s="6"/>
       <c r="D136" s="6"/>
       <c r="E136" s="6"/>
-      <c r="F136" s="6"/>
+      <c r="F136" s="7"/>
       <c r="G136" s="6"/>
       <c r="H136" s="6"/>
       <c r="I136" s="6"/>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A137" s="6"/>
-      <c r="B137" s="6"/>
+      <c r="A137" s="5"/>
+      <c r="B137" s="5"/>
       <c r="C137" s="6"/>
       <c r="D137" s="6"/>
       <c r="E137" s="6"/>
-      <c r="F137" s="6"/>
+      <c r="F137" s="7"/>
       <c r="G137" s="6"/>
       <c r="H137" s="6"/>
       <c r="I137" s="6"/>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A138" s="6"/>
-      <c r="B138" s="6"/>
+      <c r="A138" s="5"/>
+      <c r="B138" s="5"/>
       <c r="C138" s="6"/>
       <c r="D138" s="6"/>
       <c r="E138" s="6"/>
-      <c r="F138" s="6"/>
+      <c r="F138" s="7"/>
       <c r="G138" s="6"/>
       <c r="H138" s="6"/>
       <c r="I138" s="6"/>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A139" s="6"/>
-      <c r="B139" s="6"/>
+      <c r="A139" s="5"/>
+      <c r="B139" s="5"/>
       <c r="C139" s="6"/>
       <c r="D139" s="6"/>
       <c r="E139" s="6"/>
-      <c r="F139" s="6"/>
+      <c r="F139" s="7"/>
       <c r="G139" s="6"/>
       <c r="H139" s="6"/>
       <c r="I139" s="6"/>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A140" s="6"/>
-      <c r="B140" s="6"/>
+      <c r="A140" s="5"/>
+      <c r="B140" s="5"/>
       <c r="C140" s="6"/>
       <c r="D140" s="6"/>
       <c r="E140" s="6"/>
-      <c r="F140" s="6"/>
+      <c r="F140" s="7"/>
       <c r="G140" s="6"/>
       <c r="H140" s="6"/>
       <c r="I140" s="6"/>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A141" s="6"/>
-      <c r="B141" s="6"/>
+      <c r="A141" s="5"/>
+      <c r="B141" s="5"/>
       <c r="C141" s="6"/>
       <c r="D141" s="6"/>
       <c r="E141" s="6"/>
-      <c r="F141" s="6"/>
+      <c r="F141" s="7"/>
       <c r="G141" s="6"/>
       <c r="H141" s="6"/>
       <c r="I141" s="6"/>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A142" s="6"/>
-      <c r="B142" s="6"/>
+      <c r="A142" s="5"/>
+      <c r="B142" s="5"/>
       <c r="C142" s="6"/>
       <c r="D142" s="6"/>
       <c r="E142" s="6"/>
-      <c r="F142" s="6"/>
+      <c r="F142" s="7"/>
       <c r="G142" s="6"/>
       <c r="H142" s="6"/>
       <c r="I142" s="6"/>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A143" s="6"/>
-      <c r="B143" s="6"/>
+      <c r="A143" s="5"/>
+      <c r="B143" s="5"/>
       <c r="C143" s="6"/>
       <c r="D143" s="6"/>
       <c r="E143" s="6"/>
-      <c r="F143" s="6"/>
+      <c r="F143" s="7"/>
       <c r="G143" s="6"/>
       <c r="H143" s="6"/>
       <c r="I143" s="6"/>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A144" s="6"/>
-      <c r="B144" s="6"/>
+      <c r="A144" s="5"/>
+      <c r="B144" s="5"/>
       <c r="C144" s="6"/>
       <c r="D144" s="6"/>
       <c r="E144" s="6"/>
-      <c r="F144" s="6"/>
+      <c r="F144" s="7"/>
       <c r="G144" s="6"/>
       <c r="H144" s="6"/>
       <c r="I144" s="6"/>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A145" s="6"/>
-      <c r="B145" s="6"/>
+      <c r="A145" s="5"/>
+      <c r="B145" s="5"/>
       <c r="C145" s="6"/>
       <c r="D145" s="6"/>
       <c r="E145" s="6"/>
-      <c r="F145" s="6"/>
+      <c r="F145" s="7"/>
       <c r="G145" s="6"/>
       <c r="H145" s="6"/>
       <c r="I145" s="6"/>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A146" s="6"/>
-      <c r="B146" s="6"/>
+      <c r="A146" s="5"/>
+      <c r="B146" s="5"/>
       <c r="C146" s="6"/>
       <c r="D146" s="6"/>
       <c r="E146" s="6"/>
-      <c r="F146" s="6"/>
+      <c r="F146" s="7"/>
       <c r="G146" s="6"/>
       <c r="H146" s="6"/>
       <c r="I146" s="6"/>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A147" s="6"/>
-      <c r="B147" s="6"/>
+      <c r="A147" s="5"/>
+      <c r="B147" s="5"/>
       <c r="C147" s="6"/>
       <c r="D147" s="6"/>
       <c r="E147" s="6"/>
-      <c r="F147" s="6"/>
+      <c r="F147" s="7"/>
       <c r="G147" s="6"/>
       <c r="H147" s="6"/>
       <c r="I147" s="6"/>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A148" s="6"/>
-      <c r="B148" s="6"/>
+      <c r="A148" s="5"/>
+      <c r="B148" s="5"/>
       <c r="C148" s="6"/>
       <c r="D148" s="6"/>
       <c r="E148" s="6"/>
-      <c r="F148" s="6"/>
+      <c r="F148" s="7"/>
       <c r="G148" s="6"/>
       <c r="H148" s="6"/>
       <c r="I148" s="6"/>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A149" s="6"/>
-      <c r="B149" s="6"/>
+      <c r="A149" s="5"/>
+      <c r="B149" s="5"/>
       <c r="C149" s="6"/>
       <c r="D149" s="6"/>
       <c r="E149" s="6"/>
-      <c r="F149" s="6"/>
+      <c r="F149" s="7"/>
       <c r="G149" s="6"/>
       <c r="H149" s="6"/>
       <c r="I149" s="6"/>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A150" s="6"/>
-      <c r="B150" s="6"/>
+      <c r="A150" s="5"/>
+      <c r="B150" s="5"/>
       <c r="C150" s="6"/>
       <c r="D150" s="6"/>
       <c r="E150" s="6"/>
-      <c r="F150" s="6"/>
+      <c r="F150" s="7"/>
       <c r="G150" s="6"/>
       <c r="H150" s="6"/>
       <c r="I150" s="6"/>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A151" s="6"/>
-      <c r="B151" s="6"/>
+      <c r="A151" s="5"/>
+      <c r="B151" s="5"/>
       <c r="C151" s="6"/>
       <c r="D151" s="6"/>
       <c r="E151" s="6"/>
-      <c r="F151" s="6"/>
+      <c r="F151" s="7"/>
       <c r="G151" s="6"/>
       <c r="H151" s="6"/>
       <c r="I151" s="6"/>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A152" s="6"/>
-      <c r="B152" s="6"/>
+      <c r="A152" s="5"/>
+      <c r="B152" s="5"/>
       <c r="C152" s="6"/>
       <c r="D152" s="6"/>
       <c r="E152" s="6"/>
-      <c r="F152" s="6"/>
+      <c r="F152" s="7"/>
       <c r="G152" s="6"/>
       <c r="H152" s="6"/>
       <c r="I152" s="6"/>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A153" s="6"/>
-      <c r="B153" s="6"/>
+      <c r="A153" s="5"/>
+      <c r="B153" s="5"/>
       <c r="C153" s="6"/>
       <c r="D153" s="6"/>
       <c r="E153" s="6"/>
-      <c r="F153" s="6"/>
+      <c r="F153" s="7"/>
       <c r="G153" s="6"/>
       <c r="H153" s="6"/>
       <c r="I153" s="6"/>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A154" s="6"/>
-      <c r="B154" s="6"/>
+      <c r="A154" s="5"/>
+      <c r="B154" s="5"/>
       <c r="C154" s="6"/>
       <c r="D154" s="6"/>
       <c r="E154" s="6"/>
-      <c r="F154" s="6"/>
+      <c r="F154" s="7"/>
       <c r="G154" s="6"/>
       <c r="H154" s="6"/>
       <c r="I154" s="6"/>
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A155" s="6"/>
-      <c r="B155" s="6"/>
+      <c r="A155" s="5"/>
+      <c r="B155" s="5"/>
       <c r="C155" s="6"/>
       <c r="D155" s="6"/>
       <c r="E155" s="6"/>
-      <c r="F155" s="6"/>
+      <c r="F155" s="7"/>
       <c r="G155" s="6"/>
       <c r="H155" s="6"/>
       <c r="I155" s="6"/>
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A156" s="6"/>
-      <c r="B156" s="6"/>
+      <c r="A156" s="5"/>
+      <c r="B156" s="5"/>
       <c r="C156" s="6"/>
       <c r="D156" s="6"/>
       <c r="E156" s="6"/>
-      <c r="F156" s="6"/>
+      <c r="F156" s="7"/>
       <c r="G156" s="6"/>
       <c r="H156" s="6"/>
       <c r="I156" s="6"/>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A157" s="6"/>
-      <c r="B157" s="6"/>
+      <c r="A157" s="5"/>
+      <c r="B157" s="5"/>
       <c r="C157" s="6"/>
       <c r="D157" s="6"/>
       <c r="E157" s="6"/>
-      <c r="F157" s="6"/>
+      <c r="F157" s="7"/>
       <c r="G157" s="6"/>
       <c r="H157" s="6"/>
       <c r="I157" s="6"/>
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A158" s="6"/>
-      <c r="B158" s="6"/>
+      <c r="A158" s="5"/>
+      <c r="B158" s="5"/>
       <c r="C158" s="6"/>
       <c r="D158" s="6"/>
       <c r="E158" s="6"/>
-      <c r="F158" s="6"/>
+      <c r="F158" s="7"/>
       <c r="G158" s="6"/>
       <c r="H158" s="6"/>
       <c r="I158" s="6"/>
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A159" s="6"/>
-      <c r="B159" s="6"/>
+      <c r="A159" s="5"/>
+      <c r="B159" s="5"/>
       <c r="C159" s="6"/>
       <c r="D159" s="6"/>
       <c r="E159" s="6"/>
-      <c r="F159" s="6"/>
+      <c r="F159" s="7"/>
       <c r="G159" s="6"/>
       <c r="H159" s="6"/>
       <c r="I159" s="6"/>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A160" s="6"/>
-      <c r="B160" s="6"/>
+      <c r="A160" s="5"/>
+      <c r="B160" s="5"/>
       <c r="C160" s="6"/>
       <c r="D160" s="6"/>
       <c r="E160" s="6"/>
-      <c r="F160" s="6"/>
+      <c r="F160" s="7"/>
       <c r="G160" s="6"/>
       <c r="H160" s="6"/>
       <c r="I160" s="6"/>
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A161" s="6"/>
-      <c r="B161" s="6"/>
+      <c r="A161" s="5"/>
+      <c r="B161" s="5"/>
       <c r="C161" s="6"/>
       <c r="D161" s="6"/>
       <c r="E161" s="6"/>
-      <c r="F161" s="6"/>
+      <c r="F161" s="7"/>
       <c r="G161" s="6"/>
       <c r="H161" s="6"/>
       <c r="I161" s="6"/>
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A162" s="6"/>
-      <c r="B162" s="6"/>
+      <c r="A162" s="5"/>
+      <c r="B162" s="5"/>
       <c r="C162" s="6"/>
       <c r="D162" s="6"/>
       <c r="E162" s="6"/>
-      <c r="F162" s="6"/>
+      <c r="F162" s="7"/>
       <c r="G162" s="6"/>
       <c r="H162" s="6"/>
       <c r="I162" s="6"/>
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A163" s="6"/>
-      <c r="B163" s="6"/>
+      <c r="A163" s="5"/>
+      <c r="B163" s="5"/>
       <c r="C163" s="6"/>
       <c r="D163" s="6"/>
       <c r="E163" s="6"/>
-      <c r="F163" s="6"/>
+      <c r="F163" s="7"/>
       <c r="G163" s="6"/>
       <c r="H163" s="6"/>
       <c r="I163" s="6"/>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A164" s="6"/>
-      <c r="B164" s="6"/>
+      <c r="A164" s="5"/>
+      <c r="B164" s="5"/>
       <c r="C164" s="6"/>
       <c r="D164" s="6"/>
       <c r="E164" s="6"/>
-      <c r="F164" s="6"/>
+      <c r="F164" s="7"/>
       <c r="G164" s="6"/>
       <c r="H164" s="6"/>
       <c r="I164" s="6"/>
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A165" s="6"/>
-      <c r="B165" s="6"/>
+      <c r="A165" s="5"/>
+      <c r="B165" s="5"/>
       <c r="C165" s="6"/>
       <c r="D165" s="6"/>
       <c r="E165" s="6"/>
-      <c r="F165" s="6"/>
+      <c r="F165" s="7"/>
       <c r="G165" s="6"/>
       <c r="H165" s="6"/>
       <c r="I165" s="6"/>
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A166" s="6"/>
-      <c r="B166" s="6"/>
+      <c r="A166" s="5"/>
+      <c r="B166" s="5"/>
       <c r="C166" s="6"/>
       <c r="D166" s="6"/>
       <c r="E166" s="6"/>
-      <c r="F166" s="6"/>
+      <c r="F166" s="7"/>
       <c r="G166" s="6"/>
       <c r="H166" s="6"/>
       <c r="I166" s="6"/>
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A167" s="6"/>
-      <c r="B167" s="6"/>
+      <c r="A167" s="5"/>
+      <c r="B167" s="5"/>
       <c r="C167" s="6"/>
       <c r="D167" s="6"/>
       <c r="E167" s="6"/>
-      <c r="F167" s="6"/>
+      <c r="F167" s="7"/>
       <c r="G167" s="6"/>
       <c r="H167" s="6"/>
       <c r="I167" s="6"/>
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A168" s="6"/>
-      <c r="B168" s="6"/>
+      <c r="A168" s="5"/>
+      <c r="B168" s="5"/>
       <c r="C168" s="6"/>
       <c r="D168" s="6"/>
       <c r="E168" s="6"/>
-      <c r="F168" s="6"/>
+      <c r="F168" s="7"/>
       <c r="G168" s="6"/>
       <c r="H168" s="6"/>
       <c r="I168" s="6"/>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A169" s="6"/>
-      <c r="B169" s="6"/>
+      <c r="A169" s="5"/>
+      <c r="B169" s="5"/>
       <c r="C169" s="6"/>
       <c r="D169" s="6"/>
       <c r="E169" s="6"/>
-      <c r="F169" s="6"/>
+      <c r="F169" s="7"/>
       <c r="G169" s="6"/>
       <c r="H169" s="6"/>
       <c r="I169" s="6"/>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A170" s="6"/>
-      <c r="B170" s="6"/>
+      <c r="A170" s="5"/>
+      <c r="B170" s="5"/>
       <c r="C170" s="6"/>
       <c r="D170" s="6"/>
       <c r="E170" s="6"/>
-      <c r="F170" s="6"/>
+      <c r="F170" s="7"/>
       <c r="G170" s="6"/>
       <c r="H170" s="6"/>
       <c r="I170" s="6"/>
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A171" s="6"/>
-      <c r="B171" s="6"/>
+      <c r="A171" s="5"/>
+      <c r="B171" s="5"/>
       <c r="C171" s="6"/>
       <c r="D171" s="6"/>
       <c r="E171" s="6"/>
-      <c r="F171" s="6"/>
+      <c r="F171" s="7"/>
       <c r="G171" s="6"/>
       <c r="H171" s="6"/>
       <c r="I171" s="6"/>
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A172" s="6"/>
-      <c r="B172" s="6"/>
+      <c r="A172" s="5"/>
+      <c r="B172" s="5"/>
       <c r="C172" s="6"/>
       <c r="D172" s="6"/>
       <c r="E172" s="6"/>
-      <c r="F172" s="6"/>
+      <c r="F172" s="7"/>
       <c r="G172" s="6"/>
       <c r="H172" s="6"/>
       <c r="I172" s="6"/>
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A173" s="6"/>
-      <c r="B173" s="6"/>
+      <c r="A173" s="5"/>
+      <c r="B173" s="5"/>
       <c r="C173" s="6"/>
       <c r="D173" s="6"/>
       <c r="E173" s="6"/>
-      <c r="F173" s="6"/>
+      <c r="F173" s="7"/>
       <c r="G173" s="6"/>
       <c r="H173" s="6"/>
       <c r="I173" s="6"/>
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A174" s="6"/>
-      <c r="B174" s="6"/>
+      <c r="A174" s="5"/>
+      <c r="B174" s="5"/>
       <c r="C174" s="6"/>
       <c r="D174" s="6"/>
       <c r="E174" s="6"/>
-      <c r="F174" s="6"/>
+      <c r="F174" s="7"/>
       <c r="G174" s="6"/>
       <c r="H174" s="6"/>
       <c r="I174" s="6"/>
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A175" s="6"/>
-      <c r="B175" s="6"/>
+      <c r="A175" s="5"/>
+      <c r="B175" s="5"/>
       <c r="C175" s="6"/>
       <c r="D175" s="6"/>
       <c r="E175" s="6"/>
-      <c r="F175" s="6"/>
+      <c r="F175" s="7"/>
       <c r="G175" s="6"/>
       <c r="H175" s="6"/>
       <c r="I175" s="6"/>
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A176" s="6"/>
-      <c r="B176" s="6"/>
+      <c r="A176" s="5"/>
+      <c r="B176" s="5"/>
       <c r="C176" s="6"/>
       <c r="D176" s="6"/>
       <c r="E176" s="6"/>
-      <c r="F176" s="6"/>
+      <c r="F176" s="7"/>
       <c r="G176" s="6"/>
       <c r="H176" s="6"/>
       <c r="I176" s="6"/>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A177" s="6"/>
-      <c r="B177" s="6"/>
+      <c r="A177" s="5"/>
+      <c r="B177" s="5"/>
       <c r="C177" s="6"/>
       <c r="D177" s="6"/>
       <c r="E177" s="6"/>
-      <c r="F177" s="6"/>
+      <c r="F177" s="7"/>
       <c r="G177" s="6"/>
       <c r="H177" s="6"/>
       <c r="I177" s="6"/>
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A178" s="6"/>
-      <c r="B178" s="6"/>
+      <c r="A178" s="5"/>
+      <c r="B178" s="5"/>
       <c r="C178" s="6"/>
       <c r="D178" s="6"/>
       <c r="E178" s="6"/>
-      <c r="F178" s="6"/>
+      <c r="F178" s="7"/>
       <c r="G178" s="6"/>
       <c r="H178" s="6"/>
       <c r="I178" s="6"/>
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A179" s="6"/>
-      <c r="B179" s="6"/>
+      <c r="A179" s="5"/>
+      <c r="B179" s="5"/>
       <c r="C179" s="6"/>
       <c r="D179" s="6"/>
       <c r="E179" s="6"/>
-      <c r="F179" s="6"/>
+      <c r="F179" s="7"/>
       <c r="G179" s="6"/>
       <c r="H179" s="6"/>
       <c r="I179" s="6"/>
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A180" s="6"/>
-      <c r="B180" s="6"/>
+      <c r="A180" s="5"/>
+      <c r="B180" s="5"/>
       <c r="C180" s="6"/>
       <c r="D180" s="6"/>
       <c r="E180" s="6"/>
-      <c r="F180" s="6"/>
+      <c r="F180" s="7"/>
       <c r="G180" s="6"/>
       <c r="H180" s="6"/>
       <c r="I180" s="6"/>
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A181" s="6"/>
-      <c r="B181" s="6"/>
+      <c r="A181" s="5"/>
+      <c r="B181" s="5"/>
       <c r="C181" s="6"/>
       <c r="D181" s="6"/>
       <c r="E181" s="6"/>
-      <c r="F181" s="6"/>
+      <c r="F181" s="7"/>
       <c r="G181" s="6"/>
       <c r="H181" s="6"/>
       <c r="I181" s="6"/>
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A182" s="6"/>
-      <c r="B182" s="6"/>
+      <c r="A182" s="5"/>
+      <c r="B182" s="5"/>
       <c r="C182" s="6"/>
       <c r="D182" s="6"/>
       <c r="E182" s="6"/>
-      <c r="F182" s="6"/>
+      <c r="F182" s="7"/>
       <c r="G182" s="6"/>
       <c r="H182" s="6"/>
       <c r="I182" s="6"/>
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A183" s="6"/>
-      <c r="B183" s="6"/>
+      <c r="A183" s="5"/>
+      <c r="B183" s="5"/>
       <c r="C183" s="6"/>
       <c r="D183" s="6"/>
       <c r="E183" s="6"/>
-      <c r="F183" s="6"/>
+      <c r="F183" s="7"/>
       <c r="G183" s="6"/>
       <c r="H183" s="6"/>
       <c r="I183" s="6"/>
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A184" s="6"/>
-      <c r="B184" s="6"/>
+      <c r="A184" s="5"/>
+      <c r="B184" s="5"/>
       <c r="C184" s="6"/>
       <c r="D184" s="6"/>
       <c r="E184" s="6"/>
-      <c r="F184" s="6"/>
+      <c r="F184" s="7"/>
       <c r="G184" s="6"/>
       <c r="H184" s="6"/>
       <c r="I184" s="6"/>
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A185" s="6"/>
-      <c r="B185" s="6"/>
+      <c r="A185" s="5"/>
+      <c r="B185" s="5"/>
       <c r="C185" s="6"/>
       <c r="D185" s="6"/>
       <c r="E185" s="6"/>
-      <c r="F185" s="6"/>
+      <c r="F185" s="7"/>
       <c r="G185" s="6"/>
       <c r="H185" s="6"/>
       <c r="I185" s="6"/>
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A186" s="6"/>
-      <c r="B186" s="6"/>
+      <c r="A186" s="5"/>
+      <c r="B186" s="5"/>
       <c r="C186" s="6"/>
       <c r="D186" s="6"/>
       <c r="E186" s="6"/>
-      <c r="F186" s="6"/>
+      <c r="F186" s="7"/>
       <c r="G186" s="6"/>
       <c r="H186" s="6"/>
       <c r="I186" s="6"/>
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A187" s="6"/>
-      <c r="B187" s="6"/>
+      <c r="A187" s="5"/>
+      <c r="B187" s="5"/>
       <c r="C187" s="6"/>
       <c r="D187" s="6"/>
       <c r="E187" s="6"/>
-      <c r="F187" s="6"/>
+      <c r="F187" s="7"/>
       <c r="G187" s="6"/>
       <c r="H187" s="6"/>
       <c r="I187" s="6"/>
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A188" s="6"/>
-      <c r="B188" s="6"/>
+      <c r="A188" s="5"/>
+      <c r="B188" s="5"/>
       <c r="C188" s="6"/>
       <c r="D188" s="6"/>
       <c r="E188" s="6"/>
-      <c r="F188" s="6"/>
+      <c r="F188" s="7"/>
       <c r="G188" s="6"/>
       <c r="H188" s="6"/>
       <c r="I188" s="6"/>
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A189" s="6"/>
-      <c r="B189" s="6"/>
+      <c r="A189" s="5"/>
+      <c r="B189" s="5"/>
       <c r="C189" s="6"/>
       <c r="D189" s="6"/>
       <c r="E189" s="6"/>
-      <c r="F189" s="6"/>
+      <c r="F189" s="7"/>
       <c r="G189" s="6"/>
       <c r="H189" s="6"/>
       <c r="I189" s="6"/>
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A190" s="6"/>
-      <c r="B190" s="6"/>
+      <c r="A190" s="5"/>
+      <c r="B190" s="5"/>
       <c r="C190" s="6"/>
       <c r="D190" s="6"/>
       <c r="E190" s="6"/>
-      <c r="F190" s="6"/>
+      <c r="F190" s="7"/>
       <c r="G190" s="6"/>
       <c r="H190" s="6"/>
       <c r="I190" s="6"/>
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A191" s="6"/>
-      <c r="B191" s="6"/>
+      <c r="A191" s="5"/>
+      <c r="B191" s="5"/>
       <c r="C191" s="6"/>
       <c r="D191" s="6"/>
       <c r="E191" s="6"/>
-      <c r="F191" s="6"/>
+      <c r="F191" s="7"/>
       <c r="G191" s="6"/>
       <c r="H191" s="6"/>
       <c r="I191" s="6"/>
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A192" s="6"/>
-      <c r="B192" s="6"/>
+      <c r="A192" s="5"/>
+      <c r="B192" s="5"/>
       <c r="C192" s="6"/>
       <c r="D192" s="6"/>
       <c r="E192" s="6"/>
-      <c r="F192" s="6"/>
+      <c r="F192" s="7"/>
       <c r="G192" s="6"/>
       <c r="H192" s="6"/>
       <c r="I192" s="6"/>
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A193" s="6"/>
-      <c r="B193" s="6"/>
+      <c r="A193" s="5"/>
+      <c r="B193" s="5"/>
       <c r="C193" s="6"/>
       <c r="D193" s="6"/>
       <c r="E193" s="6"/>
-      <c r="F193" s="6"/>
+      <c r="F193" s="7"/>
       <c r="G193" s="6"/>
       <c r="H193" s="6"/>
       <c r="I193" s="6"/>
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A194" s="6"/>
-      <c r="B194" s="6"/>
+      <c r="A194" s="5"/>
+      <c r="B194" s="5"/>
       <c r="C194" s="6"/>
       <c r="D194" s="6"/>
       <c r="E194" s="6"/>
-      <c r="F194" s="6"/>
+      <c r="F194" s="7"/>
       <c r="G194" s="6"/>
       <c r="H194" s="6"/>
       <c r="I194" s="6"/>
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A195" s="6"/>
-      <c r="B195" s="6"/>
+      <c r="A195" s="5"/>
+      <c r="B195" s="5"/>
       <c r="C195" s="6"/>
       <c r="D195" s="6"/>
       <c r="E195" s="6"/>
-      <c r="F195" s="6"/>
+      <c r="F195" s="7"/>
       <c r="G195" s="6"/>
       <c r="H195" s="6"/>
       <c r="I195" s="6"/>
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A196" s="6"/>
-      <c r="B196" s="6"/>
+      <c r="A196" s="5"/>
+      <c r="B196" s="5"/>
       <c r="C196" s="6"/>
       <c r="D196" s="6"/>
       <c r="E196" s="6"/>
-      <c r="F196" s="6"/>
+      <c r="F196" s="7"/>
       <c r="G196" s="6"/>
       <c r="H196" s="6"/>
       <c r="I196" s="6"/>
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A197" s="6"/>
-      <c r="B197" s="6"/>
+      <c r="A197" s="5"/>
+      <c r="B197" s="5"/>
       <c r="C197" s="6"/>
       <c r="D197" s="6"/>
       <c r="E197" s="6"/>
-      <c r="F197" s="6"/>
+      <c r="F197" s="7"/>
       <c r="G197" s="6"/>
       <c r="H197" s="6"/>
       <c r="I197" s="6"/>
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A198" s="6"/>
-      <c r="B198" s="6"/>
+      <c r="A198" s="5"/>
+      <c r="B198" s="5"/>
       <c r="C198" s="6"/>
       <c r="D198" s="6"/>
       <c r="E198" s="6"/>
-      <c r="F198" s="6"/>
+      <c r="F198" s="7"/>
       <c r="G198" s="6"/>
       <c r="H198" s="6"/>
       <c r="I198" s="6"/>
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A199" s="6"/>
-      <c r="B199" s="6"/>
+      <c r="A199" s="5"/>
+      <c r="B199" s="5"/>
       <c r="C199" s="6"/>
       <c r="D199" s="6"/>
       <c r="E199" s="6"/>
-      <c r="F199" s="6"/>
+      <c r="F199" s="7"/>
       <c r="G199" s="6"/>
       <c r="H199" s="6"/>
       <c r="I199" s="6"/>
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A200" s="6"/>
-      <c r="B200" s="6"/>
+      <c r="A200" s="5"/>
+      <c r="B200" s="5"/>
       <c r="C200" s="6"/>
       <c r="D200" s="6"/>
       <c r="E200" s="6"/>
-      <c r="F200" s="6"/>
+      <c r="F200" s="7"/>
       <c r="G200" s="6"/>
       <c r="H200" s="6"/>
       <c r="I200" s="6"/>
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A201" s="6"/>
-      <c r="B201" s="6"/>
+      <c r="A201" s="5"/>
+      <c r="B201" s="5"/>
       <c r="C201" s="6"/>
       <c r="D201" s="6"/>
       <c r="E201" s="6"/>
-      <c r="F201" s="6"/>
+      <c r="F201" s="7"/>
       <c r="G201" s="6"/>
       <c r="H201" s="6"/>
       <c r="I201" s="6"/>
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A202" s="6"/>
-      <c r="B202" s="6"/>
+      <c r="A202" s="5"/>
+      <c r="B202" s="5"/>
       <c r="C202" s="6"/>
       <c r="D202" s="6"/>
       <c r="E202" s="6"/>
-      <c r="F202" s="6"/>
+      <c r="F202" s="7"/>
       <c r="G202" s="6"/>
       <c r="H202" s="6"/>
       <c r="I202" s="6"/>
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A203" s="6"/>
-      <c r="B203" s="6"/>
+      <c r="A203" s="5"/>
+      <c r="B203" s="5"/>
       <c r="C203" s="6"/>
       <c r="D203" s="6"/>
       <c r="E203" s="6"/>
-      <c r="F203" s="6"/>
+      <c r="F203" s="7"/>
       <c r="G203" s="6"/>
       <c r="H203" s="6"/>
       <c r="I203" s="6"/>
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A204" s="6"/>
-      <c r="B204" s="6"/>
+      <c r="A204" s="5"/>
+      <c r="B204" s="5"/>
       <c r="C204" s="6"/>
       <c r="D204" s="6"/>
       <c r="E204" s="6"/>
-      <c r="F204" s="6"/>
+      <c r="F204" s="7"/>
       <c r="G204" s="6"/>
       <c r="H204" s="6"/>
       <c r="I204" s="6"/>
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A205" s="6"/>
-      <c r="B205" s="6"/>
+      <c r="A205" s="5"/>
+      <c r="B205" s="5"/>
       <c r="C205" s="6"/>
       <c r="D205" s="6"/>
       <c r="E205" s="6"/>
-      <c r="F205" s="6"/>
+      <c r="F205" s="7"/>
       <c r="G205" s="6"/>
       <c r="H205" s="6"/>
       <c r="I205" s="6"/>
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A206" s="6"/>
-      <c r="B206" s="6"/>
+      <c r="A206" s="5"/>
+      <c r="B206" s="5"/>
       <c r="C206" s="6"/>
       <c r="D206" s="6"/>
       <c r="E206" s="6"/>
-      <c r="F206" s="6"/>
+      <c r="F206" s="7"/>
       <c r="G206" s="6"/>
       <c r="H206" s="6"/>
       <c r="I206" s="6"/>
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A207" s="6"/>
-      <c r="B207" s="6"/>
+      <c r="A207" s="5"/>
+      <c r="B207" s="5"/>
       <c r="C207" s="6"/>
       <c r="D207" s="6"/>
       <c r="E207" s="6"/>
-      <c r="F207" s="6"/>
+      <c r="F207" s="7"/>
       <c r="G207" s="6"/>
       <c r="H207" s="6"/>
       <c r="I207" s="6"/>
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A208" s="6"/>
-      <c r="B208" s="6"/>
+      <c r="A208" s="5"/>
+      <c r="B208" s="5"/>
       <c r="C208" s="6"/>
       <c r="D208" s="6"/>
       <c r="E208" s="6"/>
-      <c r="F208" s="6"/>
+      <c r="F208" s="7"/>
       <c r="G208" s="6"/>
       <c r="H208" s="6"/>
       <c r="I208" s="6"/>
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A209" s="6"/>
-      <c r="B209" s="6"/>
+      <c r="A209" s="5"/>
+      <c r="B209" s="5"/>
       <c r="C209" s="6"/>
       <c r="D209" s="6"/>
       <c r="E209" s="6"/>
-      <c r="F209" s="6"/>
+      <c r="F209" s="7"/>
       <c r="G209" s="6"/>
       <c r="H209" s="6"/>
       <c r="I209" s="6"/>
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A210" s="6"/>
-      <c r="B210" s="6"/>
+      <c r="A210" s="5"/>
+      <c r="B210" s="5"/>
       <c r="C210" s="6"/>
       <c r="D210" s="6"/>
       <c r="E210" s="6"/>
-      <c r="F210" s="6"/>
+      <c r="F210" s="7"/>
       <c r="G210" s="6"/>
       <c r="H210" s="6"/>
       <c r="I210" s="6"/>
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A211" s="6"/>
-      <c r="B211" s="6"/>
+      <c r="A211" s="5"/>
+      <c r="B211" s="5"/>
       <c r="C211" s="6"/>
       <c r="D211" s="6"/>
       <c r="E211" s="6"/>
-      <c r="F211" s="6"/>
+      <c r="F211" s="7"/>
       <c r="G211" s="6"/>
       <c r="H211" s="6"/>
       <c r="I211" s="6"/>
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A212" s="6"/>
-      <c r="B212" s="6"/>
+      <c r="A212" s="5"/>
+      <c r="B212" s="5"/>
       <c r="C212" s="6"/>
       <c r="D212" s="6"/>
       <c r="E212" s="6"/>
-      <c r="F212" s="6"/>
+      <c r="F212" s="7"/>
       <c r="G212" s="6"/>
       <c r="H212" s="6"/>
       <c r="I212" s="6"/>
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A213" s="6"/>
-      <c r="B213" s="6"/>
+      <c r="A213" s="5"/>
+      <c r="B213" s="5"/>
       <c r="C213" s="6"/>
       <c r="D213" s="6"/>
       <c r="E213" s="6"/>
-      <c r="F213" s="6"/>
+      <c r="F213" s="7"/>
       <c r="G213" s="6"/>
       <c r="H213" s="6"/>
       <c r="I213" s="6"/>
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A214" s="6"/>
-      <c r="B214" s="6"/>
+      <c r="A214" s="5"/>
+      <c r="B214" s="5"/>
       <c r="C214" s="6"/>
       <c r="D214" s="6"/>
       <c r="E214" s="6"/>
-      <c r="F214" s="6"/>
+      <c r="F214" s="7"/>
       <c r="G214" s="6"/>
       <c r="H214" s="6"/>
       <c r="I214" s="6"/>
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A215" s="6"/>
-      <c r="B215" s="6"/>
+      <c r="A215" s="5"/>
+      <c r="B215" s="5"/>
       <c r="C215" s="6"/>
       <c r="D215" s="6"/>
       <c r="E215" s="6"/>
-      <c r="F215" s="6"/>
+      <c r="F215" s="7"/>
       <c r="G215" s="6"/>
       <c r="H215" s="6"/>
       <c r="I215" s="6"/>
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A216" s="6"/>
-      <c r="B216" s="6"/>
+      <c r="A216" s="5"/>
+      <c r="B216" s="5"/>
       <c r="C216" s="6"/>
       <c r="D216" s="6"/>
       <c r="E216" s="6"/>
-      <c r="F216" s="6"/>
+      <c r="F216" s="7"/>
       <c r="G216" s="6"/>
       <c r="H216" s="6"/>
       <c r="I216" s="6"/>
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A217" s="6"/>
-      <c r="B217" s="6"/>
+      <c r="A217" s="5"/>
+      <c r="B217" s="5"/>
       <c r="C217" s="6"/>
       <c r="D217" s="6"/>
       <c r="E217" s="6"/>
-      <c r="F217" s="6"/>
+      <c r="F217" s="7"/>
       <c r="G217" s="6"/>
       <c r="H217" s="6"/>
       <c r="I217" s="6"/>
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A218" s="6"/>
-      <c r="B218" s="6"/>
+      <c r="A218" s="5"/>
+      <c r="B218" s="5"/>
       <c r="C218" s="6"/>
       <c r="D218" s="6"/>
       <c r="E218" s="6"/>
-      <c r="F218" s="6"/>
+      <c r="F218" s="7"/>
       <c r="G218" s="6"/>
       <c r="H218" s="6"/>
       <c r="I218" s="6"/>
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A219" s="6"/>
-      <c r="B219" s="6"/>
+      <c r="A219" s="5"/>
+      <c r="B219" s="5"/>
       <c r="C219" s="6"/>
       <c r="D219" s="6"/>
       <c r="E219" s="6"/>
-      <c r="F219" s="6"/>
+      <c r="F219" s="7"/>
       <c r="G219" s="6"/>
       <c r="H219" s="6"/>
       <c r="I219" s="6"/>
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A220" s="6"/>
-      <c r="B220" s="6"/>
+      <c r="A220" s="5"/>
+      <c r="B220" s="5"/>
       <c r="C220" s="6"/>
       <c r="D220" s="6"/>
       <c r="E220" s="6"/>
-      <c r="F220" s="6"/>
+      <c r="F220" s="7"/>
       <c r="G220" s="6"/>
       <c r="H220" s="6"/>
       <c r="I220" s="6"/>
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A221" s="6"/>
-      <c r="B221" s="6"/>
+      <c r="A221" s="5"/>
+      <c r="B221" s="5"/>
       <c r="C221" s="6"/>
       <c r="D221" s="6"/>
       <c r="E221" s="6"/>
-      <c r="F221" s="6"/>
+      <c r="F221" s="7"/>
       <c r="G221" s="6"/>
       <c r="H221" s="6"/>
       <c r="I221" s="6"/>
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A222" s="6"/>
-      <c r="B222" s="6"/>
+      <c r="A222" s="5"/>
+      <c r="B222" s="5"/>
       <c r="C222" s="6"/>
       <c r="D222" s="6"/>
       <c r="E222" s="6"/>
-      <c r="F222" s="6"/>
+      <c r="F222" s="7"/>
       <c r="G222" s="6"/>
       <c r="H222" s="6"/>
       <c r="I222" s="6"/>
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A223" s="6"/>
-      <c r="B223" s="6"/>
+      <c r="A223" s="5"/>
+      <c r="B223" s="5"/>
       <c r="C223" s="6"/>
       <c r="D223" s="6"/>
       <c r="E223" s="6"/>
-      <c r="F223" s="6"/>
+      <c r="F223" s="7"/>
       <c r="G223" s="6"/>
       <c r="H223" s="6"/>
       <c r="I223" s="6"/>
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A224" s="6"/>
-      <c r="B224" s="6"/>
+      <c r="A224" s="5"/>
+      <c r="B224" s="5"/>
       <c r="C224" s="6"/>
       <c r="D224" s="6"/>
       <c r="E224" s="6"/>
-      <c r="F224" s="6"/>
+      <c r="F224" s="7"/>
       <c r="G224" s="6"/>
       <c r="H224" s="6"/>
       <c r="I224" s="6"/>
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A225" s="6"/>
-      <c r="B225" s="6"/>
+      <c r="A225" s="5"/>
+      <c r="B225" s="5"/>
       <c r="C225" s="6"/>
       <c r="D225" s="6"/>
       <c r="E225" s="6"/>
-      <c r="F225" s="6"/>
+      <c r="F225" s="7"/>
       <c r="G225" s="6"/>
       <c r="H225" s="6"/>
       <c r="I225" s="6"/>
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A226" s="6"/>
-      <c r="B226" s="6"/>
+      <c r="A226" s="5"/>
+      <c r="B226" s="5"/>
       <c r="C226" s="6"/>
       <c r="D226" s="6"/>
       <c r="E226" s="6"/>
-      <c r="F226" s="6"/>
+      <c r="F226" s="7"/>
       <c r="G226" s="6"/>
       <c r="H226" s="6"/>
       <c r="I226" s="6"/>
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A227" s="6"/>
-      <c r="B227" s="6"/>
+      <c r="A227" s="5"/>
+      <c r="B227" s="5"/>
       <c r="C227" s="6"/>
       <c r="D227" s="6"/>
       <c r="E227" s="6"/>
-      <c r="F227" s="6"/>
+      <c r="F227" s="7"/>
       <c r="G227" s="6"/>
       <c r="H227" s="6"/>
       <c r="I227" s="6"/>
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A228" s="6"/>
-      <c r="B228" s="6"/>
+      <c r="A228" s="5"/>
+      <c r="B228" s="5"/>
       <c r="C228" s="6"/>
       <c r="D228" s="6"/>
       <c r="E228" s="6"/>
-      <c r="F228" s="6"/>
+      <c r="F228" s="7"/>
       <c r="G228" s="6"/>
       <c r="H228" s="6"/>
       <c r="I228" s="6"/>
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A229" s="6"/>
-      <c r="B229" s="6"/>
+      <c r="A229" s="5"/>
+      <c r="B229" s="5"/>
       <c r="C229" s="6"/>
       <c r="D229" s="6"/>
       <c r="E229" s="6"/>
-      <c r="F229" s="6"/>
+      <c r="F229" s="7"/>
       <c r="G229" s="6"/>
       <c r="H229" s="6"/>
       <c r="I229" s="6"/>
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A230" s="6"/>
-      <c r="B230" s="6"/>
+      <c r="A230" s="5"/>
+      <c r="B230" s="5"/>
       <c r="C230" s="6"/>
       <c r="D230" s="6"/>
       <c r="E230" s="6"/>
-      <c r="F230" s="6"/>
+      <c r="F230" s="7"/>
       <c r="G230" s="6"/>
       <c r="H230" s="6"/>
       <c r="I230" s="6"/>
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A231" s="6"/>
-      <c r="B231" s="6"/>
+      <c r="A231" s="5"/>
+      <c r="B231" s="5"/>
       <c r="C231" s="6"/>
       <c r="D231" s="6"/>
       <c r="E231" s="6"/>
-      <c r="F231" s="6"/>
+      <c r="F231" s="7"/>
       <c r="G231" s="6"/>
       <c r="H231" s="6"/>
       <c r="I231" s="6"/>
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A232" s="6"/>
-      <c r="B232" s="6"/>
+      <c r="A232" s="5"/>
+      <c r="B232" s="5"/>
       <c r="C232" s="6"/>
       <c r="D232" s="6"/>
       <c r="E232" s="6"/>
-      <c r="F232" s="6"/>
+      <c r="F232" s="7"/>
       <c r="G232" s="6"/>
       <c r="H232" s="6"/>
       <c r="I232" s="6"/>
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A233" s="6"/>
-      <c r="B233" s="6"/>
+      <c r="A233" s="5"/>
+      <c r="B233" s="5"/>
       <c r="C233" s="6"/>
       <c r="D233" s="6"/>
       <c r="E233" s="6"/>
-      <c r="F233" s="6"/>
+      <c r="F233" s="7"/>
       <c r="G233" s="6"/>
       <c r="H233" s="6"/>
       <c r="I233" s="6"/>
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A234" s="6"/>
-      <c r="B234" s="6"/>
+      <c r="A234" s="5"/>
+      <c r="B234" s="5"/>
       <c r="C234" s="6"/>
       <c r="D234" s="6"/>
       <c r="E234" s="6"/>
-      <c r="F234" s="6"/>
+      <c r="F234" s="7"/>
       <c r="G234" s="6"/>
       <c r="H234" s="6"/>
       <c r="I234" s="6"/>
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A235" s="6"/>
-      <c r="B235" s="6"/>
+      <c r="A235" s="5"/>
+      <c r="B235" s="5"/>
       <c r="C235" s="6"/>
       <c r="D235" s="6"/>
       <c r="E235" s="6"/>
-      <c r="F235" s="6"/>
+      <c r="F235" s="7"/>
       <c r="G235" s="6"/>
       <c r="H235" s="6"/>
       <c r="I235" s="6"/>
     </row>
     <row r="236" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A236" s="6"/>
-      <c r="B236" s="6"/>
+      <c r="A236" s="5"/>
+      <c r="B236" s="5"/>
       <c r="C236" s="6"/>
       <c r="D236" s="6"/>
       <c r="E236" s="6"/>
-      <c r="F236" s="6"/>
+      <c r="F236" s="7"/>
       <c r="G236" s="6"/>
       <c r="H236" s="6"/>
       <c r="I236" s="6"/>
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A237" s="6"/>
-      <c r="B237" s="6"/>
+      <c r="A237" s="5"/>
+      <c r="B237" s="5"/>
       <c r="C237" s="6"/>
       <c r="D237" s="6"/>
       <c r="E237" s="6"/>
-      <c r="F237" s="6"/>
+      <c r="F237" s="7"/>
       <c r="G237" s="6"/>
       <c r="H237" s="6"/>
       <c r="I237" s="6"/>
     </row>
     <row r="238" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A238" s="6"/>
-      <c r="B238" s="6"/>
+      <c r="A238" s="5"/>
+      <c r="B238" s="5"/>
       <c r="C238" s="6"/>
       <c r="D238" s="6"/>
       <c r="E238" s="6"/>
-      <c r="F238" s="6"/>
+      <c r="F238" s="7"/>
       <c r="G238" s="6"/>
       <c r="H238" s="6"/>
       <c r="I238" s="6"/>
     </row>
     <row r="239" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A239" s="6"/>
-      <c r="B239" s="6"/>
+      <c r="A239" s="5"/>
+      <c r="B239" s="5"/>
       <c r="C239" s="6"/>
       <c r="D239" s="6"/>
       <c r="E239" s="6"/>
-      <c r="F239" s="6"/>
+      <c r="F239" s="7"/>
       <c r="G239" s="6"/>
       <c r="H239" s="6"/>
       <c r="I239" s="6"/>
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A240" s="6"/>
-      <c r="B240" s="6"/>
+      <c r="A240" s="5"/>
+      <c r="B240" s="5"/>
       <c r="C240" s="6"/>
       <c r="D240" s="6"/>
       <c r="E240" s="6"/>
-      <c r="F240" s="6"/>
+      <c r="F240" s="7"/>
       <c r="G240" s="6"/>
       <c r="H240" s="6"/>
       <c r="I240" s="6"/>
     </row>
     <row r="241" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A241" s="6"/>
-      <c r="B241" s="6"/>
+      <c r="A241" s="5"/>
+      <c r="B241" s="5"/>
       <c r="C241" s="6"/>
       <c r="D241" s="6"/>
       <c r="E241" s="6"/>
-      <c r="F241" s="6"/>
+      <c r="F241" s="7"/>
       <c r="G241" s="6"/>
       <c r="H241" s="6"/>
       <c r="I241" s="6"/>
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A242" s="6"/>
-      <c r="B242" s="6"/>
+      <c r="A242" s="5"/>
+      <c r="B242" s="5"/>
       <c r="C242" s="6"/>
       <c r="D242" s="6"/>
       <c r="E242" s="6"/>
-      <c r="F242" s="6"/>
+      <c r="F242" s="7"/>
       <c r="G242" s="6"/>
       <c r="H242" s="6"/>
       <c r="I242" s="6"/>
     </row>
     <row r="243" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A243" s="6"/>
-      <c r="B243" s="6"/>
+      <c r="A243" s="5"/>
+      <c r="B243" s="5"/>
       <c r="C243" s="6"/>
       <c r="D243" s="6"/>
       <c r="E243" s="6"/>
-      <c r="F243" s="6"/>
+      <c r="F243" s="7"/>
       <c r="G243" s="6"/>
       <c r="H243" s="6"/>
       <c r="I243" s="6"/>
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A244" s="6"/>
-      <c r="B244" s="6"/>
+      <c r="A244" s="5"/>
+      <c r="B244" s="5"/>
       <c r="C244" s="6"/>
       <c r="D244" s="6"/>
       <c r="E244" s="6"/>
-      <c r="F244" s="6"/>
+      <c r="F244" s="7"/>
       <c r="G244" s="6"/>
       <c r="H244" s="6"/>
       <c r="I244" s="6"/>
     </row>
     <row r="245" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A245" s="6"/>
-      <c r="B245" s="6"/>
+      <c r="A245" s="5"/>
+      <c r="B245" s="5"/>
       <c r="C245" s="6"/>
       <c r="D245" s="6"/>
       <c r="E245" s="6"/>
-      <c r="F245" s="6"/>
+      <c r="F245" s="7"/>
       <c r="G245" s="6"/>
       <c r="H245" s="6"/>
       <c r="I245" s="6"/>
     </row>
     <row r="246" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A246" s="6"/>
-      <c r="B246" s="6"/>
+      <c r="A246" s="5"/>
+      <c r="B246" s="5"/>
       <c r="C246" s="6"/>
       <c r="D246" s="6"/>
       <c r="E246" s="6"/>
-      <c r="F246" s="6"/>
+      <c r="F246" s="7"/>
       <c r="G246" s="6"/>
       <c r="H246" s="6"/>
       <c r="I246" s="6"/>
     </row>
     <row r="247" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A247" s="6"/>
-      <c r="B247" s="6"/>
+      <c r="A247" s="5"/>
+      <c r="B247" s="5"/>
       <c r="C247" s="6"/>
       <c r="D247" s="6"/>
       <c r="E247" s="6"/>
-      <c r="F247" s="6"/>
+      <c r="F247" s="7"/>
       <c r="G247" s="6"/>
       <c r="H247" s="6"/>
       <c r="I247" s="6"/>
     </row>
     <row r="248" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A248" s="6"/>
-      <c r="B248" s="6"/>
+      <c r="A248" s="5"/>
+      <c r="B248" s="5"/>
       <c r="C248" s="6"/>
       <c r="D248" s="6"/>
       <c r="E248" s="6"/>
-      <c r="F248" s="6"/>
+      <c r="F248" s="7"/>
       <c r="G248" s="6"/>
       <c r="H248" s="6"/>
       <c r="I248" s="6"/>
     </row>
     <row r="249" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A249" s="6"/>
-      <c r="B249" s="6"/>
+      <c r="A249" s="5"/>
+      <c r="B249" s="5"/>
       <c r="C249" s="6"/>
       <c r="D249" s="6"/>
       <c r="E249" s="6"/>
-      <c r="F249" s="6"/>
+      <c r="F249" s="7"/>
       <c r="G249" s="6"/>
       <c r="H249" s="6"/>
       <c r="I249" s="6"/>
     </row>
     <row r="250" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A250" s="6"/>
-      <c r="B250" s="6"/>
+      <c r="A250" s="5"/>
+      <c r="B250" s="5"/>
       <c r="C250" s="6"/>
       <c r="D250" s="6"/>
       <c r="E250" s="6"/>
-      <c r="F250" s="6"/>
+      <c r="F250" s="7"/>
       <c r="G250" s="6"/>
       <c r="H250" s="6"/>
       <c r="I250" s="6"/>
     </row>
     <row r="251" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A251" s="6"/>
-      <c r="B251" s="6"/>
+      <c r="A251" s="5"/>
+      <c r="B251" s="5"/>
       <c r="C251" s="6"/>
       <c r="D251" s="6"/>
       <c r="E251" s="6"/>
-      <c r="F251" s="6"/>
+      <c r="F251" s="7"/>
       <c r="G251" s="6"/>
       <c r="H251" s="6"/>
       <c r="I251" s="6"/>
     </row>
     <row r="252" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A252" s="6"/>
-      <c r="B252" s="6"/>
+      <c r="A252" s="5"/>
+      <c r="B252" s="5"/>
       <c r="C252" s="6"/>
       <c r="D252" s="6"/>
       <c r="E252" s="6"/>
-      <c r="F252" s="6"/>
+      <c r="F252" s="7"/>
       <c r="G252" s="6"/>
       <c r="H252" s="6"/>
       <c r="I252" s="6"/>
     </row>
     <row r="253" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A253" s="6"/>
-      <c r="B253" s="6"/>
+      <c r="A253" s="5"/>
+      <c r="B253" s="5"/>
       <c r="C253" s="6"/>
       <c r="D253" s="6"/>
       <c r="E253" s="6"/>
-      <c r="F253" s="6"/>
+      <c r="F253" s="7"/>
       <c r="G253" s="6"/>
       <c r="H253" s="6"/>
       <c r="I253" s="6"/>
     </row>
     <row r="254" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A254" s="6"/>
-      <c r="B254" s="6"/>
+      <c r="A254" s="5"/>
+      <c r="B254" s="5"/>
       <c r="C254" s="6"/>
       <c r="D254" s="6"/>
       <c r="E254" s="6"/>
-      <c r="F254" s="6"/>
+      <c r="F254" s="7"/>
       <c r="G254" s="6"/>
       <c r="H254" s="6"/>
       <c r="I254" s="6"/>
     </row>
     <row r="255" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A255" s="6"/>
-      <c r="B255" s="6"/>
+      <c r="A255" s="5"/>
+      <c r="B255" s="5"/>
       <c r="C255" s="6"/>
       <c r="D255" s="6"/>
       <c r="E255" s="6"/>
-      <c r="F255" s="6"/>
+      <c r="F255" s="7"/>
       <c r="G255" s="6"/>
       <c r="H255" s="6"/>
       <c r="I255" s="6"/>
     </row>
     <row r="256" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A256" s="6"/>
-      <c r="B256" s="6"/>
+      <c r="A256" s="5"/>
+      <c r="B256" s="5"/>
       <c r="C256" s="6"/>
       <c r="D256" s="6"/>
       <c r="E256" s="6"/>
-      <c r="F256" s="6"/>
+      <c r="F256" s="7"/>
       <c r="G256" s="6"/>
       <c r="H256" s="6"/>
       <c r="I256" s="6"/>
     </row>
     <row r="257" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A257" s="6"/>
-      <c r="B257" s="6"/>
+      <c r="A257" s="5"/>
+      <c r="B257" s="5"/>
       <c r="C257" s="6"/>
       <c r="D257" s="6"/>
       <c r="E257" s="6"/>
-      <c r="F257" s="6"/>
+      <c r="F257" s="7"/>
       <c r="G257" s="6"/>
       <c r="H257" s="6"/>
       <c r="I257" s="6"/>
     </row>
     <row r="258" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A258" s="6"/>
-      <c r="B258" s="6"/>
+      <c r="A258" s="5"/>
+      <c r="B258" s="5"/>
       <c r="C258" s="6"/>
       <c r="D258" s="6"/>
       <c r="E258" s="6"/>
-      <c r="F258" s="6"/>
+      <c r="F258" s="7"/>
       <c r="G258" s="6"/>
       <c r="H258" s="6"/>
       <c r="I258" s="6"/>
     </row>
     <row r="259" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A259" s="6"/>
-      <c r="B259" s="6"/>
+      <c r="A259" s="5"/>
+      <c r="B259" s="5"/>
       <c r="C259" s="6"/>
       <c r="D259" s="6"/>
       <c r="E259" s="6"/>
-      <c r="F259" s="6"/>
+      <c r="F259" s="7"/>
       <c r="G259" s="6"/>
       <c r="H259" s="6"/>
       <c r="I259" s="6"/>
     </row>
     <row r="260" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A260" s="6"/>
-      <c r="B260" s="6"/>
+      <c r="A260" s="5"/>
+      <c r="B260" s="5"/>
       <c r="C260" s="6"/>
       <c r="D260" s="6"/>
       <c r="E260" s="6"/>
-      <c r="F260" s="6"/>
+      <c r="F260" s="7"/>
       <c r="G260" s="6"/>
       <c r="H260" s="6"/>
       <c r="I260" s="6"/>
     </row>
     <row r="261" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A261" s="6"/>
-      <c r="B261" s="6"/>
+      <c r="A261" s="5"/>
+      <c r="B261" s="5"/>
       <c r="C261" s="6"/>
       <c r="D261" s="6"/>
       <c r="E261" s="6"/>
-      <c r="F261" s="6"/>
+      <c r="F261" s="7"/>
       <c r="G261" s="6"/>
       <c r="H261" s="6"/>
       <c r="I261" s="6"/>
     </row>
     <row r="262" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A262" s="6"/>
-      <c r="B262" s="6"/>
+      <c r="A262" s="5"/>
+      <c r="B262" s="5"/>
       <c r="C262" s="6"/>
       <c r="D262" s="6"/>
       <c r="E262" s="6"/>
-      <c r="F262" s="6"/>
+      <c r="F262" s="7"/>
       <c r="G262" s="6"/>
       <c r="H262" s="6"/>
       <c r="I262" s="6"/>
     </row>
     <row r="263" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A263" s="6"/>
-      <c r="B263" s="6"/>
+      <c r="A263" s="5"/>
+      <c r="B263" s="5"/>
       <c r="C263" s="6"/>
       <c r="D263" s="6"/>
       <c r="E263" s="6"/>
-      <c r="F263" s="6"/>
+      <c r="F263" s="7"/>
       <c r="G263" s="6"/>
       <c r="H263" s="6"/>
       <c r="I263" s="6"/>
     </row>
     <row r="264" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A264" s="6"/>
-      <c r="B264" s="6"/>
+      <c r="A264" s="5"/>
+      <c r="B264" s="5"/>
       <c r="C264" s="6"/>
       <c r="D264" s="6"/>
       <c r="E264" s="6"/>
-      <c r="F264" s="6"/>
+      <c r="F264" s="7"/>
       <c r="G264" s="6"/>
       <c r="H264" s="6"/>
       <c r="I264" s="6"/>
     </row>
     <row r="265" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A265" s="6"/>
-      <c r="B265" s="6"/>
+      <c r="A265" s="5"/>
+      <c r="B265" s="5"/>
       <c r="C265" s="6"/>
       <c r="D265" s="6"/>
       <c r="E265" s="6"/>
-      <c r="F265" s="6"/>
+      <c r="F265" s="7"/>
       <c r="G265" s="6"/>
       <c r="H265" s="6"/>
       <c r="I265" s="6"/>
     </row>
     <row r="266" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A266" s="6"/>
-      <c r="B266" s="6"/>
+      <c r="A266" s="5"/>
+      <c r="B266" s="5"/>
       <c r="C266" s="6"/>
       <c r="D266" s="6"/>
       <c r="E266" s="6"/>
-      <c r="F266" s="6"/>
+      <c r="F266" s="7"/>
       <c r="G266" s="6"/>
       <c r="H266" s="6"/>
       <c r="I266" s="6"/>
     </row>
     <row r="267" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A267" s="6"/>
-      <c r="B267" s="6"/>
+      <c r="A267" s="5"/>
+      <c r="B267" s="5"/>
       <c r="C267" s="6"/>
       <c r="D267" s="6"/>
       <c r="E267" s="6"/>
-      <c r="F267" s="6"/>
+      <c r="F267" s="7"/>
       <c r="G267" s="6"/>
       <c r="H267" s="6"/>
       <c r="I267" s="6"/>
     </row>
     <row r="268" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A268" s="6"/>
-      <c r="B268" s="6"/>
+      <c r="A268" s="5"/>
+      <c r="B268" s="5"/>
       <c r="C268" s="6"/>
       <c r="D268" s="6"/>
       <c r="E268" s="6"/>
-      <c r="F268" s="6"/>
+      <c r="F268" s="7"/>
       <c r="G268" s="6"/>
       <c r="H268" s="6"/>
       <c r="I268" s="6"/>
     </row>
     <row r="269" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A269" s="6"/>
-      <c r="B269" s="6"/>
+      <c r="A269" s="5"/>
+      <c r="B269" s="5"/>
       <c r="C269" s="6"/>
       <c r="D269" s="6"/>
       <c r="E269" s="6"/>
-      <c r="F269" s="6"/>
+      <c r="F269" s="7"/>
       <c r="G269" s="6"/>
       <c r="H269" s="6"/>
       <c r="I269" s="6"/>
     </row>
     <row r="270" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A270" s="6"/>
-      <c r="B270" s="6"/>
+      <c r="A270" s="5"/>
+      <c r="B270" s="5"/>
       <c r="C270" s="6"/>
       <c r="D270" s="6"/>
       <c r="E270" s="6"/>
-      <c r="F270" s="6"/>
+      <c r="F270" s="7"/>
       <c r="G270" s="6"/>
       <c r="H270" s="6"/>
       <c r="I270" s="6"/>
     </row>
     <row r="271" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A271" s="6"/>
-      <c r="B271" s="6"/>
+      <c r="A271" s="5"/>
+      <c r="B271" s="5"/>
       <c r="C271" s="6"/>
       <c r="D271" s="6"/>
       <c r="E271" s="6"/>
-      <c r="F271" s="6"/>
+      <c r="F271" s="7"/>
       <c r="G271" s="6"/>
       <c r="H271" s="6"/>
       <c r="I271" s="6"/>
     </row>
     <row r="272" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A272" s="6"/>
-      <c r="B272" s="6"/>
+      <c r="A272" s="5"/>
+      <c r="B272" s="5"/>
       <c r="C272" s="6"/>
       <c r="D272" s="6"/>
       <c r="E272" s="6"/>
-      <c r="F272" s="6"/>
+      <c r="F272" s="7"/>
       <c r="G272" s="6"/>
       <c r="H272" s="6"/>
       <c r="I272" s="6"/>
     </row>
     <row r="273" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A273" s="6"/>
-      <c r="B273" s="6"/>
+      <c r="A273" s="5"/>
+      <c r="B273" s="5"/>
       <c r="C273" s="6"/>
       <c r="D273" s="6"/>
       <c r="E273" s="6"/>
-      <c r="F273" s="6"/>
+      <c r="F273" s="7"/>
       <c r="G273" s="6"/>
       <c r="H273" s="6"/>
       <c r="I273" s="6"/>
     </row>
     <row r="274" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A274" s="6"/>
-      <c r="B274" s="6"/>
+      <c r="A274" s="5"/>
+      <c r="B274" s="5"/>
       <c r="C274" s="6"/>
       <c r="D274" s="6"/>
       <c r="E274" s="6"/>
-      <c r="F274" s="6"/>
+      <c r="F274" s="7"/>
       <c r="G274" s="6"/>
       <c r="H274" s="6"/>
       <c r="I274" s="6"/>
     </row>
     <row r="275" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A275" s="6"/>
-      <c r="B275" s="6"/>
+      <c r="A275" s="5"/>
+      <c r="B275" s="5"/>
       <c r="C275" s="6"/>
       <c r="D275" s="6"/>
       <c r="E275" s="6"/>
-      <c r="F275" s="6"/>
+      <c r="F275" s="7"/>
       <c r="G275" s="6"/>
       <c r="H275" s="6"/>
       <c r="I275" s="6"/>
     </row>
     <row r="276" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A276" s="6"/>
-      <c r="B276" s="6"/>
+      <c r="A276" s="5"/>
+      <c r="B276" s="5"/>
       <c r="C276" s="6"/>
       <c r="D276" s="6"/>
       <c r="E276" s="6"/>
-      <c r="F276" s="6"/>
+      <c r="F276" s="7"/>
       <c r="G276" s="6"/>
       <c r="H276" s="6"/>
       <c r="I276" s="6"/>
     </row>
     <row r="277" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A277" s="6"/>
-      <c r="B277" s="6"/>
+      <c r="A277" s="5"/>
+      <c r="B277" s="5"/>
       <c r="C277" s="6"/>
       <c r="D277" s="6"/>
       <c r="E277" s="6"/>
-      <c r="F277" s="6"/>
+      <c r="F277" s="7"/>
       <c r="G277" s="6"/>
       <c r="H277" s="6"/>
       <c r="I277" s="6"/>
     </row>
     <row r="278" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A278" s="6"/>
-      <c r="B278" s="6"/>
+      <c r="A278" s="5"/>
+      <c r="B278" s="5"/>
       <c r="C278" s="6"/>
       <c r="D278" s="6"/>
       <c r="E278" s="6"/>
-      <c r="F278" s="6"/>
+      <c r="F278" s="7"/>
       <c r="G278" s="6"/>
       <c r="H278" s="6"/>
       <c r="I278" s="6"/>
     </row>
     <row r="279" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A279" s="6"/>
-      <c r="B279" s="6"/>
+      <c r="A279" s="5"/>
+      <c r="B279" s="5"/>
       <c r="C279" s="6"/>
       <c r="D279" s="6"/>
       <c r="E279" s="6"/>
-      <c r="F279" s="6"/>
+      <c r="F279" s="7"/>
       <c r="G279" s="6"/>
       <c r="H279" s="6"/>
       <c r="I279" s="6"/>
     </row>
     <row r="280" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A280" s="6"/>
-      <c r="B280" s="6"/>
+      <c r="A280" s="5"/>
+      <c r="B280" s="5"/>
       <c r="C280" s="6"/>
       <c r="D280" s="6"/>
       <c r="E280" s="6"/>
-      <c r="F280" s="6"/>
+      <c r="F280" s="7"/>
       <c r="G280" s="6"/>
       <c r="H280" s="6"/>
       <c r="I280" s="6"/>
     </row>
     <row r="281" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A281" s="6"/>
-      <c r="B281" s="6"/>
+      <c r="A281" s="5"/>
+      <c r="B281" s="5"/>
       <c r="C281" s="6"/>
       <c r="D281" s="6"/>
       <c r="E281" s="6"/>
-      <c r="F281" s="6"/>
+      <c r="F281" s="7"/>
       <c r="G281" s="6"/>
       <c r="H281" s="6"/>
       <c r="I281" s="6"/>
     </row>
     <row r="282" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A282" s="6"/>
-      <c r="B282" s="6"/>
+      <c r="A282" s="5"/>
+      <c r="B282" s="5"/>
       <c r="C282" s="6"/>
       <c r="D282" s="6"/>
       <c r="E282" s="6"/>
-      <c r="F282" s="6"/>
+      <c r="F282" s="7"/>
       <c r="G282" s="6"/>
       <c r="H282" s="6"/>
       <c r="I282" s="6"/>
     </row>
     <row r="283" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A283" s="6"/>
-      <c r="B283" s="6"/>
+      <c r="A283" s="5"/>
+      <c r="B283" s="5"/>
       <c r="C283" s="6"/>
       <c r="D283" s="6"/>
       <c r="E283" s="6"/>
-      <c r="F283" s="6"/>
+      <c r="F283" s="7"/>
       <c r="G283" s="6"/>
       <c r="H283" s="6"/>
       <c r="I283" s="6"/>
     </row>
     <row r="284" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A284" s="6"/>
-      <c r="B284" s="6"/>
+      <c r="A284" s="5"/>
+      <c r="B284" s="5"/>
       <c r="C284" s="6"/>
       <c r="D284" s="6"/>
       <c r="E284" s="6"/>
-      <c r="F284" s="6"/>
+      <c r="F284" s="7"/>
       <c r="G284" s="6"/>
       <c r="H284" s="6"/>
       <c r="I284" s="6"/>
     </row>
     <row r="285" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A285" s="6"/>
-      <c r="B285" s="6"/>
+      <c r="A285" s="5"/>
+      <c r="B285" s="5"/>
       <c r="C285" s="6"/>
       <c r="D285" s="6"/>
       <c r="E285" s="6"/>
-      <c r="F285" s="6"/>
+      <c r="F285" s="7"/>
       <c r="G285" s="6"/>
       <c r="H285" s="6"/>
       <c r="I285" s="6"/>
     </row>
     <row r="286" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A286" s="6"/>
-      <c r="B286" s="6"/>
+      <c r="A286" s="5"/>
+      <c r="B286" s="5"/>
       <c r="C286" s="6"/>
       <c r="D286" s="6"/>
       <c r="E286" s="6"/>
-      <c r="F286" s="6"/>
+      <c r="F286" s="7"/>
       <c r="G286" s="6"/>
       <c r="H286" s="6"/>
       <c r="I286" s="6"/>
     </row>
     <row r="287" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A287" s="6"/>
-      <c r="B287" s="6"/>
+      <c r="A287" s="5"/>
+      <c r="B287" s="5"/>
       <c r="C287" s="6"/>
       <c r="D287" s="6"/>
       <c r="E287" s="6"/>
-      <c r="F287" s="6"/>
+      <c r="F287" s="7"/>
       <c r="G287" s="6"/>
       <c r="H287" s="6"/>
       <c r="I287" s="6"/>
     </row>
     <row r="288" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A288" s="6"/>
-      <c r="B288" s="6"/>
+      <c r="A288" s="5"/>
+      <c r="B288" s="5"/>
       <c r="C288" s="6"/>
       <c r="D288" s="6"/>
       <c r="E288" s="6"/>
-      <c r="F288" s="6"/>
+      <c r="F288" s="7"/>
       <c r="G288" s="6"/>
       <c r="H288" s="6"/>
       <c r="I288" s="6"/>
     </row>
     <row r="289" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A289" s="6"/>
-      <c r="B289" s="6"/>
+      <c r="A289" s="5"/>
+      <c r="B289" s="5"/>
       <c r="C289" s="6"/>
       <c r="D289" s="6"/>
       <c r="E289" s="6"/>
-      <c r="F289" s="6"/>
+      <c r="F289" s="7"/>
       <c r="G289" s="6"/>
       <c r="H289" s="6"/>
       <c r="I289" s="6"/>
     </row>
     <row r="290" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A290" s="6"/>
-      <c r="B290" s="6"/>
+      <c r="A290" s="5"/>
+      <c r="B290" s="5"/>
       <c r="C290" s="6"/>
       <c r="D290" s="6"/>
       <c r="E290" s="6"/>
-      <c r="F290" s="6"/>
+      <c r="F290" s="7"/>
       <c r="G290" s="6"/>
       <c r="H290" s="6"/>
       <c r="I290" s="6"/>
     </row>
     <row r="291" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A291" s="6"/>
-      <c r="B291" s="6"/>
+      <c r="A291" s="5"/>
+      <c r="B291" s="5"/>
       <c r="C291" s="6"/>
       <c r="D291" s="6"/>
       <c r="E291" s="6"/>
-      <c r="F291" s="6"/>
+      <c r="F291" s="7"/>
       <c r="G291" s="6"/>
       <c r="H291" s="6"/>
       <c r="I291" s="6"/>
     </row>
     <row r="292" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A292" s="6"/>
-      <c r="B292" s="6"/>
+      <c r="A292" s="5"/>
+      <c r="B292" s="5"/>
       <c r="C292" s="6"/>
       <c r="D292" s="6"/>
       <c r="E292" s="6"/>
-      <c r="F292" s="6"/>
+      <c r="F292" s="7"/>
       <c r="G292" s="6"/>
       <c r="H292" s="6"/>
       <c r="I292" s="6"/>
     </row>
     <row r="293" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A293" s="6"/>
-      <c r="B293" s="6"/>
+      <c r="A293" s="5"/>
+      <c r="B293" s="5"/>
       <c r="C293" s="6"/>
       <c r="D293" s="6"/>
       <c r="E293" s="6"/>
-      <c r="F293" s="6"/>
+      <c r="F293" s="7"/>
       <c r="G293" s="6"/>
       <c r="H293" s="6"/>
       <c r="I293" s="6"/>
     </row>
     <row r="294" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A294" s="6"/>
-      <c r="B294" s="6"/>
+      <c r="A294" s="5"/>
+      <c r="B294" s="5"/>
       <c r="C294" s="6"/>
       <c r="D294" s="6"/>
       <c r="E294" s="6"/>
-      <c r="F294" s="6"/>
+      <c r="F294" s="7"/>
       <c r="G294" s="6"/>
       <c r="H294" s="6"/>
       <c r="I294" s="6"/>
     </row>
     <row r="295" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A295" s="6"/>
-      <c r="B295" s="6"/>
+      <c r="A295" s="5"/>
+      <c r="B295" s="5"/>
       <c r="C295" s="6"/>
       <c r="D295" s="6"/>
       <c r="E295" s="6"/>
-      <c r="F295" s="6"/>
+      <c r="F295" s="7"/>
       <c r="G295" s="6"/>
       <c r="H295" s="6"/>
       <c r="I295" s="6"/>
@@ -4452,57 +4775,45 @@
       <c r="H302" s="6"/>
       <c r="I302" s="6"/>
     </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A303" s="5"/>
-      <c r="B303" s="5"/>
-      <c r="C303" s="6"/>
-      <c r="D303" s="6"/>
-      <c r="E303" s="6"/>
-      <c r="F303" s="7"/>
-      <c r="G303" s="6"/>
-      <c r="H303" s="6"/>
-      <c r="I303" s="6"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I303" xr:uid="{00000000-0009-0000-0000-000001000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I303">
-      <sortCondition ref="B1:B303"/>
-    </sortState>
-  </autoFilter>
-  <conditionalFormatting sqref="E2:E303">
-    <cfRule type="expression" dxfId="6" priority="1">
+  <autoFilter ref="A1:I302" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <conditionalFormatting sqref="E2:E302">
+    <cfRule type="expression" dxfId="49" priority="1">
       <formula>$E2="Competición FPCV"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="2">
+    <cfRule type="expression" dxfId="48" priority="2">
       <formula>$E2="Campeonato de España"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="3">
+    <cfRule type="expression" dxfId="47" priority="3">
       <formula>$E2="Competición Internacional"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="4">
+    <cfRule type="expression" dxfId="46" priority="4">
       <formula>$E2="Trofeo Club"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="5">
+    <cfRule type="expression" dxfId="45" priority="5">
       <formula>$E2="Curso"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="6">
+    <cfRule type="expression" dxfId="44" priority="6">
       <formula>$E2="Reunión"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="7">
+    <cfRule type="expression" dxfId="43" priority="7">
       <formula>$E2="Prueba de Acceso"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="42" priority="8">
+      <formula>$E2="Día festivo"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" errorTitle="Valor no válido" error="Elige una categoría de la lista" sqref="E2:E21 E24:E303" xr:uid="{00000000-0002-0000-0100-000000000000}">
-      <formula1>"Competición FPCV,Campeonato de España,Competición Internacional,Trofeo Club,Curso,Reunión,Prueba de Acceso"</formula1>
+    <dataValidation type="list" allowBlank="1" errorTitle="Valor no válido" error="Elige una categoría de la lista" sqref="E2:E302" xr:uid="{00000000-0002-0000-0100-000000000000}">
+      <formula1>"Competición FPCV,Campeonato de España,Competición Internacional,Trofeo Club,Curso,Reunión,Prueba de Acceso,Día festivo"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" errorTitle="Valor no válido" error="Huecos: pon 0, 1 o 2" sqref="F2:F21 F24:F303" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" errorTitle="Valor no válido" error="Huecos: pon 0, 1 o 2" sqref="F2:F302" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"0,1,2"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" errorTitle="Valor no válido" error="Elige Mañana, Tarde o Todo el día" sqref="G2:I21 G24:I303 H22" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" errorTitle="Valor no válido" error="Elige Mañana, Tarde o Todo el día" sqref="G2:I302" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"Mañana,Tarde,Todo el día"</formula1>
     </dataValidation>
-    <dataValidation type="date" operator="greaterThan" allowBlank="1" errorTitle="Fecha" error="Escribe una fecha, por ejemplo 17/10/2026" sqref="A24:B303 A2:B21" xr:uid="{00000000-0002-0000-0100-000003000000}">
+    <dataValidation type="date" operator="greaterThan" allowBlank="1" errorTitle="Fecha" error="Escribe una fecha, por ejemplo 17/10/2026" sqref="A2:B302" xr:uid="{00000000-0002-0000-0100-000003000000}">
       <formula1>36526</formula1>
     </dataValidation>
   </dataValidations>

--- a/calendario-fpcv-eventos.xlsx
+++ b/calendario-fpcv-eventos.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bea Pallero\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5bbe44e6a3b5fd34/Federación/EVENTOS AÑO 2026/Trofeos Clubes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D398B8E-8F88-483F-8CEF-2E75185AB50A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{4D398B8E-8F88-483F-8CEF-2E75185AB50A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{34DDF576-3AC8-450A-A6F3-64F2FE57B9D2}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,14 +17,14 @@
     <sheet name="Eventos" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Eventos!$A$1:$I$302</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Eventos!$A$1:$I$305</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="76">
   <si>
     <t>Inicio</t>
   </si>
@@ -231,6 +231,27 @@
   </si>
   <si>
     <t>Día de la Constitución</t>
+  </si>
+  <si>
+    <t>Día de Todos los Santos</t>
+  </si>
+  <si>
+    <t>Prueba Danza y Libre</t>
+  </si>
+  <si>
+    <t>World Skate Games</t>
+  </si>
+  <si>
+    <t>3ª Prueba Acceso Categoría Territorial</t>
+  </si>
+  <si>
+    <t>L'Alcudia de Crespins</t>
+  </si>
+  <si>
+    <t>Asunción</t>
+  </si>
+  <si>
+    <t>Quart</t>
   </si>
 </sst>
 </file>
@@ -323,343 +344,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="50">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE3EBCB"/>
-          <bgColor rgb="FFE3EBCB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE1E6EB"/>
-          <bgColor rgb="FFE1E6EB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCDEBE7"/>
-          <bgColor rgb="FFCDEBE7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCEBCB"/>
-          <bgColor rgb="FFFCEBCB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE8D5F5"/>
-          <bgColor rgb="FFE8D5F5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD5E3FA"/>
-          <bgColor rgb="FFD5E3FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFBD9DF"/>
-          <bgColor rgb="FFFBD9DF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE3EBCB"/>
-          <bgColor rgb="FFE3EBCB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE1E6EB"/>
-          <bgColor rgb="FFE1E6EB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCDEBE7"/>
-          <bgColor rgb="FFCDEBE7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCEBCB"/>
-          <bgColor rgb="FFFCEBCB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE8D5F5"/>
-          <bgColor rgb="FFE8D5F5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD5E3FA"/>
-          <bgColor rgb="FFD5E3FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFBD9DF"/>
-          <bgColor rgb="FFFBD9DF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE3EBCB"/>
-          <bgColor rgb="FFE3EBCB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE1E6EB"/>
-          <bgColor rgb="FFE1E6EB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCDEBE7"/>
-          <bgColor rgb="FFCDEBE7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCEBCB"/>
-          <bgColor rgb="FFFCEBCB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE8D5F5"/>
-          <bgColor rgb="FFE8D5F5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD5E3FA"/>
-          <bgColor rgb="FFD5E3FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFBD9DF"/>
-          <bgColor rgb="FFFBD9DF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE3EBCB"/>
-          <bgColor rgb="FFE3EBCB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE1E6EB"/>
-          <bgColor rgb="FFE1E6EB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCDEBE7"/>
-          <bgColor rgb="FFCDEBE7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCEBCB"/>
-          <bgColor rgb="FFFCEBCB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE8D5F5"/>
-          <bgColor rgb="FFE8D5F5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD5E3FA"/>
-          <bgColor rgb="FFD5E3FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFBD9DF"/>
-          <bgColor rgb="FFFBD9DF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE3EBCB"/>
-          <bgColor rgb="FFE3EBCB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE1E6EB"/>
-          <bgColor rgb="FFE1E6EB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCDEBE7"/>
-          <bgColor rgb="FFCDEBE7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCEBCB"/>
-          <bgColor rgb="FFFCEBCB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE8D5F5"/>
-          <bgColor rgb="FFE8D5F5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD5E3FA"/>
-          <bgColor rgb="FFD5E3FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFBD9DF"/>
-          <bgColor rgb="FFFBD9DF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE3EBCB"/>
-          <bgColor rgb="FFE3EBCB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE1E6EB"/>
-          <bgColor rgb="FFE1E6EB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCDEBE7"/>
-          <bgColor rgb="FFCDEBE7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCEBCB"/>
-          <bgColor rgb="FFFCEBCB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE8D5F5"/>
-          <bgColor rgb="FFE8D5F5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD5E3FA"/>
-          <bgColor rgb="FFD5E3FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFBD9DF"/>
-          <bgColor rgb="FFFBD9DF"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="8">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1154,7 +839,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I302"/>
+  <dimension ref="A1:I305"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="13" customWidth="1"/>
@@ -1196,16 +881,16 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="5">
-        <v>46311</v>
+        <v>46298</v>
       </c>
       <c r="B2" s="5">
-        <v>46313</v>
+        <v>46298</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>11</v>
+        <v>73</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>17</v>
@@ -1214,23 +899,21 @@
         <v>0</v>
       </c>
       <c r="G2" s="6"/>
-      <c r="H2" s="6" t="s">
-        <v>47</v>
-      </c>
+      <c r="H2" s="6"/>
       <c r="I2" s="6"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
-        <v>46312</v>
+        <v>46301</v>
       </c>
       <c r="B3" s="5">
-        <v>46319</v>
+        <v>46313</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>50</v>
@@ -1249,16 +932,16 @@
         <v>46312</v>
       </c>
       <c r="B4" s="5">
-        <v>46313</v>
+        <v>46312</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F4" s="7">
         <v>1</v>
@@ -1267,22 +950,20 @@
       <c r="H4" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I4" s="6" t="s">
-        <v>52</v>
-      </c>
+      <c r="I4" s="6"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
-        <v>46320</v>
+        <v>46311</v>
       </c>
       <c r="B5" s="5">
-        <v>46320</v>
+        <v>46313</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>53</v>
+        <v>11</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>17</v>
@@ -1298,22 +979,22 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
-        <v>46319</v>
+        <v>46312</v>
       </c>
       <c r="B6" s="5">
         <v>46319</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="F6" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G6" s="6"/>
       <c r="H6" s="6" t="s">
@@ -1323,45 +1004,49 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
-        <v>46327</v>
+        <v>46312</v>
       </c>
       <c r="B7" s="5">
-        <v>46327</v>
+        <v>46313</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D7" s="6"/>
+        <v>51</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>16</v>
+      </c>
       <c r="E7" s="6" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="F7" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7" s="6"/>
       <c r="H7" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I7" s="6"/>
+      <c r="I7" s="6" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
-        <v>46333</v>
+        <v>46320</v>
       </c>
       <c r="B8" s="5">
-        <v>46333</v>
+        <v>46320</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="F8" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" s="6"/>
       <c r="H8" s="6" t="s">
@@ -1371,22 +1056,22 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
-        <v>46333</v>
+        <v>46319</v>
       </c>
       <c r="B9" s="5">
-        <v>46333</v>
+        <v>46319</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="F9" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G9" s="6"/>
       <c r="H9" s="6" t="s">
@@ -1396,22 +1081,20 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="5">
-        <v>46333</v>
+        <v>46327</v>
       </c>
       <c r="B10" s="5">
-        <v>46334</v>
+        <v>46327</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>58</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="D10" s="6"/>
       <c r="E10" s="6" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="F10" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G10" s="6"/>
       <c r="H10" s="6" t="s">
@@ -1421,16 +1104,16 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
-        <v>46339</v>
+        <v>46333</v>
       </c>
       <c r="B11" s="5">
-        <v>46339</v>
+        <v>46333</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>9</v>
@@ -1438,30 +1121,30 @@
       <c r="F11" s="7">
         <v>1</v>
       </c>
-      <c r="G11" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="H11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6" t="s">
+        <v>47</v>
+      </c>
       <c r="I11" s="6"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
-        <v>46340</v>
+        <v>46333</v>
       </c>
       <c r="B12" s="5">
-        <v>46340</v>
+        <v>46333</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F12" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G12" s="6"/>
       <c r="H12" s="6" t="s">
@@ -1471,22 +1154,22 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
-        <v>46347</v>
+        <v>46333</v>
       </c>
       <c r="B13" s="5">
-        <v>46347</v>
+        <v>46334</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>62</v>
+        <v>18</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="F13" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" s="6"/>
       <c r="H13" s="6" t="s">
@@ -1496,16 +1179,16 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="5">
-        <v>46347</v>
+        <v>46339</v>
       </c>
       <c r="B14" s="5">
-        <v>46347</v>
+        <v>46339</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>9</v>
@@ -1513,28 +1196,30 @@
       <c r="F14" s="7">
         <v>1</v>
       </c>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6" t="s">
-        <v>47</v>
-      </c>
+      <c r="G14" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="H14" s="6"/>
       <c r="I14" s="6"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
-        <v>46347</v>
+        <v>46340</v>
       </c>
       <c r="B15" s="5">
-        <v>46348</v>
+        <v>46340</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="6"/>
+        <v>19</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>11</v>
+      </c>
       <c r="E15" s="6" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F15" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G15" s="6"/>
       <c r="H15" s="6" t="s">
@@ -1544,45 +1229,47 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="5">
-        <v>46354</v>
+        <v>46347</v>
       </c>
       <c r="B16" s="5">
-        <v>46354</v>
+        <v>46347</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="F16" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="6" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="I16" s="6"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
-        <v>46354</v>
+        <v>46347</v>
       </c>
       <c r="B17" s="5">
-        <v>46355</v>
+        <v>46347</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D17" s="6"/>
+        <v>64</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>58</v>
+      </c>
       <c r="E17" s="6" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="F17" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" s="6"/>
       <c r="H17" s="6" t="s">
@@ -1592,20 +1279,20 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="5">
-        <v>46355</v>
+        <v>46347</v>
       </c>
       <c r="B18" s="5">
-        <v>46355</v>
+        <v>46348</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="D18" s="6"/>
       <c r="E18" s="6" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F18" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G18" s="6"/>
       <c r="H18" s="6" t="s">
@@ -1615,43 +1302,45 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
-        <v>46362</v>
+        <v>46354</v>
       </c>
       <c r="B19" s="5">
-        <v>46362</v>
+        <v>46354</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="D19" s="6"/>
+        <v>22</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>23</v>
+      </c>
       <c r="E19" s="6" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="F19" s="7">
         <v>2</v>
       </c>
       <c r="G19" s="6"/>
       <c r="H19" s="6" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="I19" s="6"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="5">
-        <v>46368</v>
+        <v>46354</v>
       </c>
       <c r="B20" s="5">
-        <v>46368</v>
+        <v>46355</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D20" s="6"/>
       <c r="E20" s="6" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F20" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20" s="6"/>
       <c r="H20" s="6" t="s">
@@ -1661,22 +1350,20 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
-        <v>46397</v>
+        <v>46355</v>
       </c>
       <c r="B21" s="5">
-        <v>46397</v>
+        <v>46355</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>67</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="D21" s="6"/>
       <c r="E21" s="6" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="F21" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G21" s="6"/>
       <c r="H21" s="6" t="s">
@@ -1685,36 +1372,74 @@
       <c r="I21" s="6"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="5"/>
-      <c r="B22" s="5"/>
-      <c r="C22" s="6"/>
+      <c r="A22" s="5">
+        <v>46362</v>
+      </c>
+      <c r="B22" s="5">
+        <v>46362</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>68</v>
+      </c>
       <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="7"/>
+      <c r="E22" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F22" s="7">
+        <v>2</v>
+      </c>
       <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
+      <c r="H22" s="6" t="s">
+        <v>47</v>
+      </c>
       <c r="I22" s="6"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="5"/>
-      <c r="B23" s="5"/>
-      <c r="C23" s="6"/>
+      <c r="A23" s="5">
+        <v>46368</v>
+      </c>
+      <c r="B23" s="5">
+        <v>46368</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>25</v>
+      </c>
       <c r="D23" s="6"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="7"/>
+      <c r="E23" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F23" s="7">
+        <v>1</v>
+      </c>
       <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
+      <c r="H23" s="6" t="s">
+        <v>47</v>
+      </c>
       <c r="I23" s="6"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="5"/>
-      <c r="B24" s="5"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="7"/>
+      <c r="A24" s="5">
+        <v>46397</v>
+      </c>
+      <c r="B24" s="5">
+        <v>46397</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F24" s="7">
+        <v>1</v>
+      </c>
       <c r="G24" s="6"/>
-      <c r="H24" s="6"/>
+      <c r="H24" s="6" t="s">
+        <v>47</v>
+      </c>
       <c r="I24" s="6"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
@@ -4775,45 +4500,78 @@
       <c r="H302" s="6"/>
       <c r="I302" s="6"/>
     </row>
+    <row r="303" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A303" s="5"/>
+      <c r="B303" s="5"/>
+      <c r="C303" s="6"/>
+      <c r="D303" s="6"/>
+      <c r="E303" s="6"/>
+      <c r="F303" s="7"/>
+      <c r="G303" s="6"/>
+      <c r="H303" s="6"/>
+      <c r="I303" s="6"/>
+    </row>
+    <row r="304" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A304" s="5"/>
+      <c r="B304" s="5"/>
+      <c r="C304" s="6"/>
+      <c r="D304" s="6"/>
+      <c r="E304" s="6"/>
+      <c r="F304" s="7"/>
+      <c r="G304" s="6"/>
+      <c r="H304" s="6"/>
+      <c r="I304" s="6"/>
+    </row>
+    <row r="305" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A305" s="5"/>
+      <c r="B305" s="5"/>
+      <c r="C305" s="6"/>
+      <c r="D305" s="6"/>
+      <c r="E305" s="6"/>
+      <c r="F305" s="7"/>
+      <c r="G305" s="6"/>
+      <c r="H305" s="6"/>
+      <c r="I305" s="6"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I302" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
-  <conditionalFormatting sqref="E2:E302">
-    <cfRule type="expression" dxfId="49" priority="1">
+  <autoFilter ref="A1:I305" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <conditionalFormatting sqref="E2:E305">
+    <cfRule type="expression" dxfId="7" priority="1">
       <formula>$E2="Competición FPCV"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="48" priority="2">
+    <cfRule type="expression" dxfId="6" priority="2">
       <formula>$E2="Campeonato de España"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="47" priority="3">
+    <cfRule type="expression" dxfId="5" priority="3">
       <formula>$E2="Competición Internacional"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="46" priority="4">
+    <cfRule type="expression" dxfId="4" priority="4">
       <formula>$E2="Trofeo Club"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="45" priority="5">
+    <cfRule type="expression" dxfId="3" priority="5">
       <formula>$E2="Curso"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="44" priority="6">
+    <cfRule type="expression" dxfId="2" priority="6">
       <formula>$E2="Reunión"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="43" priority="7">
+    <cfRule type="expression" dxfId="1" priority="7">
       <formula>$E2="Prueba de Acceso"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="42" priority="8">
+    <cfRule type="expression" dxfId="0" priority="8">
       <formula>$E2="Día festivo"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" errorTitle="Valor no válido" error="Elige una categoría de la lista" sqref="E2:E302" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" errorTitle="Valor no válido" error="Elige una categoría de la lista" sqref="E2:E305" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Competición FPCV,Campeonato de España,Competición Internacional,Trofeo Club,Curso,Reunión,Prueba de Acceso,Día festivo"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" errorTitle="Valor no válido" error="Huecos: pon 0, 1 o 2" sqref="F2:F302" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" errorTitle="Valor no válido" error="Huecos: pon 0, 1 o 2" sqref="F2:F305" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"0,1,2"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" errorTitle="Valor no válido" error="Elige Mañana, Tarde o Todo el día" sqref="G2:I302" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" errorTitle="Valor no válido" error="Elige Mañana, Tarde o Todo el día" sqref="G2:I305" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"Mañana,Tarde,Todo el día"</formula1>
     </dataValidation>
-    <dataValidation type="date" operator="greaterThan" allowBlank="1" errorTitle="Fecha" error="Escribe una fecha, por ejemplo 17/10/2026" sqref="A2:B302" xr:uid="{00000000-0002-0000-0100-000003000000}">
+    <dataValidation type="date" operator="greaterThan" allowBlank="1" errorTitle="Fecha" error="Escribe una fecha, por ejemplo 17/10/2026" sqref="A2:B305" xr:uid="{00000000-0002-0000-0100-000003000000}">
       <formula1>36526</formula1>
     </dataValidation>
   </dataValidations>

--- a/calendario-fpcv-eventos.xlsx
+++ b/calendario-fpcv-eventos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5bbe44e6a3b5fd34/Federación/EVENTOS AÑO 2026/Trofeos Clubes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{4D398B8E-8F88-483F-8CEF-2E75185AB50A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{34DDF576-3AC8-450A-A6F3-64F2FE57B9D2}"/>
+  <xr:revisionPtr revIDLastSave="29" documentId="13_ncr:1_{4D398B8E-8F88-483F-8CEF-2E75185AB50A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1968F625-18FB-4E7C-A86D-5B955293F9B9}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,14 +17,14 @@
     <sheet name="Eventos" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Eventos!$A$1:$I$305</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Eventos!$A$1:$I$307</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="76">
   <si>
     <t>Inicio</t>
   </si>
@@ -224,12 +224,6 @@
     <t>Elecciones Generales</t>
   </si>
   <si>
-    <t>Trofeo Iniciación Azalea</t>
-  </si>
-  <si>
-    <t>Castelló de la Plana</t>
-  </si>
-  <si>
     <t>Día de la Constitución</t>
   </si>
   <si>
@@ -252,6 +246,12 @@
   </si>
   <si>
     <t>Quart</t>
+  </si>
+  <si>
+    <t>Navidad</t>
+  </si>
+  <si>
+    <t>2º día Navidad</t>
   </si>
 </sst>
 </file>
@@ -420,6 +420,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -839,7 +843,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I305"/>
+  <dimension ref="A1:I307"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="13" customWidth="1"/>
@@ -887,10 +891,10 @@
         <v>46298</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>17</v>
@@ -910,10 +914,10 @@
         <v>46313</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>50</v>
@@ -935,10 +939,10 @@
         <v>46312</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>13</v>
@@ -1087,7 +1091,7 @@
         <v>46327</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D10" s="6"/>
       <c r="E10" s="6" t="s">
@@ -1379,7 +1383,7 @@
         <v>46362</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D22" s="6"/>
       <c r="E22" s="6" t="s">
@@ -1404,7 +1408,9 @@
       <c r="C23" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D23" s="6"/>
+      <c r="D23" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="E23" s="6" t="s">
         <v>13</v>
       </c>
@@ -1419,22 +1425,20 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="5">
-        <v>46397</v>
+        <v>46381</v>
       </c>
       <c r="B24" s="5">
-        <v>46397</v>
+        <v>46381</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>67</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="D24" s="6"/>
       <c r="E24" s="6" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="F24" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G24" s="6"/>
       <c r="H24" s="6" t="s">
@@ -1443,14 +1447,26 @@
       <c r="I24" s="6"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="5"/>
-      <c r="B25" s="5"/>
-      <c r="C25" s="6"/>
+      <c r="A25" s="5">
+        <v>46382</v>
+      </c>
+      <c r="B25" s="5">
+        <v>46382</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="7"/>
+      <c r="E25" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F25" s="7">
+        <v>2</v>
+      </c>
       <c r="G25" s="6"/>
-      <c r="H25" s="6"/>
+      <c r="H25" s="6" t="s">
+        <v>47</v>
+      </c>
       <c r="I25" s="6"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
@@ -4533,9 +4549,31 @@
       <c r="H305" s="6"/>
       <c r="I305" s="6"/>
     </row>
+    <row r="306" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A306" s="5"/>
+      <c r="B306" s="5"/>
+      <c r="C306" s="6"/>
+      <c r="D306" s="6"/>
+      <c r="E306" s="6"/>
+      <c r="F306" s="7"/>
+      <c r="G306" s="6"/>
+      <c r="H306" s="6"/>
+      <c r="I306" s="6"/>
+    </row>
+    <row r="307" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A307" s="5"/>
+      <c r="B307" s="5"/>
+      <c r="C307" s="6"/>
+      <c r="D307" s="6"/>
+      <c r="E307" s="6"/>
+      <c r="F307" s="7"/>
+      <c r="G307" s="6"/>
+      <c r="H307" s="6"/>
+      <c r="I307" s="6"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I305" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
-  <conditionalFormatting sqref="E2:E305">
+  <autoFilter ref="A1:I307" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <conditionalFormatting sqref="E2:E307">
     <cfRule type="expression" dxfId="7" priority="1">
       <formula>$E2="Competición FPCV"</formula>
     </cfRule>
@@ -4562,16 +4600,16 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" errorTitle="Valor no válido" error="Elige una categoría de la lista" sqref="E2:E305" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" errorTitle="Valor no válido" error="Elige una categoría de la lista" sqref="E2:E307" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Competición FPCV,Campeonato de España,Competición Internacional,Trofeo Club,Curso,Reunión,Prueba de Acceso,Día festivo"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" errorTitle="Valor no válido" error="Huecos: pon 0, 1 o 2" sqref="F2:F305" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" errorTitle="Valor no válido" error="Huecos: pon 0, 1 o 2" sqref="F2:F307" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"0,1,2"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" errorTitle="Valor no válido" error="Elige Mañana, Tarde o Todo el día" sqref="G2:I305" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" errorTitle="Valor no válido" error="Elige Mañana, Tarde o Todo el día" sqref="G2:I307" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"Mañana,Tarde,Todo el día"</formula1>
     </dataValidation>
-    <dataValidation type="date" operator="greaterThan" allowBlank="1" errorTitle="Fecha" error="Escribe una fecha, por ejemplo 17/10/2026" sqref="A2:B305" xr:uid="{00000000-0002-0000-0100-000003000000}">
+    <dataValidation type="date" operator="greaterThan" allowBlank="1" errorTitle="Fecha" error="Escribe una fecha, por ejemplo 17/10/2026" sqref="A2:B307" xr:uid="{00000000-0002-0000-0100-000003000000}">
       <formula1>36526</formula1>
     </dataValidation>
   </dataValidations>

--- a/calendario-fpcv-eventos.xlsx
+++ b/calendario-fpcv-eventos.xlsx
@@ -194,7 +194,7 @@
     <t>Rafelbunyol</t>
   </si>
   <si>
-    <t>Trofeo Iniciación Llombai</t>
+    <t>Trofeo Iniciación Marquesat</t>
   </si>
   <si>
     <t>Llombai</t>
